--- a/Budget_Manager_Superpowered.xlsx
+++ b/Budget_Manager_Superpowered.xlsx
@@ -88,7 +88,7 @@
     <numFmt numFmtId="171" formatCode="0.00&quot;%&quot;"/>
     <numFmt numFmtId="172" formatCode="#,##0.0000"/>
   </numFmts>
-  <fonts count="52">
+  <fonts count="49">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -351,7 +351,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00E2E8F0"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
@@ -397,27 +397,10 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="0094A3B8"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <color rgb="000F1117"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <color rgb="003B82F6"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -781,7 +764,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="182">
+  <cellXfs count="180">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1121,25 +1104,33 @@
     <xf numFmtId="169" fontId="43" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="43" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="38" fillId="13" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="170" fontId="44" fillId="17" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="44" fillId="17" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="44" fillId="17" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="17" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="44" fillId="17" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="170" fontId="44" fillId="16" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="44" fillId="16" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="44" fillId="16" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="16" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="44" fillId="16" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="39" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1148,18 +1139,10 @@
     <xf numFmtId="0" fontId="40" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="17" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="41" fillId="17" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="17" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="41" fillId="16" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="16" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="16" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1168,7 +1151,7 @@
     <xf numFmtId="171" fontId="43" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="44" fillId="17" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1183,9 +1166,6 @@
     </xf>
     <xf numFmtId="171" fontId="0" fillId="17" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="17" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="16" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1202,18 +1182,19 @@
     <xf numFmtId="171" fontId="0" fillId="16" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="16" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="48" fillId="13" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="13" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="51" fillId="13" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="48" fillId="13" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
   </cellStyles>
-  <dxfs count="77">
+  <dxfs count="76">
     <dxf>
       <fill>
         <patternFill>
@@ -2039,16 +2020,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="003B0A0A"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="0094A3B8"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="001A1D27"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5127,21 +5098,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Month</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -5154,21 +5110,6 @@
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Amount (USD)</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -5196,7 +5137,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Subscription Cost Breakdown</a:t>
+              <a:t>Monthly Cost by Subscription</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -5210,7 +5151,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Subscriptions'!H6</f>
+              <f>'Subscriptions'!G6</f>
             </strRef>
           </tx>
           <spPr>
@@ -5225,7 +5166,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Subscriptions'!$H$7:$H$57</f>
+              <f>'Subscriptions'!$G$7:$G$57</f>
             </numRef>
           </val>
         </ser>
@@ -5289,122 +5230,6 @@
         </ser>
         <firstSliceAng val="0"/>
       </pieChart>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Gain / Loss by Holding</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Portfolio'!G6</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="F59E0B"/>
-            </a:solidFill>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Portfolio'!$A$8:$A$57</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Portfolio'!$G$7:$G$57</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Ticker</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>USD</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
     </plotArea>
     <legend>
       <legendPos val="r"/>
@@ -5559,7 +5384,7 @@
       <row>210</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="4320000"/>
+    <ext cx="7920000" cy="5040000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -5586,7 +5411,7 @@
       <row>59</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6480000" cy="4320000"/>
+    <ext cx="6480000" cy="4680000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -5613,7 +5438,7 @@
       <row>60</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6480000" cy="4320000"/>
+    <ext cx="6480000" cy="4680000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -5623,28 +5448,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>60</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6480000" cy="4320000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -5711,7 +5514,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Transactions" displayName="Transactions" ref="A6:H207" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TxLedger" displayName="TxLedger" ref="A6:H207" headerRowCount="1">
   <autoFilter ref="A6:H207"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date"/>
@@ -5723,12 +5526,12 @@
     <tableColumn id="7" name="Flagged?"/>
     <tableColumn id="8" name="Effective Date"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleDark2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleDark2" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Subscriptions" displayName="Subscriptions" ref="A6:I57" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="SubTracker" displayName="SubTracker" ref="A6:I57" headerRowCount="1">
   <autoFilter ref="A6:I57"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Service Name"/>
@@ -5738,7 +5541,7 @@
     <tableColumn id="5" name="Notes"/>
     <tableColumn id="6" name="Last Paid Date"/>
     <tableColumn id="7" name="Monthly Equiv"/>
-    <tableColumn id="8" name="Monthly Cost"/>
+    <tableColumn id="8" name="Annual Equiv"/>
     <tableColumn id="9" name="Status"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark9" showRowStripes="1"/>
@@ -5746,18 +5549,17 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Portfolio" displayName="Portfolio" ref="A6:I57" headerRowCount="1">
-  <autoFilter ref="A6:I57"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Holdings" displayName="Holdings" ref="A6:H57" headerRowCount="1">
+  <autoFilter ref="A6:H57"/>
+  <tableColumns count="8">
     <tableColumn id="1" name="Ticker"/>
     <tableColumn id="2" name="Company Name"/>
     <tableColumn id="3" name="Shares"/>
-    <tableColumn id="4" name="Current Value"/>
-    <tableColumn id="5" name="Price/Share"/>
+    <tableColumn id="4" name="Market Value"/>
+    <tableColumn id="5" name="Price / Share"/>
     <tableColumn id="6" name="Cost Basis"/>
     <tableColumn id="7" name="Gain / Loss"/>
     <tableColumn id="8" name="% of Portfolio"/>
-    <tableColumn id="9" name="Allocation"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark3" showRowStripes="1"/>
 </table>
@@ -6396,27 +6198,26 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="164" t="inlineStr">
         <is>
-          <t>📈 INVESTMENT PORTFOLIO</t>
+          <t>INVESTMENT PORTFOLIO</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" ht="18" customHeight="1">
       <c r="A2" s="142" t="inlineStr">
         <is>
-          <t>Track your holdings · Enter ticker, shares, current price, and cost basis manually</t>
+          <t>Enter Ticker, Shares, Price/Share, and Cost Basis  ·  Value auto-calculates</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6239,7 @@
       </c>
       <c r="G3" s="143" t="inlineStr">
         <is>
-          <t>GAIN/LOSS %</t>
+          <t>RETURN %</t>
         </is>
       </c>
     </row>
@@ -6452,64 +6253,59 @@
         <v/>
       </c>
       <c r="E4" s="144">
-        <f>IFERROR(E4-E3,0)</f>
+        <f>A4-C4</f>
         <v/>
       </c>
       <c r="G4" s="165">
-        <f>IFERROR((E4-E3)/E3*100,0)</f>
+        <f>IFERROR((A4-C4)/C4*100,0)</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="8" customHeight="1"/>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="145" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="146" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B6" s="145" t="inlineStr">
+      <c r="B6" s="146" t="inlineStr">
         <is>
           <t>Company Name</t>
         </is>
       </c>
-      <c r="C6" s="145" t="inlineStr">
+      <c r="C6" s="146" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D6" s="145" t="inlineStr">
+      <c r="D6" s="146" t="inlineStr">
         <is>
-          <t>Current Value</t>
+          <t>Market Value</t>
         </is>
       </c>
-      <c r="E6" s="145" t="inlineStr">
+      <c r="E6" s="146" t="inlineStr">
         <is>
-          <t>Price/Share</t>
+          <t>Price / Share</t>
         </is>
       </c>
-      <c r="F6" s="145" t="inlineStr">
+      <c r="F6" s="146" t="inlineStr">
         <is>
           <t>Cost Basis</t>
         </is>
       </c>
-      <c r="G6" s="145" t="inlineStr">
+      <c r="G6" s="146" t="inlineStr">
         <is>
           <t>Gain / Loss</t>
         </is>
       </c>
-      <c r="H6" s="145" t="inlineStr">
+      <c r="H6" s="146" t="inlineStr">
         <is>
           <t>% of Portfolio</t>
         </is>
       </c>
-      <c r="I6" s="145" t="inlineStr">
-        <is>
-          <t>Allocation</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="D7" s="166">
+      <c r="I7" s="166">
         <f>IFERROR(SUMPRODUCT((A8:A57&lt;&gt;"")*D8:D57),1)</f>
         <v/>
       </c>
@@ -6529,34 +6325,26 @@
         <v/>
       </c>
       <c r="H8" s="171">
-        <f>IFERROR(IF(A8="","",D8/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I8" s="172">
-        <f>IFERROR(IF(A8="","",REPT("█",ROUND(D8/$D$7*20,0))),"")</f>
+        <f>IFERROR(IF(A8="","",D8/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="173" t="n"/>
-      <c r="B9" s="173" t="n"/>
-      <c r="C9" s="174" t="n"/>
-      <c r="D9" s="175">
+      <c r="A9" s="172" t="n"/>
+      <c r="B9" s="172" t="n"/>
+      <c r="C9" s="173" t="n"/>
+      <c r="D9" s="174">
         <f>IFERROR(IF(A9="","",C9*E9),"")</f>
         <v/>
       </c>
-      <c r="E9" s="176" t="n"/>
-      <c r="F9" s="176" t="n"/>
-      <c r="G9" s="175">
+      <c r="E9" s="175" t="n"/>
+      <c r="F9" s="175" t="n"/>
+      <c r="G9" s="174">
         <f>IFERROR(IF(A9="","",D9-F9),"")</f>
         <v/>
       </c>
-      <c r="H9" s="177">
-        <f>IFERROR(IF(A9="","",D9/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I9" s="178">
-        <f>IFERROR(IF(A9="","",REPT("█",ROUND(D9/$D$7*20,0))),"")</f>
+      <c r="H9" s="176">
+        <f>IFERROR(IF(A9="","",D9/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
@@ -6575,34 +6363,26 @@
         <v/>
       </c>
       <c r="H10" s="171">
-        <f>IFERROR(IF(A10="","",D10/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I10" s="172">
-        <f>IFERROR(IF(A10="","",REPT("█",ROUND(D10/$D$7*20,0))),"")</f>
+        <f>IFERROR(IF(A10="","",D10/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="173" t="n"/>
-      <c r="B11" s="173" t="n"/>
-      <c r="C11" s="174" t="n"/>
-      <c r="D11" s="175">
+      <c r="A11" s="172" t="n"/>
+      <c r="B11" s="172" t="n"/>
+      <c r="C11" s="173" t="n"/>
+      <c r="D11" s="174">
         <f>IFERROR(IF(A11="","",C11*E11),"")</f>
         <v/>
       </c>
-      <c r="E11" s="176" t="n"/>
-      <c r="F11" s="176" t="n"/>
-      <c r="G11" s="175">
+      <c r="E11" s="175" t="n"/>
+      <c r="F11" s="175" t="n"/>
+      <c r="G11" s="174">
         <f>IFERROR(IF(A11="","",D11-F11),"")</f>
         <v/>
       </c>
-      <c r="H11" s="177">
-        <f>IFERROR(IF(A11="","",D11/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I11" s="178">
-        <f>IFERROR(IF(A11="","",REPT("█",ROUND(D11/$D$7*20,0))),"")</f>
+      <c r="H11" s="176">
+        <f>IFERROR(IF(A11="","",D11/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
@@ -6621,34 +6401,26 @@
         <v/>
       </c>
       <c r="H12" s="171">
-        <f>IFERROR(IF(A12="","",D12/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I12" s="172">
-        <f>IFERROR(IF(A12="","",REPT("█",ROUND(D12/$D$7*20,0))),"")</f>
+        <f>IFERROR(IF(A12="","",D12/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="173" t="n"/>
-      <c r="B13" s="173" t="n"/>
-      <c r="C13" s="174" t="n"/>
-      <c r="D13" s="175">
+      <c r="A13" s="172" t="n"/>
+      <c r="B13" s="172" t="n"/>
+      <c r="C13" s="173" t="n"/>
+      <c r="D13" s="174">
         <f>IFERROR(IF(A13="","",C13*E13),"")</f>
         <v/>
       </c>
-      <c r="E13" s="176" t="n"/>
-      <c r="F13" s="176" t="n"/>
-      <c r="G13" s="175">
+      <c r="E13" s="175" t="n"/>
+      <c r="F13" s="175" t="n"/>
+      <c r="G13" s="174">
         <f>IFERROR(IF(A13="","",D13-F13),"")</f>
         <v/>
       </c>
-      <c r="H13" s="177">
-        <f>IFERROR(IF(A13="","",D13/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I13" s="178">
-        <f>IFERROR(IF(A13="","",REPT("█",ROUND(D13/$D$7*20,0))),"")</f>
+      <c r="H13" s="176">
+        <f>IFERROR(IF(A13="","",D13/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
@@ -6667,34 +6439,26 @@
         <v/>
       </c>
       <c r="H14" s="171">
-        <f>IFERROR(IF(A14="","",D14/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I14" s="172">
-        <f>IFERROR(IF(A14="","",REPT("█",ROUND(D14/$D$7*20,0))),"")</f>
+        <f>IFERROR(IF(A14="","",D14/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="173" t="n"/>
-      <c r="B15" s="173" t="n"/>
-      <c r="C15" s="174" t="n"/>
-      <c r="D15" s="175">
+      <c r="A15" s="172" t="n"/>
+      <c r="B15" s="172" t="n"/>
+      <c r="C15" s="173" t="n"/>
+      <c r="D15" s="174">
         <f>IFERROR(IF(A15="","",C15*E15),"")</f>
         <v/>
       </c>
-      <c r="E15" s="176" t="n"/>
-      <c r="F15" s="176" t="n"/>
-      <c r="G15" s="175">
+      <c r="E15" s="175" t="n"/>
+      <c r="F15" s="175" t="n"/>
+      <c r="G15" s="174">
         <f>IFERROR(IF(A15="","",D15-F15),"")</f>
         <v/>
       </c>
-      <c r="H15" s="177">
-        <f>IFERROR(IF(A15="","",D15/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I15" s="178">
-        <f>IFERROR(IF(A15="","",REPT("█",ROUND(D15/$D$7*20,0))),"")</f>
+      <c r="H15" s="176">
+        <f>IFERROR(IF(A15="","",D15/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
@@ -6713,34 +6477,26 @@
         <v/>
       </c>
       <c r="H16" s="171">
-        <f>IFERROR(IF(A16="","",D16/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I16" s="172">
-        <f>IFERROR(IF(A16="","",REPT("█",ROUND(D16/$D$7*20,0))),"")</f>
+        <f>IFERROR(IF(A16="","",D16/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="173" t="n"/>
-      <c r="B17" s="173" t="n"/>
-      <c r="C17" s="174" t="n"/>
-      <c r="D17" s="175">
+      <c r="A17" s="172" t="n"/>
+      <c r="B17" s="172" t="n"/>
+      <c r="C17" s="173" t="n"/>
+      <c r="D17" s="174">
         <f>IFERROR(IF(A17="","",C17*E17),"")</f>
         <v/>
       </c>
-      <c r="E17" s="176" t="n"/>
-      <c r="F17" s="176" t="n"/>
-      <c r="G17" s="175">
+      <c r="E17" s="175" t="n"/>
+      <c r="F17" s="175" t="n"/>
+      <c r="G17" s="174">
         <f>IFERROR(IF(A17="","",D17-F17),"")</f>
         <v/>
       </c>
-      <c r="H17" s="177">
-        <f>IFERROR(IF(A17="","",D17/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I17" s="178">
-        <f>IFERROR(IF(A17="","",REPT("█",ROUND(D17/$D$7*20,0))),"")</f>
+      <c r="H17" s="176">
+        <f>IFERROR(IF(A17="","",D17/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
@@ -6759,34 +6515,26 @@
         <v/>
       </c>
       <c r="H18" s="171">
-        <f>IFERROR(IF(A18="","",D18/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I18" s="172">
-        <f>IFERROR(IF(A18="","",REPT("█",ROUND(D18/$D$7*20,0))),"")</f>
+        <f>IFERROR(IF(A18="","",D18/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="173" t="n"/>
-      <c r="B19" s="173" t="n"/>
-      <c r="C19" s="174" t="n"/>
-      <c r="D19" s="175">
+      <c r="A19" s="172" t="n"/>
+      <c r="B19" s="172" t="n"/>
+      <c r="C19" s="173" t="n"/>
+      <c r="D19" s="174">
         <f>IFERROR(IF(A19="","",C19*E19),"")</f>
         <v/>
       </c>
-      <c r="E19" s="176" t="n"/>
-      <c r="F19" s="176" t="n"/>
-      <c r="G19" s="175">
+      <c r="E19" s="175" t="n"/>
+      <c r="F19" s="175" t="n"/>
+      <c r="G19" s="174">
         <f>IFERROR(IF(A19="","",D19-F19),"")</f>
         <v/>
       </c>
-      <c r="H19" s="177">
-        <f>IFERROR(IF(A19="","",D19/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I19" s="178">
-        <f>IFERROR(IF(A19="","",REPT("█",ROUND(D19/$D$7*20,0))),"")</f>
+      <c r="H19" s="176">
+        <f>IFERROR(IF(A19="","",D19/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
@@ -6805,34 +6553,26 @@
         <v/>
       </c>
       <c r="H20" s="171">
-        <f>IFERROR(IF(A20="","",D20/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I20" s="172">
-        <f>IFERROR(IF(A20="","",REPT("█",ROUND(D20/$D$7*20,0))),"")</f>
+        <f>IFERROR(IF(A20="","",D20/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="173" t="n"/>
-      <c r="B21" s="173" t="n"/>
-      <c r="C21" s="174" t="n"/>
-      <c r="D21" s="175">
+      <c r="A21" s="172" t="n"/>
+      <c r="B21" s="172" t="n"/>
+      <c r="C21" s="173" t="n"/>
+      <c r="D21" s="174">
         <f>IFERROR(IF(A21="","",C21*E21),"")</f>
         <v/>
       </c>
-      <c r="E21" s="176" t="n"/>
-      <c r="F21" s="176" t="n"/>
-      <c r="G21" s="175">
+      <c r="E21" s="175" t="n"/>
+      <c r="F21" s="175" t="n"/>
+      <c r="G21" s="174">
         <f>IFERROR(IF(A21="","",D21-F21),"")</f>
         <v/>
       </c>
-      <c r="H21" s="177">
-        <f>IFERROR(IF(A21="","",D21/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I21" s="178">
-        <f>IFERROR(IF(A21="","",REPT("█",ROUND(D21/$D$7*20,0))),"")</f>
+      <c r="H21" s="176">
+        <f>IFERROR(IF(A21="","",D21/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
@@ -6851,34 +6591,26 @@
         <v/>
       </c>
       <c r="H22" s="171">
-        <f>IFERROR(IF(A22="","",D22/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I22" s="172">
-        <f>IFERROR(IF(A22="","",REPT("█",ROUND(D22/$D$7*20,0))),"")</f>
+        <f>IFERROR(IF(A22="","",D22/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="173" t="n"/>
-      <c r="B23" s="173" t="n"/>
-      <c r="C23" s="174" t="n"/>
-      <c r="D23" s="175">
+      <c r="A23" s="172" t="n"/>
+      <c r="B23" s="172" t="n"/>
+      <c r="C23" s="173" t="n"/>
+      <c r="D23" s="174">
         <f>IFERROR(IF(A23="","",C23*E23),"")</f>
         <v/>
       </c>
-      <c r="E23" s="176" t="n"/>
-      <c r="F23" s="176" t="n"/>
-      <c r="G23" s="175">
+      <c r="E23" s="175" t="n"/>
+      <c r="F23" s="175" t="n"/>
+      <c r="G23" s="174">
         <f>IFERROR(IF(A23="","",D23-F23),"")</f>
         <v/>
       </c>
-      <c r="H23" s="177">
-        <f>IFERROR(IF(A23="","",D23/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I23" s="178">
-        <f>IFERROR(IF(A23="","",REPT("█",ROUND(D23/$D$7*20,0))),"")</f>
+      <c r="H23" s="176">
+        <f>IFERROR(IF(A23="","",D23/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
@@ -6897,34 +6629,26 @@
         <v/>
       </c>
       <c r="H24" s="171">
-        <f>IFERROR(IF(A24="","",D24/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I24" s="172">
-        <f>IFERROR(IF(A24="","",REPT("█",ROUND(D24/$D$7*20,0))),"")</f>
+        <f>IFERROR(IF(A24="","",D24/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="173" t="n"/>
-      <c r="B25" s="173" t="n"/>
-      <c r="C25" s="174" t="n"/>
-      <c r="D25" s="175">
+      <c r="A25" s="172" t="n"/>
+      <c r="B25" s="172" t="n"/>
+      <c r="C25" s="173" t="n"/>
+      <c r="D25" s="174">
         <f>IFERROR(IF(A25="","",C25*E25),"")</f>
         <v/>
       </c>
-      <c r="E25" s="176" t="n"/>
-      <c r="F25" s="176" t="n"/>
-      <c r="G25" s="175">
+      <c r="E25" s="175" t="n"/>
+      <c r="F25" s="175" t="n"/>
+      <c r="G25" s="174">
         <f>IFERROR(IF(A25="","",D25-F25),"")</f>
         <v/>
       </c>
-      <c r="H25" s="177">
-        <f>IFERROR(IF(A25="","",D25/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I25" s="178">
-        <f>IFERROR(IF(A25="","",REPT("█",ROUND(D25/$D$7*20,0))),"")</f>
+      <c r="H25" s="176">
+        <f>IFERROR(IF(A25="","",D25/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
@@ -6943,34 +6667,26 @@
         <v/>
       </c>
       <c r="H26" s="171">
-        <f>IFERROR(IF(A26="","",D26/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I26" s="172">
-        <f>IFERROR(IF(A26="","",REPT("█",ROUND(D26/$D$7*20,0))),"")</f>
+        <f>IFERROR(IF(A26="","",D26/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="173" t="n"/>
-      <c r="B27" s="173" t="n"/>
-      <c r="C27" s="174" t="n"/>
-      <c r="D27" s="175">
+      <c r="A27" s="172" t="n"/>
+      <c r="B27" s="172" t="n"/>
+      <c r="C27" s="173" t="n"/>
+      <c r="D27" s="174">
         <f>IFERROR(IF(A27="","",C27*E27),"")</f>
         <v/>
       </c>
-      <c r="E27" s="176" t="n"/>
-      <c r="F27" s="176" t="n"/>
-      <c r="G27" s="175">
+      <c r="E27" s="175" t="n"/>
+      <c r="F27" s="175" t="n"/>
+      <c r="G27" s="174">
         <f>IFERROR(IF(A27="","",D27-F27),"")</f>
         <v/>
       </c>
-      <c r="H27" s="177">
-        <f>IFERROR(IF(A27="","",D27/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I27" s="178">
-        <f>IFERROR(IF(A27="","",REPT("█",ROUND(D27/$D$7*20,0))),"")</f>
+      <c r="H27" s="176">
+        <f>IFERROR(IF(A27="","",D27/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
@@ -6989,34 +6705,26 @@
         <v/>
       </c>
       <c r="H28" s="171">
-        <f>IFERROR(IF(A28="","",D28/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I28" s="172">
-        <f>IFERROR(IF(A28="","",REPT("█",ROUND(D28/$D$7*20,0))),"")</f>
+        <f>IFERROR(IF(A28="","",D28/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="173" t="n"/>
-      <c r="B29" s="173" t="n"/>
-      <c r="C29" s="174" t="n"/>
-      <c r="D29" s="175">
+      <c r="A29" s="172" t="n"/>
+      <c r="B29" s="172" t="n"/>
+      <c r="C29" s="173" t="n"/>
+      <c r="D29" s="174">
         <f>IFERROR(IF(A29="","",C29*E29),"")</f>
         <v/>
       </c>
-      <c r="E29" s="176" t="n"/>
-      <c r="F29" s="176" t="n"/>
-      <c r="G29" s="175">
+      <c r="E29" s="175" t="n"/>
+      <c r="F29" s="175" t="n"/>
+      <c r="G29" s="174">
         <f>IFERROR(IF(A29="","",D29-F29),"")</f>
         <v/>
       </c>
-      <c r="H29" s="177">
-        <f>IFERROR(IF(A29="","",D29/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I29" s="178">
-        <f>IFERROR(IF(A29="","",REPT("█",ROUND(D29/$D$7*20,0))),"")</f>
+      <c r="H29" s="176">
+        <f>IFERROR(IF(A29="","",D29/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
@@ -7035,34 +6743,26 @@
         <v/>
       </c>
       <c r="H30" s="171">
-        <f>IFERROR(IF(A30="","",D30/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I30" s="172">
-        <f>IFERROR(IF(A30="","",REPT("█",ROUND(D30/$D$7*20,0))),"")</f>
+        <f>IFERROR(IF(A30="","",D30/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="173" t="n"/>
-      <c r="B31" s="173" t="n"/>
-      <c r="C31" s="174" t="n"/>
-      <c r="D31" s="175">
+      <c r="A31" s="172" t="n"/>
+      <c r="B31" s="172" t="n"/>
+      <c r="C31" s="173" t="n"/>
+      <c r="D31" s="174">
         <f>IFERROR(IF(A31="","",C31*E31),"")</f>
         <v/>
       </c>
-      <c r="E31" s="176" t="n"/>
-      <c r="F31" s="176" t="n"/>
-      <c r="G31" s="175">
+      <c r="E31" s="175" t="n"/>
+      <c r="F31" s="175" t="n"/>
+      <c r="G31" s="174">
         <f>IFERROR(IF(A31="","",D31-F31),"")</f>
         <v/>
       </c>
-      <c r="H31" s="177">
-        <f>IFERROR(IF(A31="","",D31/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I31" s="178">
-        <f>IFERROR(IF(A31="","",REPT("█",ROUND(D31/$D$7*20,0))),"")</f>
+      <c r="H31" s="176">
+        <f>IFERROR(IF(A31="","",D31/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
@@ -7081,34 +6781,26 @@
         <v/>
       </c>
       <c r="H32" s="171">
-        <f>IFERROR(IF(A32="","",D32/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I32" s="172">
-        <f>IFERROR(IF(A32="","",REPT("█",ROUND(D32/$D$7*20,0))),"")</f>
+        <f>IFERROR(IF(A32="","",D32/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="173" t="n"/>
-      <c r="B33" s="173" t="n"/>
-      <c r="C33" s="174" t="n"/>
-      <c r="D33" s="175">
+      <c r="A33" s="172" t="n"/>
+      <c r="B33" s="172" t="n"/>
+      <c r="C33" s="173" t="n"/>
+      <c r="D33" s="174">
         <f>IFERROR(IF(A33="","",C33*E33),"")</f>
         <v/>
       </c>
-      <c r="E33" s="176" t="n"/>
-      <c r="F33" s="176" t="n"/>
-      <c r="G33" s="175">
+      <c r="E33" s="175" t="n"/>
+      <c r="F33" s="175" t="n"/>
+      <c r="G33" s="174">
         <f>IFERROR(IF(A33="","",D33-F33),"")</f>
         <v/>
       </c>
-      <c r="H33" s="177">
-        <f>IFERROR(IF(A33="","",D33/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I33" s="178">
-        <f>IFERROR(IF(A33="","",REPT("█",ROUND(D33/$D$7*20,0))),"")</f>
+      <c r="H33" s="176">
+        <f>IFERROR(IF(A33="","",D33/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
@@ -7127,34 +6819,26 @@
         <v/>
       </c>
       <c r="H34" s="171">
-        <f>IFERROR(IF(A34="","",D34/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I34" s="172">
-        <f>IFERROR(IF(A34="","",REPT("█",ROUND(D34/$D$7*20,0))),"")</f>
+        <f>IFERROR(IF(A34="","",D34/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="173" t="n"/>
-      <c r="B35" s="173" t="n"/>
-      <c r="C35" s="174" t="n"/>
-      <c r="D35" s="175">
+      <c r="A35" s="172" t="n"/>
+      <c r="B35" s="172" t="n"/>
+      <c r="C35" s="173" t="n"/>
+      <c r="D35" s="174">
         <f>IFERROR(IF(A35="","",C35*E35),"")</f>
         <v/>
       </c>
-      <c r="E35" s="176" t="n"/>
-      <c r="F35" s="176" t="n"/>
-      <c r="G35" s="175">
+      <c r="E35" s="175" t="n"/>
+      <c r="F35" s="175" t="n"/>
+      <c r="G35" s="174">
         <f>IFERROR(IF(A35="","",D35-F35),"")</f>
         <v/>
       </c>
-      <c r="H35" s="177">
-        <f>IFERROR(IF(A35="","",D35/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I35" s="178">
-        <f>IFERROR(IF(A35="","",REPT("█",ROUND(D35/$D$7*20,0))),"")</f>
+      <c r="H35" s="176">
+        <f>IFERROR(IF(A35="","",D35/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
@@ -7173,34 +6857,26 @@
         <v/>
       </c>
       <c r="H36" s="171">
-        <f>IFERROR(IF(A36="","",D36/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I36" s="172">
-        <f>IFERROR(IF(A36="","",REPT("█",ROUND(D36/$D$7*20,0))),"")</f>
+        <f>IFERROR(IF(A36="","",D36/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="173" t="n"/>
-      <c r="B37" s="173" t="n"/>
-      <c r="C37" s="174" t="n"/>
-      <c r="D37" s="175">
+      <c r="A37" s="172" t="n"/>
+      <c r="B37" s="172" t="n"/>
+      <c r="C37" s="173" t="n"/>
+      <c r="D37" s="174">
         <f>IFERROR(IF(A37="","",C37*E37),"")</f>
         <v/>
       </c>
-      <c r="E37" s="176" t="n"/>
-      <c r="F37" s="176" t="n"/>
-      <c r="G37" s="175">
+      <c r="E37" s="175" t="n"/>
+      <c r="F37" s="175" t="n"/>
+      <c r="G37" s="174">
         <f>IFERROR(IF(A37="","",D37-F37),"")</f>
         <v/>
       </c>
-      <c r="H37" s="177">
-        <f>IFERROR(IF(A37="","",D37/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I37" s="178">
-        <f>IFERROR(IF(A37="","",REPT("█",ROUND(D37/$D$7*20,0))),"")</f>
+      <c r="H37" s="176">
+        <f>IFERROR(IF(A37="","",D37/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
@@ -7219,34 +6895,26 @@
         <v/>
       </c>
       <c r="H38" s="171">
-        <f>IFERROR(IF(A38="","",D38/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I38" s="172">
-        <f>IFERROR(IF(A38="","",REPT("█",ROUND(D38/$D$7*20,0))),"")</f>
+        <f>IFERROR(IF(A38="","",D38/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="173" t="n"/>
-      <c r="B39" s="173" t="n"/>
-      <c r="C39" s="174" t="n"/>
-      <c r="D39" s="175">
+      <c r="A39" s="172" t="n"/>
+      <c r="B39" s="172" t="n"/>
+      <c r="C39" s="173" t="n"/>
+      <c r="D39" s="174">
         <f>IFERROR(IF(A39="","",C39*E39),"")</f>
         <v/>
       </c>
-      <c r="E39" s="176" t="n"/>
-      <c r="F39" s="176" t="n"/>
-      <c r="G39" s="175">
+      <c r="E39" s="175" t="n"/>
+      <c r="F39" s="175" t="n"/>
+      <c r="G39" s="174">
         <f>IFERROR(IF(A39="","",D39-F39),"")</f>
         <v/>
       </c>
-      <c r="H39" s="177">
-        <f>IFERROR(IF(A39="","",D39/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I39" s="178">
-        <f>IFERROR(IF(A39="","",REPT("█",ROUND(D39/$D$7*20,0))),"")</f>
+      <c r="H39" s="176">
+        <f>IFERROR(IF(A39="","",D39/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
@@ -7265,34 +6933,26 @@
         <v/>
       </c>
       <c r="H40" s="171">
-        <f>IFERROR(IF(A40="","",D40/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I40" s="172">
-        <f>IFERROR(IF(A40="","",REPT("█",ROUND(D40/$D$7*20,0))),"")</f>
+        <f>IFERROR(IF(A40="","",D40/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="173" t="n"/>
-      <c r="B41" s="173" t="n"/>
-      <c r="C41" s="174" t="n"/>
-      <c r="D41" s="175">
+      <c r="A41" s="172" t="n"/>
+      <c r="B41" s="172" t="n"/>
+      <c r="C41" s="173" t="n"/>
+      <c r="D41" s="174">
         <f>IFERROR(IF(A41="","",C41*E41),"")</f>
         <v/>
       </c>
-      <c r="E41" s="176" t="n"/>
-      <c r="F41" s="176" t="n"/>
-      <c r="G41" s="175">
+      <c r="E41" s="175" t="n"/>
+      <c r="F41" s="175" t="n"/>
+      <c r="G41" s="174">
         <f>IFERROR(IF(A41="","",D41-F41),"")</f>
         <v/>
       </c>
-      <c r="H41" s="177">
-        <f>IFERROR(IF(A41="","",D41/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I41" s="178">
-        <f>IFERROR(IF(A41="","",REPT("█",ROUND(D41/$D$7*20,0))),"")</f>
+      <c r="H41" s="176">
+        <f>IFERROR(IF(A41="","",D41/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
@@ -7311,34 +6971,26 @@
         <v/>
       </c>
       <c r="H42" s="171">
-        <f>IFERROR(IF(A42="","",D42/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I42" s="172">
-        <f>IFERROR(IF(A42="","",REPT("█",ROUND(D42/$D$7*20,0))),"")</f>
+        <f>IFERROR(IF(A42="","",D42/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="173" t="n"/>
-      <c r="B43" s="173" t="n"/>
-      <c r="C43" s="174" t="n"/>
-      <c r="D43" s="175">
+      <c r="A43" s="172" t="n"/>
+      <c r="B43" s="172" t="n"/>
+      <c r="C43" s="173" t="n"/>
+      <c r="D43" s="174">
         <f>IFERROR(IF(A43="","",C43*E43),"")</f>
         <v/>
       </c>
-      <c r="E43" s="176" t="n"/>
-      <c r="F43" s="176" t="n"/>
-      <c r="G43" s="175">
+      <c r="E43" s="175" t="n"/>
+      <c r="F43" s="175" t="n"/>
+      <c r="G43" s="174">
         <f>IFERROR(IF(A43="","",D43-F43),"")</f>
         <v/>
       </c>
-      <c r="H43" s="177">
-        <f>IFERROR(IF(A43="","",D43/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I43" s="178">
-        <f>IFERROR(IF(A43="","",REPT("█",ROUND(D43/$D$7*20,0))),"")</f>
+      <c r="H43" s="176">
+        <f>IFERROR(IF(A43="","",D43/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
@@ -7357,34 +7009,26 @@
         <v/>
       </c>
       <c r="H44" s="171">
-        <f>IFERROR(IF(A44="","",D44/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I44" s="172">
-        <f>IFERROR(IF(A44="","",REPT("█",ROUND(D44/$D$7*20,0))),"")</f>
+        <f>IFERROR(IF(A44="","",D44/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="173" t="n"/>
-      <c r="B45" s="173" t="n"/>
-      <c r="C45" s="174" t="n"/>
-      <c r="D45" s="175">
+      <c r="A45" s="172" t="n"/>
+      <c r="B45" s="172" t="n"/>
+      <c r="C45" s="173" t="n"/>
+      <c r="D45" s="174">
         <f>IFERROR(IF(A45="","",C45*E45),"")</f>
         <v/>
       </c>
-      <c r="E45" s="176" t="n"/>
-      <c r="F45" s="176" t="n"/>
-      <c r="G45" s="175">
+      <c r="E45" s="175" t="n"/>
+      <c r="F45" s="175" t="n"/>
+      <c r="G45" s="174">
         <f>IFERROR(IF(A45="","",D45-F45),"")</f>
         <v/>
       </c>
-      <c r="H45" s="177">
-        <f>IFERROR(IF(A45="","",D45/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I45" s="178">
-        <f>IFERROR(IF(A45="","",REPT("█",ROUND(D45/$D$7*20,0))),"")</f>
+      <c r="H45" s="176">
+        <f>IFERROR(IF(A45="","",D45/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
@@ -7403,34 +7047,26 @@
         <v/>
       </c>
       <c r="H46" s="171">
-        <f>IFERROR(IF(A46="","",D46/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I46" s="172">
-        <f>IFERROR(IF(A46="","",REPT("█",ROUND(D46/$D$7*20,0))),"")</f>
+        <f>IFERROR(IF(A46="","",D46/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="173" t="n"/>
-      <c r="B47" s="173" t="n"/>
-      <c r="C47" s="174" t="n"/>
-      <c r="D47" s="175">
+      <c r="A47" s="172" t="n"/>
+      <c r="B47" s="172" t="n"/>
+      <c r="C47" s="173" t="n"/>
+      <c r="D47" s="174">
         <f>IFERROR(IF(A47="","",C47*E47),"")</f>
         <v/>
       </c>
-      <c r="E47" s="176" t="n"/>
-      <c r="F47" s="176" t="n"/>
-      <c r="G47" s="175">
+      <c r="E47" s="175" t="n"/>
+      <c r="F47" s="175" t="n"/>
+      <c r="G47" s="174">
         <f>IFERROR(IF(A47="","",D47-F47),"")</f>
         <v/>
       </c>
-      <c r="H47" s="177">
-        <f>IFERROR(IF(A47="","",D47/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I47" s="178">
-        <f>IFERROR(IF(A47="","",REPT("█",ROUND(D47/$D$7*20,0))),"")</f>
+      <c r="H47" s="176">
+        <f>IFERROR(IF(A47="","",D47/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
@@ -7449,34 +7085,26 @@
         <v/>
       </c>
       <c r="H48" s="171">
-        <f>IFERROR(IF(A48="","",D48/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I48" s="172">
-        <f>IFERROR(IF(A48="","",REPT("█",ROUND(D48/$D$7*20,0))),"")</f>
+        <f>IFERROR(IF(A48="","",D48/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="173" t="n"/>
-      <c r="B49" s="173" t="n"/>
-      <c r="C49" s="174" t="n"/>
-      <c r="D49" s="175">
+      <c r="A49" s="172" t="n"/>
+      <c r="B49" s="172" t="n"/>
+      <c r="C49" s="173" t="n"/>
+      <c r="D49" s="174">
         <f>IFERROR(IF(A49="","",C49*E49),"")</f>
         <v/>
       </c>
-      <c r="E49" s="176" t="n"/>
-      <c r="F49" s="176" t="n"/>
-      <c r="G49" s="175">
+      <c r="E49" s="175" t="n"/>
+      <c r="F49" s="175" t="n"/>
+      <c r="G49" s="174">
         <f>IFERROR(IF(A49="","",D49-F49),"")</f>
         <v/>
       </c>
-      <c r="H49" s="177">
-        <f>IFERROR(IF(A49="","",D49/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I49" s="178">
-        <f>IFERROR(IF(A49="","",REPT("█",ROUND(D49/$D$7*20,0))),"")</f>
+      <c r="H49" s="176">
+        <f>IFERROR(IF(A49="","",D49/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
@@ -7495,34 +7123,26 @@
         <v/>
       </c>
       <c r="H50" s="171">
-        <f>IFERROR(IF(A50="","",D50/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I50" s="172">
-        <f>IFERROR(IF(A50="","",REPT("█",ROUND(D50/$D$7*20,0))),"")</f>
+        <f>IFERROR(IF(A50="","",D50/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="173" t="n"/>
-      <c r="B51" s="173" t="n"/>
-      <c r="C51" s="174" t="n"/>
-      <c r="D51" s="175">
+      <c r="A51" s="172" t="n"/>
+      <c r="B51" s="172" t="n"/>
+      <c r="C51" s="173" t="n"/>
+      <c r="D51" s="174">
         <f>IFERROR(IF(A51="","",C51*E51),"")</f>
         <v/>
       </c>
-      <c r="E51" s="176" t="n"/>
-      <c r="F51" s="176" t="n"/>
-      <c r="G51" s="175">
+      <c r="E51" s="175" t="n"/>
+      <c r="F51" s="175" t="n"/>
+      <c r="G51" s="174">
         <f>IFERROR(IF(A51="","",D51-F51),"")</f>
         <v/>
       </c>
-      <c r="H51" s="177">
-        <f>IFERROR(IF(A51="","",D51/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I51" s="178">
-        <f>IFERROR(IF(A51="","",REPT("█",ROUND(D51/$D$7*20,0))),"")</f>
+      <c r="H51" s="176">
+        <f>IFERROR(IF(A51="","",D51/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
@@ -7541,34 +7161,26 @@
         <v/>
       </c>
       <c r="H52" s="171">
-        <f>IFERROR(IF(A52="","",D52/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I52" s="172">
-        <f>IFERROR(IF(A52="","",REPT("█",ROUND(D52/$D$7*20,0))),"")</f>
+        <f>IFERROR(IF(A52="","",D52/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="173" t="n"/>
-      <c r="B53" s="173" t="n"/>
-      <c r="C53" s="174" t="n"/>
-      <c r="D53" s="175">
+      <c r="A53" s="172" t="n"/>
+      <c r="B53" s="172" t="n"/>
+      <c r="C53" s="173" t="n"/>
+      <c r="D53" s="174">
         <f>IFERROR(IF(A53="","",C53*E53),"")</f>
         <v/>
       </c>
-      <c r="E53" s="176" t="n"/>
-      <c r="F53" s="176" t="n"/>
-      <c r="G53" s="175">
+      <c r="E53" s="175" t="n"/>
+      <c r="F53" s="175" t="n"/>
+      <c r="G53" s="174">
         <f>IFERROR(IF(A53="","",D53-F53),"")</f>
         <v/>
       </c>
-      <c r="H53" s="177">
-        <f>IFERROR(IF(A53="","",D53/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I53" s="178">
-        <f>IFERROR(IF(A53="","",REPT("█",ROUND(D53/$D$7*20,0))),"")</f>
+      <c r="H53" s="176">
+        <f>IFERROR(IF(A53="","",D53/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
@@ -7587,34 +7199,26 @@
         <v/>
       </c>
       <c r="H54" s="171">
-        <f>IFERROR(IF(A54="","",D54/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I54" s="172">
-        <f>IFERROR(IF(A54="","",REPT("█",ROUND(D54/$D$7*20,0))),"")</f>
+        <f>IFERROR(IF(A54="","",D54/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="173" t="n"/>
-      <c r="B55" s="173" t="n"/>
-      <c r="C55" s="174" t="n"/>
-      <c r="D55" s="175">
+      <c r="A55" s="172" t="n"/>
+      <c r="B55" s="172" t="n"/>
+      <c r="C55" s="173" t="n"/>
+      <c r="D55" s="174">
         <f>IFERROR(IF(A55="","",C55*E55),"")</f>
         <v/>
       </c>
-      <c r="E55" s="176" t="n"/>
-      <c r="F55" s="176" t="n"/>
-      <c r="G55" s="175">
+      <c r="E55" s="175" t="n"/>
+      <c r="F55" s="175" t="n"/>
+      <c r="G55" s="174">
         <f>IFERROR(IF(A55="","",D55-F55),"")</f>
         <v/>
       </c>
-      <c r="H55" s="177">
-        <f>IFERROR(IF(A55="","",D55/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I55" s="178">
-        <f>IFERROR(IF(A55="","",REPT("█",ROUND(D55/$D$7*20,0))),"")</f>
+      <c r="H55" s="176">
+        <f>IFERROR(IF(A55="","",D55/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
@@ -7633,60 +7237,51 @@
         <v/>
       </c>
       <c r="H56" s="171">
-        <f>IFERROR(IF(A56="","",D56/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I56" s="172">
-        <f>IFERROR(IF(A56="","",REPT("█",ROUND(D56/$D$7*20,0))),"")</f>
+        <f>IFERROR(IF(A56="","",D56/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="173" t="n"/>
-      <c r="B57" s="173" t="n"/>
-      <c r="C57" s="174" t="n"/>
-      <c r="D57" s="175">
+      <c r="A57" s="172" t="n"/>
+      <c r="B57" s="172" t="n"/>
+      <c r="C57" s="173" t="n"/>
+      <c r="D57" s="174">
         <f>IFERROR(IF(A57="","",C57*E57),"")</f>
         <v/>
       </c>
-      <c r="E57" s="176" t="n"/>
-      <c r="F57" s="176" t="n"/>
-      <c r="G57" s="175">
+      <c r="E57" s="175" t="n"/>
+      <c r="F57" s="175" t="n"/>
+      <c r="G57" s="174">
         <f>IFERROR(IF(A57="","",D57-F57),"")</f>
         <v/>
       </c>
-      <c r="H57" s="177">
-        <f>IFERROR(IF(A57="","",D57/$D$7*100),"")</f>
-        <v/>
-      </c>
-      <c r="I57" s="178">
-        <f>IFERROR(IF(A57="","",REPT("█",ROUND(D57/$D$7*20,0))),"")</f>
+      <c r="H57" s="176">
+        <f>IFERROR(IF(A57="","",D57/$I$7*100),"")</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="179" t="inlineStr">
+      <c r="A58" s="177" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B58" s="180" t="n"/>
-      <c r="C58" s="180" t="n"/>
-      <c r="D58" s="181">
+      <c r="B58" s="178" t="n"/>
+      <c r="C58" s="178" t="n"/>
+      <c r="D58" s="179">
         <f>SUM(D8:D57)</f>
         <v/>
       </c>
-      <c r="E58" s="180" t="n"/>
-      <c r="F58" s="181">
+      <c r="E58" s="178" t="n"/>
+      <c r="F58" s="179">
         <f>SUM(F8:F57)</f>
         <v/>
       </c>
-      <c r="G58" s="181">
+      <c r="G58" s="179">
         <f>SUM(G8:G57)</f>
         <v/>
       </c>
-      <c r="H58" s="180" t="n"/>
-      <c r="I58" s="180" t="n"/>
+      <c r="H58" s="178" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7700,27 +7295,14 @@
     <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="75">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="76">
-      <formula>0</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8:H57">
-    <cfRule type="dataBar" priority="4">
+    <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min" val="0"/>
         <cfvo type="max"/>
         <color rgb="00F59E0B"/>
       </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I8:I57">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="001E3A5F"/>
-        <color rgb="003B82F6"/>
-      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -31532,22 +31114,22 @@
       </c>
       <c r="N1" s="139" t="inlineStr">
         <is>
-          <t>Income Categories</t>
+          <t>Income Cats</t>
         </is>
       </c>
       <c r="O1" s="139" t="inlineStr">
         <is>
-          <t>Expense Categories</t>
+          <t>Expense Cats</t>
         </is>
       </c>
       <c r="P1" s="139" t="inlineStr">
         <is>
-          <t>Savings Categories</t>
+          <t>Savings Cats</t>
         </is>
       </c>
       <c r="Q1" s="139" t="inlineStr">
         <is>
-          <t>All Categories</t>
+          <t>All Cats</t>
         </is>
       </c>
     </row>
@@ -31949,11 +31531,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
@@ -31961,14 +31543,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="141" t="inlineStr">
         <is>
-          <t>💰 TRANSACTION LEDGER</t>
+          <t>TRANSACTION LEDGER</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" ht="18" customHeight="1">
       <c r="A2" s="142" t="inlineStr">
         <is>
-          <t>Zero-Based Budget Manager  ·  All transactions tracked below</t>
+          <t>Zero-Based Budget Manager  ·  Record every dollar</t>
         </is>
       </c>
     </row>
@@ -31978,14 +31560,9 @@
           <t>TOTAL INCOME</t>
         </is>
       </c>
-      <c r="B3" s="143" t="inlineStr">
+      <c r="C3" s="143" t="inlineStr">
         <is>
           <t>TOTAL EXPENSES</t>
-        </is>
-      </c>
-      <c r="C3" s="143" t="inlineStr">
-        <is>
-          <t>TOTAL SAVINGS</t>
         </is>
       </c>
       <c r="E3" s="143" t="inlineStr">
@@ -31995,7 +31572,7 @@
       </c>
       <c r="G3" s="143" t="inlineStr">
         <is>
-          <t>FLAGGED TXs</t>
+          <t>FLAGGED</t>
         </is>
       </c>
     </row>
@@ -32004,2975 +31581,2971 @@
         <f>SUMIF(C8:C10000,"Income",E8:E10000)</f>
         <v/>
       </c>
-      <c r="B4" s="144">
+      <c r="C4" s="144">
         <f>SUMIF(C8:C10000,"Expense",E8:E10000)</f>
         <v/>
       </c>
-      <c r="C4" s="144">
-        <f>SUMIF(C8:C10000,"Savings",E8:E10000)</f>
-        <v/>
-      </c>
       <c r="E4" s="144">
-        <f>SUMIF(C8:C10000,"Income",E8:E10000)-SUMIF(C8:C10000,"Expense",E8:E10000)-SUMIF(C8:C10000,"Savings",E8:E10000)</f>
-        <v/>
-      </c>
-      <c r="G4" s="144">
+        <f>A4-C4</f>
+        <v/>
+      </c>
+      <c r="G4" s="145">
         <f>COUNTIF(G8:G10000,"Yes")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="8" customHeight="1"/>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="145" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="146" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B6" s="145" t="inlineStr">
+      <c r="B6" s="146" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C6" s="145" t="inlineStr">
+      <c r="C6" s="146" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D6" s="145" t="inlineStr">
+      <c r="D6" s="146" t="inlineStr">
         <is>
           <t>Details / Notes</t>
         </is>
       </c>
-      <c r="E6" s="145" t="inlineStr">
+      <c r="E6" s="146" t="inlineStr">
         <is>
           <t>Amount (USD)</t>
         </is>
       </c>
-      <c r="F6" s="145" t="inlineStr">
+      <c r="F6" s="146" t="inlineStr">
         <is>
           <t>Running Balance</t>
         </is>
       </c>
-      <c r="G6" s="145" t="inlineStr">
+      <c r="G6" s="146" t="inlineStr">
         <is>
           <t>Flagged?</t>
         </is>
       </c>
-      <c r="H6" s="145" t="inlineStr">
+      <c r="H6" s="146" t="inlineStr">
         <is>
           <t>Effective Date</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="146" t="n"/>
-      <c r="B8" s="147" t="n"/>
-      <c r="C8" s="147" t="n"/>
-      <c r="D8" s="147" t="n"/>
-      <c r="E8" s="148" t="n"/>
-      <c r="F8" s="148">
+      <c r="A8" s="147" t="n"/>
+      <c r="B8" s="148" t="n"/>
+      <c r="C8" s="148" t="n"/>
+      <c r="D8" s="148" t="n"/>
+      <c r="E8" s="149" t="n"/>
+      <c r="F8" s="150">
         <f>IFERROR(SUMIF($C$8:C8,"Income",$E$8:E8)-SUMIF($C$8:C8,"Expense",$E$8:E8)-SUMIF($C$8:C8,"Savings",$E$8:E8),"")</f>
         <v/>
       </c>
-      <c r="G8" s="149" t="n"/>
-      <c r="H8" s="146" t="n"/>
+      <c r="G8" s="151" t="n"/>
+      <c r="H8" s="147" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="150" t="n"/>
-      <c r="B9" s="151" t="n"/>
-      <c r="C9" s="151" t="n"/>
-      <c r="D9" s="151" t="n"/>
-      <c r="E9" s="152" t="n"/>
-      <c r="F9" s="152">
+      <c r="A9" s="152" t="n"/>
+      <c r="B9" s="153" t="n"/>
+      <c r="C9" s="153" t="n"/>
+      <c r="D9" s="153" t="n"/>
+      <c r="E9" s="154" t="n"/>
+      <c r="F9" s="155">
         <f>IFERROR(SUMIF($C$8:C9,"Income",$E$8:E9)-SUMIF($C$8:C9,"Expense",$E$8:E9)-SUMIF($C$8:C9,"Savings",$E$8:E9),"")</f>
         <v/>
       </c>
-      <c r="G9" s="153" t="n"/>
-      <c r="H9" s="150" t="n"/>
+      <c r="G9" s="156" t="n"/>
+      <c r="H9" s="152" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="146" t="n"/>
-      <c r="B10" s="147" t="n"/>
-      <c r="C10" s="147" t="n"/>
-      <c r="D10" s="147" t="n"/>
-      <c r="E10" s="148" t="n"/>
-      <c r="F10" s="148">
+      <c r="A10" s="147" t="n"/>
+      <c r="B10" s="148" t="n"/>
+      <c r="C10" s="148" t="n"/>
+      <c r="D10" s="148" t="n"/>
+      <c r="E10" s="149" t="n"/>
+      <c r="F10" s="150">
         <f>IFERROR(SUMIF($C$8:C10,"Income",$E$8:E10)-SUMIF($C$8:C10,"Expense",$E$8:E10)-SUMIF($C$8:C10,"Savings",$E$8:E10),"")</f>
         <v/>
       </c>
-      <c r="G10" s="149" t="n"/>
-      <c r="H10" s="146" t="n"/>
+      <c r="G10" s="151" t="n"/>
+      <c r="H10" s="147" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="150" t="n"/>
-      <c r="B11" s="151" t="n"/>
-      <c r="C11" s="151" t="n"/>
-      <c r="D11" s="151" t="n"/>
-      <c r="E11" s="152" t="n"/>
-      <c r="F11" s="152">
+      <c r="A11" s="152" t="n"/>
+      <c r="B11" s="153" t="n"/>
+      <c r="C11" s="153" t="n"/>
+      <c r="D11" s="153" t="n"/>
+      <c r="E11" s="154" t="n"/>
+      <c r="F11" s="155">
         <f>IFERROR(SUMIF($C$8:C11,"Income",$E$8:E11)-SUMIF($C$8:C11,"Expense",$E$8:E11)-SUMIF($C$8:C11,"Savings",$E$8:E11),"")</f>
         <v/>
       </c>
-      <c r="G11" s="153" t="n"/>
-      <c r="H11" s="150" t="n"/>
+      <c r="G11" s="156" t="n"/>
+      <c r="H11" s="152" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="146" t="n"/>
-      <c r="B12" s="147" t="n"/>
-      <c r="C12" s="147" t="n"/>
-      <c r="D12" s="147" t="n"/>
-      <c r="E12" s="148" t="n"/>
-      <c r="F12" s="148">
+      <c r="A12" s="147" t="n"/>
+      <c r="B12" s="148" t="n"/>
+      <c r="C12" s="148" t="n"/>
+      <c r="D12" s="148" t="n"/>
+      <c r="E12" s="149" t="n"/>
+      <c r="F12" s="150">
         <f>IFERROR(SUMIF($C$8:C12,"Income",$E$8:E12)-SUMIF($C$8:C12,"Expense",$E$8:E12)-SUMIF($C$8:C12,"Savings",$E$8:E12),"")</f>
         <v/>
       </c>
-      <c r="G12" s="149" t="n"/>
-      <c r="H12" s="146" t="n"/>
+      <c r="G12" s="151" t="n"/>
+      <c r="H12" s="147" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="150" t="n"/>
-      <c r="B13" s="151" t="n"/>
-      <c r="C13" s="151" t="n"/>
-      <c r="D13" s="151" t="n"/>
-      <c r="E13" s="152" t="n"/>
-      <c r="F13" s="152">
+      <c r="A13" s="152" t="n"/>
+      <c r="B13" s="153" t="n"/>
+      <c r="C13" s="153" t="n"/>
+      <c r="D13" s="153" t="n"/>
+      <c r="E13" s="154" t="n"/>
+      <c r="F13" s="155">
         <f>IFERROR(SUMIF($C$8:C13,"Income",$E$8:E13)-SUMIF($C$8:C13,"Expense",$E$8:E13)-SUMIF($C$8:C13,"Savings",$E$8:E13),"")</f>
         <v/>
       </c>
-      <c r="G13" s="153" t="n"/>
-      <c r="H13" s="150" t="n"/>
+      <c r="G13" s="156" t="n"/>
+      <c r="H13" s="152" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="146" t="n"/>
-      <c r="B14" s="147" t="n"/>
-      <c r="C14" s="147" t="n"/>
-      <c r="D14" s="147" t="n"/>
-      <c r="E14" s="148" t="n"/>
-      <c r="F14" s="148">
+      <c r="A14" s="147" t="n"/>
+      <c r="B14" s="148" t="n"/>
+      <c r="C14" s="148" t="n"/>
+      <c r="D14" s="148" t="n"/>
+      <c r="E14" s="149" t="n"/>
+      <c r="F14" s="150">
         <f>IFERROR(SUMIF($C$8:C14,"Income",$E$8:E14)-SUMIF($C$8:C14,"Expense",$E$8:E14)-SUMIF($C$8:C14,"Savings",$E$8:E14),"")</f>
         <v/>
       </c>
-      <c r="G14" s="149" t="n"/>
-      <c r="H14" s="146" t="n"/>
+      <c r="G14" s="151" t="n"/>
+      <c r="H14" s="147" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="150" t="n"/>
-      <c r="B15" s="151" t="n"/>
-      <c r="C15" s="151" t="n"/>
-      <c r="D15" s="151" t="n"/>
-      <c r="E15" s="152" t="n"/>
-      <c r="F15" s="152">
+      <c r="A15" s="152" t="n"/>
+      <c r="B15" s="153" t="n"/>
+      <c r="C15" s="153" t="n"/>
+      <c r="D15" s="153" t="n"/>
+      <c r="E15" s="154" t="n"/>
+      <c r="F15" s="155">
         <f>IFERROR(SUMIF($C$8:C15,"Income",$E$8:E15)-SUMIF($C$8:C15,"Expense",$E$8:E15)-SUMIF($C$8:C15,"Savings",$E$8:E15),"")</f>
         <v/>
       </c>
-      <c r="G15" s="153" t="n"/>
-      <c r="H15" s="150" t="n"/>
+      <c r="G15" s="156" t="n"/>
+      <c r="H15" s="152" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="146" t="n"/>
-      <c r="B16" s="147" t="n"/>
-      <c r="C16" s="147" t="n"/>
-      <c r="D16" s="147" t="n"/>
-      <c r="E16" s="148" t="n"/>
-      <c r="F16" s="148">
+      <c r="A16" s="147" t="n"/>
+      <c r="B16" s="148" t="n"/>
+      <c r="C16" s="148" t="n"/>
+      <c r="D16" s="148" t="n"/>
+      <c r="E16" s="149" t="n"/>
+      <c r="F16" s="150">
         <f>IFERROR(SUMIF($C$8:C16,"Income",$E$8:E16)-SUMIF($C$8:C16,"Expense",$E$8:E16)-SUMIF($C$8:C16,"Savings",$E$8:E16),"")</f>
         <v/>
       </c>
-      <c r="G16" s="149" t="n"/>
-      <c r="H16" s="146" t="n"/>
+      <c r="G16" s="151" t="n"/>
+      <c r="H16" s="147" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="150" t="n"/>
-      <c r="B17" s="151" t="n"/>
-      <c r="C17" s="151" t="n"/>
-      <c r="D17" s="151" t="n"/>
-      <c r="E17" s="152" t="n"/>
-      <c r="F17" s="152">
+      <c r="A17" s="152" t="n"/>
+      <c r="B17" s="153" t="n"/>
+      <c r="C17" s="153" t="n"/>
+      <c r="D17" s="153" t="n"/>
+      <c r="E17" s="154" t="n"/>
+      <c r="F17" s="155">
         <f>IFERROR(SUMIF($C$8:C17,"Income",$E$8:E17)-SUMIF($C$8:C17,"Expense",$E$8:E17)-SUMIF($C$8:C17,"Savings",$E$8:E17),"")</f>
         <v/>
       </c>
-      <c r="G17" s="153" t="n"/>
-      <c r="H17" s="150" t="n"/>
+      <c r="G17" s="156" t="n"/>
+      <c r="H17" s="152" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="146" t="n"/>
-      <c r="B18" s="147" t="n"/>
-      <c r="C18" s="147" t="n"/>
-      <c r="D18" s="147" t="n"/>
-      <c r="E18" s="148" t="n"/>
-      <c r="F18" s="148">
+      <c r="A18" s="147" t="n"/>
+      <c r="B18" s="148" t="n"/>
+      <c r="C18" s="148" t="n"/>
+      <c r="D18" s="148" t="n"/>
+      <c r="E18" s="149" t="n"/>
+      <c r="F18" s="150">
         <f>IFERROR(SUMIF($C$8:C18,"Income",$E$8:E18)-SUMIF($C$8:C18,"Expense",$E$8:E18)-SUMIF($C$8:C18,"Savings",$E$8:E18),"")</f>
         <v/>
       </c>
-      <c r="G18" s="149" t="n"/>
-      <c r="H18" s="146" t="n"/>
+      <c r="G18" s="151" t="n"/>
+      <c r="H18" s="147" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="150" t="n"/>
-      <c r="B19" s="151" t="n"/>
-      <c r="C19" s="151" t="n"/>
-      <c r="D19" s="151" t="n"/>
-      <c r="E19" s="152" t="n"/>
-      <c r="F19" s="152">
+      <c r="A19" s="152" t="n"/>
+      <c r="B19" s="153" t="n"/>
+      <c r="C19" s="153" t="n"/>
+      <c r="D19" s="153" t="n"/>
+      <c r="E19" s="154" t="n"/>
+      <c r="F19" s="155">
         <f>IFERROR(SUMIF($C$8:C19,"Income",$E$8:E19)-SUMIF($C$8:C19,"Expense",$E$8:E19)-SUMIF($C$8:C19,"Savings",$E$8:E19),"")</f>
         <v/>
       </c>
-      <c r="G19" s="153" t="n"/>
-      <c r="H19" s="150" t="n"/>
+      <c r="G19" s="156" t="n"/>
+      <c r="H19" s="152" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="146" t="n"/>
-      <c r="B20" s="147" t="n"/>
-      <c r="C20" s="147" t="n"/>
-      <c r="D20" s="147" t="n"/>
-      <c r="E20" s="148" t="n"/>
-      <c r="F20" s="148">
+      <c r="A20" s="147" t="n"/>
+      <c r="B20" s="148" t="n"/>
+      <c r="C20" s="148" t="n"/>
+      <c r="D20" s="148" t="n"/>
+      <c r="E20" s="149" t="n"/>
+      <c r="F20" s="150">
         <f>IFERROR(SUMIF($C$8:C20,"Income",$E$8:E20)-SUMIF($C$8:C20,"Expense",$E$8:E20)-SUMIF($C$8:C20,"Savings",$E$8:E20),"")</f>
         <v/>
       </c>
-      <c r="G20" s="149" t="n"/>
-      <c r="H20" s="146" t="n"/>
+      <c r="G20" s="151" t="n"/>
+      <c r="H20" s="147" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="150" t="n"/>
-      <c r="B21" s="151" t="n"/>
-      <c r="C21" s="151" t="n"/>
-      <c r="D21" s="151" t="n"/>
-      <c r="E21" s="152" t="n"/>
-      <c r="F21" s="152">
+      <c r="A21" s="152" t="n"/>
+      <c r="B21" s="153" t="n"/>
+      <c r="C21" s="153" t="n"/>
+      <c r="D21" s="153" t="n"/>
+      <c r="E21" s="154" t="n"/>
+      <c r="F21" s="155">
         <f>IFERROR(SUMIF($C$8:C21,"Income",$E$8:E21)-SUMIF($C$8:C21,"Expense",$E$8:E21)-SUMIF($C$8:C21,"Savings",$E$8:E21),"")</f>
         <v/>
       </c>
-      <c r="G21" s="153" t="n"/>
-      <c r="H21" s="150" t="n"/>
+      <c r="G21" s="156" t="n"/>
+      <c r="H21" s="152" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="146" t="n"/>
-      <c r="B22" s="147" t="n"/>
-      <c r="C22" s="147" t="n"/>
-      <c r="D22" s="147" t="n"/>
-      <c r="E22" s="148" t="n"/>
-      <c r="F22" s="148">
+      <c r="A22" s="147" t="n"/>
+      <c r="B22" s="148" t="n"/>
+      <c r="C22" s="148" t="n"/>
+      <c r="D22" s="148" t="n"/>
+      <c r="E22" s="149" t="n"/>
+      <c r="F22" s="150">
         <f>IFERROR(SUMIF($C$8:C22,"Income",$E$8:E22)-SUMIF($C$8:C22,"Expense",$E$8:E22)-SUMIF($C$8:C22,"Savings",$E$8:E22),"")</f>
         <v/>
       </c>
-      <c r="G22" s="149" t="n"/>
-      <c r="H22" s="146" t="n"/>
+      <c r="G22" s="151" t="n"/>
+      <c r="H22" s="147" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="150" t="n"/>
-      <c r="B23" s="151" t="n"/>
-      <c r="C23" s="151" t="n"/>
-      <c r="D23" s="151" t="n"/>
-      <c r="E23" s="152" t="n"/>
-      <c r="F23" s="152">
+      <c r="A23" s="152" t="n"/>
+      <c r="B23" s="153" t="n"/>
+      <c r="C23" s="153" t="n"/>
+      <c r="D23" s="153" t="n"/>
+      <c r="E23" s="154" t="n"/>
+      <c r="F23" s="155">
         <f>IFERROR(SUMIF($C$8:C23,"Income",$E$8:E23)-SUMIF($C$8:C23,"Expense",$E$8:E23)-SUMIF($C$8:C23,"Savings",$E$8:E23),"")</f>
         <v/>
       </c>
-      <c r="G23" s="153" t="n"/>
-      <c r="H23" s="150" t="n"/>
+      <c r="G23" s="156" t="n"/>
+      <c r="H23" s="152" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="146" t="n"/>
-      <c r="B24" s="147" t="n"/>
-      <c r="C24" s="147" t="n"/>
-      <c r="D24" s="147" t="n"/>
-      <c r="E24" s="148" t="n"/>
-      <c r="F24" s="148">
+      <c r="A24" s="147" t="n"/>
+      <c r="B24" s="148" t="n"/>
+      <c r="C24" s="148" t="n"/>
+      <c r="D24" s="148" t="n"/>
+      <c r="E24" s="149" t="n"/>
+      <c r="F24" s="150">
         <f>IFERROR(SUMIF($C$8:C24,"Income",$E$8:E24)-SUMIF($C$8:C24,"Expense",$E$8:E24)-SUMIF($C$8:C24,"Savings",$E$8:E24),"")</f>
         <v/>
       </c>
-      <c r="G24" s="149" t="n"/>
-      <c r="H24" s="146" t="n"/>
+      <c r="G24" s="151" t="n"/>
+      <c r="H24" s="147" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="150" t="n"/>
-      <c r="B25" s="151" t="n"/>
-      <c r="C25" s="151" t="n"/>
-      <c r="D25" s="151" t="n"/>
-      <c r="E25" s="152" t="n"/>
-      <c r="F25" s="152">
+      <c r="A25" s="152" t="n"/>
+      <c r="B25" s="153" t="n"/>
+      <c r="C25" s="153" t="n"/>
+      <c r="D25" s="153" t="n"/>
+      <c r="E25" s="154" t="n"/>
+      <c r="F25" s="155">
         <f>IFERROR(SUMIF($C$8:C25,"Income",$E$8:E25)-SUMIF($C$8:C25,"Expense",$E$8:E25)-SUMIF($C$8:C25,"Savings",$E$8:E25),"")</f>
         <v/>
       </c>
-      <c r="G25" s="153" t="n"/>
-      <c r="H25" s="150" t="n"/>
+      <c r="G25" s="156" t="n"/>
+      <c r="H25" s="152" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="146" t="n"/>
-      <c r="B26" s="147" t="n"/>
-      <c r="C26" s="147" t="n"/>
-      <c r="D26" s="147" t="n"/>
-      <c r="E26" s="148" t="n"/>
-      <c r="F26" s="148">
+      <c r="A26" s="147" t="n"/>
+      <c r="B26" s="148" t="n"/>
+      <c r="C26" s="148" t="n"/>
+      <c r="D26" s="148" t="n"/>
+      <c r="E26" s="149" t="n"/>
+      <c r="F26" s="150">
         <f>IFERROR(SUMIF($C$8:C26,"Income",$E$8:E26)-SUMIF($C$8:C26,"Expense",$E$8:E26)-SUMIF($C$8:C26,"Savings",$E$8:E26),"")</f>
         <v/>
       </c>
-      <c r="G26" s="149" t="n"/>
-      <c r="H26" s="146" t="n"/>
+      <c r="G26" s="151" t="n"/>
+      <c r="H26" s="147" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="150" t="n"/>
-      <c r="B27" s="151" t="n"/>
-      <c r="C27" s="151" t="n"/>
-      <c r="D27" s="151" t="n"/>
-      <c r="E27" s="152" t="n"/>
-      <c r="F27" s="152">
+      <c r="A27" s="152" t="n"/>
+      <c r="B27" s="153" t="n"/>
+      <c r="C27" s="153" t="n"/>
+      <c r="D27" s="153" t="n"/>
+      <c r="E27" s="154" t="n"/>
+      <c r="F27" s="155">
         <f>IFERROR(SUMIF($C$8:C27,"Income",$E$8:E27)-SUMIF($C$8:C27,"Expense",$E$8:E27)-SUMIF($C$8:C27,"Savings",$E$8:E27),"")</f>
         <v/>
       </c>
-      <c r="G27" s="153" t="n"/>
-      <c r="H27" s="150" t="n"/>
+      <c r="G27" s="156" t="n"/>
+      <c r="H27" s="152" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="146" t="n"/>
-      <c r="B28" s="147" t="n"/>
-      <c r="C28" s="147" t="n"/>
-      <c r="D28" s="147" t="n"/>
-      <c r="E28" s="148" t="n"/>
-      <c r="F28" s="148">
+      <c r="A28" s="147" t="n"/>
+      <c r="B28" s="148" t="n"/>
+      <c r="C28" s="148" t="n"/>
+      <c r="D28" s="148" t="n"/>
+      <c r="E28" s="149" t="n"/>
+      <c r="F28" s="150">
         <f>IFERROR(SUMIF($C$8:C28,"Income",$E$8:E28)-SUMIF($C$8:C28,"Expense",$E$8:E28)-SUMIF($C$8:C28,"Savings",$E$8:E28),"")</f>
         <v/>
       </c>
-      <c r="G28" s="149" t="n"/>
-      <c r="H28" s="146" t="n"/>
+      <c r="G28" s="151" t="n"/>
+      <c r="H28" s="147" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="150" t="n"/>
-      <c r="B29" s="151" t="n"/>
-      <c r="C29" s="151" t="n"/>
-      <c r="D29" s="151" t="n"/>
-      <c r="E29" s="152" t="n"/>
-      <c r="F29" s="152">
+      <c r="A29" s="152" t="n"/>
+      <c r="B29" s="153" t="n"/>
+      <c r="C29" s="153" t="n"/>
+      <c r="D29" s="153" t="n"/>
+      <c r="E29" s="154" t="n"/>
+      <c r="F29" s="155">
         <f>IFERROR(SUMIF($C$8:C29,"Income",$E$8:E29)-SUMIF($C$8:C29,"Expense",$E$8:E29)-SUMIF($C$8:C29,"Savings",$E$8:E29),"")</f>
         <v/>
       </c>
-      <c r="G29" s="153" t="n"/>
-      <c r="H29" s="150" t="n"/>
+      <c r="G29" s="156" t="n"/>
+      <c r="H29" s="152" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="146" t="n"/>
-      <c r="B30" s="147" t="n"/>
-      <c r="C30" s="147" t="n"/>
-      <c r="D30" s="147" t="n"/>
-      <c r="E30" s="148" t="n"/>
-      <c r="F30" s="148">
+      <c r="A30" s="147" t="n"/>
+      <c r="B30" s="148" t="n"/>
+      <c r="C30" s="148" t="n"/>
+      <c r="D30" s="148" t="n"/>
+      <c r="E30" s="149" t="n"/>
+      <c r="F30" s="150">
         <f>IFERROR(SUMIF($C$8:C30,"Income",$E$8:E30)-SUMIF($C$8:C30,"Expense",$E$8:E30)-SUMIF($C$8:C30,"Savings",$E$8:E30),"")</f>
         <v/>
       </c>
-      <c r="G30" s="149" t="n"/>
-      <c r="H30" s="146" t="n"/>
+      <c r="G30" s="151" t="n"/>
+      <c r="H30" s="147" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="150" t="n"/>
-      <c r="B31" s="151" t="n"/>
-      <c r="C31" s="151" t="n"/>
-      <c r="D31" s="151" t="n"/>
-      <c r="E31" s="152" t="n"/>
-      <c r="F31" s="152">
+      <c r="A31" s="152" t="n"/>
+      <c r="B31" s="153" t="n"/>
+      <c r="C31" s="153" t="n"/>
+      <c r="D31" s="153" t="n"/>
+      <c r="E31" s="154" t="n"/>
+      <c r="F31" s="155">
         <f>IFERROR(SUMIF($C$8:C31,"Income",$E$8:E31)-SUMIF($C$8:C31,"Expense",$E$8:E31)-SUMIF($C$8:C31,"Savings",$E$8:E31),"")</f>
         <v/>
       </c>
-      <c r="G31" s="153" t="n"/>
-      <c r="H31" s="150" t="n"/>
+      <c r="G31" s="156" t="n"/>
+      <c r="H31" s="152" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="146" t="n"/>
-      <c r="B32" s="147" t="n"/>
-      <c r="C32" s="147" t="n"/>
-      <c r="D32" s="147" t="n"/>
-      <c r="E32" s="148" t="n"/>
-      <c r="F32" s="148">
+      <c r="A32" s="147" t="n"/>
+      <c r="B32" s="148" t="n"/>
+      <c r="C32" s="148" t="n"/>
+      <c r="D32" s="148" t="n"/>
+      <c r="E32" s="149" t="n"/>
+      <c r="F32" s="150">
         <f>IFERROR(SUMIF($C$8:C32,"Income",$E$8:E32)-SUMIF($C$8:C32,"Expense",$E$8:E32)-SUMIF($C$8:C32,"Savings",$E$8:E32),"")</f>
         <v/>
       </c>
-      <c r="G32" s="149" t="n"/>
-      <c r="H32" s="146" t="n"/>
+      <c r="G32" s="151" t="n"/>
+      <c r="H32" s="147" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="150" t="n"/>
-      <c r="B33" s="151" t="n"/>
-      <c r="C33" s="151" t="n"/>
-      <c r="D33" s="151" t="n"/>
-      <c r="E33" s="152" t="n"/>
-      <c r="F33" s="152">
+      <c r="A33" s="152" t="n"/>
+      <c r="B33" s="153" t="n"/>
+      <c r="C33" s="153" t="n"/>
+      <c r="D33" s="153" t="n"/>
+      <c r="E33" s="154" t="n"/>
+      <c r="F33" s="155">
         <f>IFERROR(SUMIF($C$8:C33,"Income",$E$8:E33)-SUMIF($C$8:C33,"Expense",$E$8:E33)-SUMIF($C$8:C33,"Savings",$E$8:E33),"")</f>
         <v/>
       </c>
-      <c r="G33" s="153" t="n"/>
-      <c r="H33" s="150" t="n"/>
+      <c r="G33" s="156" t="n"/>
+      <c r="H33" s="152" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="146" t="n"/>
-      <c r="B34" s="147" t="n"/>
-      <c r="C34" s="147" t="n"/>
-      <c r="D34" s="147" t="n"/>
-      <c r="E34" s="148" t="n"/>
-      <c r="F34" s="148">
+      <c r="A34" s="147" t="n"/>
+      <c r="B34" s="148" t="n"/>
+      <c r="C34" s="148" t="n"/>
+      <c r="D34" s="148" t="n"/>
+      <c r="E34" s="149" t="n"/>
+      <c r="F34" s="150">
         <f>IFERROR(SUMIF($C$8:C34,"Income",$E$8:E34)-SUMIF($C$8:C34,"Expense",$E$8:E34)-SUMIF($C$8:C34,"Savings",$E$8:E34),"")</f>
         <v/>
       </c>
-      <c r="G34" s="149" t="n"/>
-      <c r="H34" s="146" t="n"/>
+      <c r="G34" s="151" t="n"/>
+      <c r="H34" s="147" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="150" t="n"/>
-      <c r="B35" s="151" t="n"/>
-      <c r="C35" s="151" t="n"/>
-      <c r="D35" s="151" t="n"/>
-      <c r="E35" s="152" t="n"/>
-      <c r="F35" s="152">
+      <c r="A35" s="152" t="n"/>
+      <c r="B35" s="153" t="n"/>
+      <c r="C35" s="153" t="n"/>
+      <c r="D35" s="153" t="n"/>
+      <c r="E35" s="154" t="n"/>
+      <c r="F35" s="155">
         <f>IFERROR(SUMIF($C$8:C35,"Income",$E$8:E35)-SUMIF($C$8:C35,"Expense",$E$8:E35)-SUMIF($C$8:C35,"Savings",$E$8:E35),"")</f>
         <v/>
       </c>
-      <c r="G35" s="153" t="n"/>
-      <c r="H35" s="150" t="n"/>
+      <c r="G35" s="156" t="n"/>
+      <c r="H35" s="152" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="146" t="n"/>
-      <c r="B36" s="147" t="n"/>
-      <c r="C36" s="147" t="n"/>
-      <c r="D36" s="147" t="n"/>
-      <c r="E36" s="148" t="n"/>
-      <c r="F36" s="148">
+      <c r="A36" s="147" t="n"/>
+      <c r="B36" s="148" t="n"/>
+      <c r="C36" s="148" t="n"/>
+      <c r="D36" s="148" t="n"/>
+      <c r="E36" s="149" t="n"/>
+      <c r="F36" s="150">
         <f>IFERROR(SUMIF($C$8:C36,"Income",$E$8:E36)-SUMIF($C$8:C36,"Expense",$E$8:E36)-SUMIF($C$8:C36,"Savings",$E$8:E36),"")</f>
         <v/>
       </c>
-      <c r="G36" s="149" t="n"/>
-      <c r="H36" s="146" t="n"/>
+      <c r="G36" s="151" t="n"/>
+      <c r="H36" s="147" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="150" t="n"/>
-      <c r="B37" s="151" t="n"/>
-      <c r="C37" s="151" t="n"/>
-      <c r="D37" s="151" t="n"/>
-      <c r="E37" s="152" t="n"/>
-      <c r="F37" s="152">
+      <c r="A37" s="152" t="n"/>
+      <c r="B37" s="153" t="n"/>
+      <c r="C37" s="153" t="n"/>
+      <c r="D37" s="153" t="n"/>
+      <c r="E37" s="154" t="n"/>
+      <c r="F37" s="155">
         <f>IFERROR(SUMIF($C$8:C37,"Income",$E$8:E37)-SUMIF($C$8:C37,"Expense",$E$8:E37)-SUMIF($C$8:C37,"Savings",$E$8:E37),"")</f>
         <v/>
       </c>
-      <c r="G37" s="153" t="n"/>
-      <c r="H37" s="150" t="n"/>
+      <c r="G37" s="156" t="n"/>
+      <c r="H37" s="152" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="146" t="n"/>
-      <c r="B38" s="147" t="n"/>
-      <c r="C38" s="147" t="n"/>
-      <c r="D38" s="147" t="n"/>
-      <c r="E38" s="148" t="n"/>
-      <c r="F38" s="148">
+      <c r="A38" s="147" t="n"/>
+      <c r="B38" s="148" t="n"/>
+      <c r="C38" s="148" t="n"/>
+      <c r="D38" s="148" t="n"/>
+      <c r="E38" s="149" t="n"/>
+      <c r="F38" s="150">
         <f>IFERROR(SUMIF($C$8:C38,"Income",$E$8:E38)-SUMIF($C$8:C38,"Expense",$E$8:E38)-SUMIF($C$8:C38,"Savings",$E$8:E38),"")</f>
         <v/>
       </c>
-      <c r="G38" s="149" t="n"/>
-      <c r="H38" s="146" t="n"/>
+      <c r="G38" s="151" t="n"/>
+      <c r="H38" s="147" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="150" t="n"/>
-      <c r="B39" s="151" t="n"/>
-      <c r="C39" s="151" t="n"/>
-      <c r="D39" s="151" t="n"/>
-      <c r="E39" s="152" t="n"/>
-      <c r="F39" s="152">
+      <c r="A39" s="152" t="n"/>
+      <c r="B39" s="153" t="n"/>
+      <c r="C39" s="153" t="n"/>
+      <c r="D39" s="153" t="n"/>
+      <c r="E39" s="154" t="n"/>
+      <c r="F39" s="155">
         <f>IFERROR(SUMIF($C$8:C39,"Income",$E$8:E39)-SUMIF($C$8:C39,"Expense",$E$8:E39)-SUMIF($C$8:C39,"Savings",$E$8:E39),"")</f>
         <v/>
       </c>
-      <c r="G39" s="153" t="n"/>
-      <c r="H39" s="150" t="n"/>
+      <c r="G39" s="156" t="n"/>
+      <c r="H39" s="152" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="146" t="n"/>
-      <c r="B40" s="147" t="n"/>
-      <c r="C40" s="147" t="n"/>
-      <c r="D40" s="147" t="n"/>
-      <c r="E40" s="148" t="n"/>
-      <c r="F40" s="148">
+      <c r="A40" s="147" t="n"/>
+      <c r="B40" s="148" t="n"/>
+      <c r="C40" s="148" t="n"/>
+      <c r="D40" s="148" t="n"/>
+      <c r="E40" s="149" t="n"/>
+      <c r="F40" s="150">
         <f>IFERROR(SUMIF($C$8:C40,"Income",$E$8:E40)-SUMIF($C$8:C40,"Expense",$E$8:E40)-SUMIF($C$8:C40,"Savings",$E$8:E40),"")</f>
         <v/>
       </c>
-      <c r="G40" s="149" t="n"/>
-      <c r="H40" s="146" t="n"/>
+      <c r="G40" s="151" t="n"/>
+      <c r="H40" s="147" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="150" t="n"/>
-      <c r="B41" s="151" t="n"/>
-      <c r="C41" s="151" t="n"/>
-      <c r="D41" s="151" t="n"/>
-      <c r="E41" s="152" t="n"/>
-      <c r="F41" s="152">
+      <c r="A41" s="152" t="n"/>
+      <c r="B41" s="153" t="n"/>
+      <c r="C41" s="153" t="n"/>
+      <c r="D41" s="153" t="n"/>
+      <c r="E41" s="154" t="n"/>
+      <c r="F41" s="155">
         <f>IFERROR(SUMIF($C$8:C41,"Income",$E$8:E41)-SUMIF($C$8:C41,"Expense",$E$8:E41)-SUMIF($C$8:C41,"Savings",$E$8:E41),"")</f>
         <v/>
       </c>
-      <c r="G41" s="153" t="n"/>
-      <c r="H41" s="150" t="n"/>
+      <c r="G41" s="156" t="n"/>
+      <c r="H41" s="152" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="146" t="n"/>
-      <c r="B42" s="147" t="n"/>
-      <c r="C42" s="147" t="n"/>
-      <c r="D42" s="147" t="n"/>
-      <c r="E42" s="148" t="n"/>
-      <c r="F42" s="148">
+      <c r="A42" s="147" t="n"/>
+      <c r="B42" s="148" t="n"/>
+      <c r="C42" s="148" t="n"/>
+      <c r="D42" s="148" t="n"/>
+      <c r="E42" s="149" t="n"/>
+      <c r="F42" s="150">
         <f>IFERROR(SUMIF($C$8:C42,"Income",$E$8:E42)-SUMIF($C$8:C42,"Expense",$E$8:E42)-SUMIF($C$8:C42,"Savings",$E$8:E42),"")</f>
         <v/>
       </c>
-      <c r="G42" s="149" t="n"/>
-      <c r="H42" s="146" t="n"/>
+      <c r="G42" s="151" t="n"/>
+      <c r="H42" s="147" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="150" t="n"/>
-      <c r="B43" s="151" t="n"/>
-      <c r="C43" s="151" t="n"/>
-      <c r="D43" s="151" t="n"/>
-      <c r="E43" s="152" t="n"/>
-      <c r="F43" s="152">
+      <c r="A43" s="152" t="n"/>
+      <c r="B43" s="153" t="n"/>
+      <c r="C43" s="153" t="n"/>
+      <c r="D43" s="153" t="n"/>
+      <c r="E43" s="154" t="n"/>
+      <c r="F43" s="155">
         <f>IFERROR(SUMIF($C$8:C43,"Income",$E$8:E43)-SUMIF($C$8:C43,"Expense",$E$8:E43)-SUMIF($C$8:C43,"Savings",$E$8:E43),"")</f>
         <v/>
       </c>
-      <c r="G43" s="153" t="n"/>
-      <c r="H43" s="150" t="n"/>
+      <c r="G43" s="156" t="n"/>
+      <c r="H43" s="152" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="146" t="n"/>
-      <c r="B44" s="147" t="n"/>
-      <c r="C44" s="147" t="n"/>
-      <c r="D44" s="147" t="n"/>
-      <c r="E44" s="148" t="n"/>
-      <c r="F44" s="148">
+      <c r="A44" s="147" t="n"/>
+      <c r="B44" s="148" t="n"/>
+      <c r="C44" s="148" t="n"/>
+      <c r="D44" s="148" t="n"/>
+      <c r="E44" s="149" t="n"/>
+      <c r="F44" s="150">
         <f>IFERROR(SUMIF($C$8:C44,"Income",$E$8:E44)-SUMIF($C$8:C44,"Expense",$E$8:E44)-SUMIF($C$8:C44,"Savings",$E$8:E44),"")</f>
         <v/>
       </c>
-      <c r="G44" s="149" t="n"/>
-      <c r="H44" s="146" t="n"/>
+      <c r="G44" s="151" t="n"/>
+      <c r="H44" s="147" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="150" t="n"/>
-      <c r="B45" s="151" t="n"/>
-      <c r="C45" s="151" t="n"/>
-      <c r="D45" s="151" t="n"/>
-      <c r="E45" s="152" t="n"/>
-      <c r="F45" s="152">
+      <c r="A45" s="152" t="n"/>
+      <c r="B45" s="153" t="n"/>
+      <c r="C45" s="153" t="n"/>
+      <c r="D45" s="153" t="n"/>
+      <c r="E45" s="154" t="n"/>
+      <c r="F45" s="155">
         <f>IFERROR(SUMIF($C$8:C45,"Income",$E$8:E45)-SUMIF($C$8:C45,"Expense",$E$8:E45)-SUMIF($C$8:C45,"Savings",$E$8:E45),"")</f>
         <v/>
       </c>
-      <c r="G45" s="153" t="n"/>
-      <c r="H45" s="150" t="n"/>
+      <c r="G45" s="156" t="n"/>
+      <c r="H45" s="152" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="146" t="n"/>
-      <c r="B46" s="147" t="n"/>
-      <c r="C46" s="147" t="n"/>
-      <c r="D46" s="147" t="n"/>
-      <c r="E46" s="148" t="n"/>
-      <c r="F46" s="148">
+      <c r="A46" s="147" t="n"/>
+      <c r="B46" s="148" t="n"/>
+      <c r="C46" s="148" t="n"/>
+      <c r="D46" s="148" t="n"/>
+      <c r="E46" s="149" t="n"/>
+      <c r="F46" s="150">
         <f>IFERROR(SUMIF($C$8:C46,"Income",$E$8:E46)-SUMIF($C$8:C46,"Expense",$E$8:E46)-SUMIF($C$8:C46,"Savings",$E$8:E46),"")</f>
         <v/>
       </c>
-      <c r="G46" s="149" t="n"/>
-      <c r="H46" s="146" t="n"/>
+      <c r="G46" s="151" t="n"/>
+      <c r="H46" s="147" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="150" t="n"/>
-      <c r="B47" s="151" t="n"/>
-      <c r="C47" s="151" t="n"/>
-      <c r="D47" s="151" t="n"/>
-      <c r="E47" s="152" t="n"/>
-      <c r="F47" s="152">
+      <c r="A47" s="152" t="n"/>
+      <c r="B47" s="153" t="n"/>
+      <c r="C47" s="153" t="n"/>
+      <c r="D47" s="153" t="n"/>
+      <c r="E47" s="154" t="n"/>
+      <c r="F47" s="155">
         <f>IFERROR(SUMIF($C$8:C47,"Income",$E$8:E47)-SUMIF($C$8:C47,"Expense",$E$8:E47)-SUMIF($C$8:C47,"Savings",$E$8:E47),"")</f>
         <v/>
       </c>
-      <c r="G47" s="153" t="n"/>
-      <c r="H47" s="150" t="n"/>
+      <c r="G47" s="156" t="n"/>
+      <c r="H47" s="152" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="146" t="n"/>
-      <c r="B48" s="147" t="n"/>
-      <c r="C48" s="147" t="n"/>
-      <c r="D48" s="147" t="n"/>
-      <c r="E48" s="148" t="n"/>
-      <c r="F48" s="148">
+      <c r="A48" s="147" t="n"/>
+      <c r="B48" s="148" t="n"/>
+      <c r="C48" s="148" t="n"/>
+      <c r="D48" s="148" t="n"/>
+      <c r="E48" s="149" t="n"/>
+      <c r="F48" s="150">
         <f>IFERROR(SUMIF($C$8:C48,"Income",$E$8:E48)-SUMIF($C$8:C48,"Expense",$E$8:E48)-SUMIF($C$8:C48,"Savings",$E$8:E48),"")</f>
         <v/>
       </c>
-      <c r="G48" s="149" t="n"/>
-      <c r="H48" s="146" t="n"/>
+      <c r="G48" s="151" t="n"/>
+      <c r="H48" s="147" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="150" t="n"/>
-      <c r="B49" s="151" t="n"/>
-      <c r="C49" s="151" t="n"/>
-      <c r="D49" s="151" t="n"/>
-      <c r="E49" s="152" t="n"/>
-      <c r="F49" s="152">
+      <c r="A49" s="152" t="n"/>
+      <c r="B49" s="153" t="n"/>
+      <c r="C49" s="153" t="n"/>
+      <c r="D49" s="153" t="n"/>
+      <c r="E49" s="154" t="n"/>
+      <c r="F49" s="155">
         <f>IFERROR(SUMIF($C$8:C49,"Income",$E$8:E49)-SUMIF($C$8:C49,"Expense",$E$8:E49)-SUMIF($C$8:C49,"Savings",$E$8:E49),"")</f>
         <v/>
       </c>
-      <c r="G49" s="153" t="n"/>
-      <c r="H49" s="150" t="n"/>
+      <c r="G49" s="156" t="n"/>
+      <c r="H49" s="152" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="146" t="n"/>
-      <c r="B50" s="147" t="n"/>
-      <c r="C50" s="147" t="n"/>
-      <c r="D50" s="147" t="n"/>
-      <c r="E50" s="148" t="n"/>
-      <c r="F50" s="148">
+      <c r="A50" s="147" t="n"/>
+      <c r="B50" s="148" t="n"/>
+      <c r="C50" s="148" t="n"/>
+      <c r="D50" s="148" t="n"/>
+      <c r="E50" s="149" t="n"/>
+      <c r="F50" s="150">
         <f>IFERROR(SUMIF($C$8:C50,"Income",$E$8:E50)-SUMIF($C$8:C50,"Expense",$E$8:E50)-SUMIF($C$8:C50,"Savings",$E$8:E50),"")</f>
         <v/>
       </c>
-      <c r="G50" s="149" t="n"/>
-      <c r="H50" s="146" t="n"/>
+      <c r="G50" s="151" t="n"/>
+      <c r="H50" s="147" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="150" t="n"/>
-      <c r="B51" s="151" t="n"/>
-      <c r="C51" s="151" t="n"/>
-      <c r="D51" s="151" t="n"/>
-      <c r="E51" s="152" t="n"/>
-      <c r="F51" s="152">
+      <c r="A51" s="152" t="n"/>
+      <c r="B51" s="153" t="n"/>
+      <c r="C51" s="153" t="n"/>
+      <c r="D51" s="153" t="n"/>
+      <c r="E51" s="154" t="n"/>
+      <c r="F51" s="155">
         <f>IFERROR(SUMIF($C$8:C51,"Income",$E$8:E51)-SUMIF($C$8:C51,"Expense",$E$8:E51)-SUMIF($C$8:C51,"Savings",$E$8:E51),"")</f>
         <v/>
       </c>
-      <c r="G51" s="153" t="n"/>
-      <c r="H51" s="150" t="n"/>
+      <c r="G51" s="156" t="n"/>
+      <c r="H51" s="152" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="146" t="n"/>
-      <c r="B52" s="147" t="n"/>
-      <c r="C52" s="147" t="n"/>
-      <c r="D52" s="147" t="n"/>
-      <c r="E52" s="148" t="n"/>
-      <c r="F52" s="148">
+      <c r="A52" s="147" t="n"/>
+      <c r="B52" s="148" t="n"/>
+      <c r="C52" s="148" t="n"/>
+      <c r="D52" s="148" t="n"/>
+      <c r="E52" s="149" t="n"/>
+      <c r="F52" s="150">
         <f>IFERROR(SUMIF($C$8:C52,"Income",$E$8:E52)-SUMIF($C$8:C52,"Expense",$E$8:E52)-SUMIF($C$8:C52,"Savings",$E$8:E52),"")</f>
         <v/>
       </c>
-      <c r="G52" s="149" t="n"/>
-      <c r="H52" s="146" t="n"/>
+      <c r="G52" s="151" t="n"/>
+      <c r="H52" s="147" t="n"/>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="150" t="n"/>
-      <c r="B53" s="151" t="n"/>
-      <c r="C53" s="151" t="n"/>
-      <c r="D53" s="151" t="n"/>
-      <c r="E53" s="152" t="n"/>
-      <c r="F53" s="152">
+      <c r="A53" s="152" t="n"/>
+      <c r="B53" s="153" t="n"/>
+      <c r="C53" s="153" t="n"/>
+      <c r="D53" s="153" t="n"/>
+      <c r="E53" s="154" t="n"/>
+      <c r="F53" s="155">
         <f>IFERROR(SUMIF($C$8:C53,"Income",$E$8:E53)-SUMIF($C$8:C53,"Expense",$E$8:E53)-SUMIF($C$8:C53,"Savings",$E$8:E53),"")</f>
         <v/>
       </c>
-      <c r="G53" s="153" t="n"/>
-      <c r="H53" s="150" t="n"/>
+      <c r="G53" s="156" t="n"/>
+      <c r="H53" s="152" t="n"/>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="146" t="n"/>
-      <c r="B54" s="147" t="n"/>
-      <c r="C54" s="147" t="n"/>
-      <c r="D54" s="147" t="n"/>
-      <c r="E54" s="148" t="n"/>
-      <c r="F54" s="148">
+      <c r="A54" s="147" t="n"/>
+      <c r="B54" s="148" t="n"/>
+      <c r="C54" s="148" t="n"/>
+      <c r="D54" s="148" t="n"/>
+      <c r="E54" s="149" t="n"/>
+      <c r="F54" s="150">
         <f>IFERROR(SUMIF($C$8:C54,"Income",$E$8:E54)-SUMIF($C$8:C54,"Expense",$E$8:E54)-SUMIF($C$8:C54,"Savings",$E$8:E54),"")</f>
         <v/>
       </c>
-      <c r="G54" s="149" t="n"/>
-      <c r="H54" s="146" t="n"/>
+      <c r="G54" s="151" t="n"/>
+      <c r="H54" s="147" t="n"/>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="150" t="n"/>
-      <c r="B55" s="151" t="n"/>
-      <c r="C55" s="151" t="n"/>
-      <c r="D55" s="151" t="n"/>
-      <c r="E55" s="152" t="n"/>
-      <c r="F55" s="152">
+      <c r="A55" s="152" t="n"/>
+      <c r="B55" s="153" t="n"/>
+      <c r="C55" s="153" t="n"/>
+      <c r="D55" s="153" t="n"/>
+      <c r="E55" s="154" t="n"/>
+      <c r="F55" s="155">
         <f>IFERROR(SUMIF($C$8:C55,"Income",$E$8:E55)-SUMIF($C$8:C55,"Expense",$E$8:E55)-SUMIF($C$8:C55,"Savings",$E$8:E55),"")</f>
         <v/>
       </c>
-      <c r="G55" s="153" t="n"/>
-      <c r="H55" s="150" t="n"/>
+      <c r="G55" s="156" t="n"/>
+      <c r="H55" s="152" t="n"/>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="146" t="n"/>
-      <c r="B56" s="147" t="n"/>
-      <c r="C56" s="147" t="n"/>
-      <c r="D56" s="147" t="n"/>
-      <c r="E56" s="148" t="n"/>
-      <c r="F56" s="148">
+      <c r="A56" s="147" t="n"/>
+      <c r="B56" s="148" t="n"/>
+      <c r="C56" s="148" t="n"/>
+      <c r="D56" s="148" t="n"/>
+      <c r="E56" s="149" t="n"/>
+      <c r="F56" s="150">
         <f>IFERROR(SUMIF($C$8:C56,"Income",$E$8:E56)-SUMIF($C$8:C56,"Expense",$E$8:E56)-SUMIF($C$8:C56,"Savings",$E$8:E56),"")</f>
         <v/>
       </c>
-      <c r="G56" s="149" t="n"/>
-      <c r="H56" s="146" t="n"/>
+      <c r="G56" s="151" t="n"/>
+      <c r="H56" s="147" t="n"/>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="150" t="n"/>
-      <c r="B57" s="151" t="n"/>
-      <c r="C57" s="151" t="n"/>
-      <c r="D57" s="151" t="n"/>
-      <c r="E57" s="152" t="n"/>
-      <c r="F57" s="152">
+      <c r="A57" s="152" t="n"/>
+      <c r="B57" s="153" t="n"/>
+      <c r="C57" s="153" t="n"/>
+      <c r="D57" s="153" t="n"/>
+      <c r="E57" s="154" t="n"/>
+      <c r="F57" s="155">
         <f>IFERROR(SUMIF($C$8:C57,"Income",$E$8:E57)-SUMIF($C$8:C57,"Expense",$E$8:E57)-SUMIF($C$8:C57,"Savings",$E$8:E57),"")</f>
         <v/>
       </c>
-      <c r="G57" s="153" t="n"/>
-      <c r="H57" s="150" t="n"/>
+      <c r="G57" s="156" t="n"/>
+      <c r="H57" s="152" t="n"/>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="146" t="n"/>
-      <c r="B58" s="147" t="n"/>
-      <c r="C58" s="147" t="n"/>
-      <c r="D58" s="147" t="n"/>
-      <c r="E58" s="148" t="n"/>
-      <c r="F58" s="148">
+      <c r="A58" s="147" t="n"/>
+      <c r="B58" s="148" t="n"/>
+      <c r="C58" s="148" t="n"/>
+      <c r="D58" s="148" t="n"/>
+      <c r="E58" s="149" t="n"/>
+      <c r="F58" s="150">
         <f>IFERROR(SUMIF($C$8:C58,"Income",$E$8:E58)-SUMIF($C$8:C58,"Expense",$E$8:E58)-SUMIF($C$8:C58,"Savings",$E$8:E58),"")</f>
         <v/>
       </c>
-      <c r="G58" s="149" t="n"/>
-      <c r="H58" s="146" t="n"/>
+      <c r="G58" s="151" t="n"/>
+      <c r="H58" s="147" t="n"/>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="150" t="n"/>
-      <c r="B59" s="151" t="n"/>
-      <c r="C59" s="151" t="n"/>
-      <c r="D59" s="151" t="n"/>
-      <c r="E59" s="152" t="n"/>
-      <c r="F59" s="152">
+      <c r="A59" s="152" t="n"/>
+      <c r="B59" s="153" t="n"/>
+      <c r="C59" s="153" t="n"/>
+      <c r="D59" s="153" t="n"/>
+      <c r="E59" s="154" t="n"/>
+      <c r="F59" s="155">
         <f>IFERROR(SUMIF($C$8:C59,"Income",$E$8:E59)-SUMIF($C$8:C59,"Expense",$E$8:E59)-SUMIF($C$8:C59,"Savings",$E$8:E59),"")</f>
         <v/>
       </c>
-      <c r="G59" s="153" t="n"/>
-      <c r="H59" s="150" t="n"/>
+      <c r="G59" s="156" t="n"/>
+      <c r="H59" s="152" t="n"/>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="146" t="n"/>
-      <c r="B60" s="147" t="n"/>
-      <c r="C60" s="147" t="n"/>
-      <c r="D60" s="147" t="n"/>
-      <c r="E60" s="148" t="n"/>
-      <c r="F60" s="148">
+      <c r="A60" s="147" t="n"/>
+      <c r="B60" s="148" t="n"/>
+      <c r="C60" s="148" t="n"/>
+      <c r="D60" s="148" t="n"/>
+      <c r="E60" s="149" t="n"/>
+      <c r="F60" s="150">
         <f>IFERROR(SUMIF($C$8:C60,"Income",$E$8:E60)-SUMIF($C$8:C60,"Expense",$E$8:E60)-SUMIF($C$8:C60,"Savings",$E$8:E60),"")</f>
         <v/>
       </c>
-      <c r="G60" s="149" t="n"/>
-      <c r="H60" s="146" t="n"/>
+      <c r="G60" s="151" t="n"/>
+      <c r="H60" s="147" t="n"/>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="150" t="n"/>
-      <c r="B61" s="151" t="n"/>
-      <c r="C61" s="151" t="n"/>
-      <c r="D61" s="151" t="n"/>
-      <c r="E61" s="152" t="n"/>
-      <c r="F61" s="152">
+      <c r="A61" s="152" t="n"/>
+      <c r="B61" s="153" t="n"/>
+      <c r="C61" s="153" t="n"/>
+      <c r="D61" s="153" t="n"/>
+      <c r="E61" s="154" t="n"/>
+      <c r="F61" s="155">
         <f>IFERROR(SUMIF($C$8:C61,"Income",$E$8:E61)-SUMIF($C$8:C61,"Expense",$E$8:E61)-SUMIF($C$8:C61,"Savings",$E$8:E61),"")</f>
         <v/>
       </c>
-      <c r="G61" s="153" t="n"/>
-      <c r="H61" s="150" t="n"/>
+      <c r="G61" s="156" t="n"/>
+      <c r="H61" s="152" t="n"/>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="146" t="n"/>
-      <c r="B62" s="147" t="n"/>
-      <c r="C62" s="147" t="n"/>
-      <c r="D62" s="147" t="n"/>
-      <c r="E62" s="148" t="n"/>
-      <c r="F62" s="148">
+      <c r="A62" s="147" t="n"/>
+      <c r="B62" s="148" t="n"/>
+      <c r="C62" s="148" t="n"/>
+      <c r="D62" s="148" t="n"/>
+      <c r="E62" s="149" t="n"/>
+      <c r="F62" s="150">
         <f>IFERROR(SUMIF($C$8:C62,"Income",$E$8:E62)-SUMIF($C$8:C62,"Expense",$E$8:E62)-SUMIF($C$8:C62,"Savings",$E$8:E62),"")</f>
         <v/>
       </c>
-      <c r="G62" s="149" t="n"/>
-      <c r="H62" s="146" t="n"/>
+      <c r="G62" s="151" t="n"/>
+      <c r="H62" s="147" t="n"/>
     </row>
     <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="150" t="n"/>
-      <c r="B63" s="151" t="n"/>
-      <c r="C63" s="151" t="n"/>
-      <c r="D63" s="151" t="n"/>
-      <c r="E63" s="152" t="n"/>
-      <c r="F63" s="152">
+      <c r="A63" s="152" t="n"/>
+      <c r="B63" s="153" t="n"/>
+      <c r="C63" s="153" t="n"/>
+      <c r="D63" s="153" t="n"/>
+      <c r="E63" s="154" t="n"/>
+      <c r="F63" s="155">
         <f>IFERROR(SUMIF($C$8:C63,"Income",$E$8:E63)-SUMIF($C$8:C63,"Expense",$E$8:E63)-SUMIF($C$8:C63,"Savings",$E$8:E63),"")</f>
         <v/>
       </c>
-      <c r="G63" s="153" t="n"/>
-      <c r="H63" s="150" t="n"/>
+      <c r="G63" s="156" t="n"/>
+      <c r="H63" s="152" t="n"/>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="146" t="n"/>
-      <c r="B64" s="147" t="n"/>
-      <c r="C64" s="147" t="n"/>
-      <c r="D64" s="147" t="n"/>
-      <c r="E64" s="148" t="n"/>
-      <c r="F64" s="148">
+      <c r="A64" s="147" t="n"/>
+      <c r="B64" s="148" t="n"/>
+      <c r="C64" s="148" t="n"/>
+      <c r="D64" s="148" t="n"/>
+      <c r="E64" s="149" t="n"/>
+      <c r="F64" s="150">
         <f>IFERROR(SUMIF($C$8:C64,"Income",$E$8:E64)-SUMIF($C$8:C64,"Expense",$E$8:E64)-SUMIF($C$8:C64,"Savings",$E$8:E64),"")</f>
         <v/>
       </c>
-      <c r="G64" s="149" t="n"/>
-      <c r="H64" s="146" t="n"/>
+      <c r="G64" s="151" t="n"/>
+      <c r="H64" s="147" t="n"/>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="150" t="n"/>
-      <c r="B65" s="151" t="n"/>
-      <c r="C65" s="151" t="n"/>
-      <c r="D65" s="151" t="n"/>
-      <c r="E65" s="152" t="n"/>
-      <c r="F65" s="152">
+      <c r="A65" s="152" t="n"/>
+      <c r="B65" s="153" t="n"/>
+      <c r="C65" s="153" t="n"/>
+      <c r="D65" s="153" t="n"/>
+      <c r="E65" s="154" t="n"/>
+      <c r="F65" s="155">
         <f>IFERROR(SUMIF($C$8:C65,"Income",$E$8:E65)-SUMIF($C$8:C65,"Expense",$E$8:E65)-SUMIF($C$8:C65,"Savings",$E$8:E65),"")</f>
         <v/>
       </c>
-      <c r="G65" s="153" t="n"/>
-      <c r="H65" s="150" t="n"/>
+      <c r="G65" s="156" t="n"/>
+      <c r="H65" s="152" t="n"/>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="146" t="n"/>
-      <c r="B66" s="147" t="n"/>
-      <c r="C66" s="147" t="n"/>
-      <c r="D66" s="147" t="n"/>
-      <c r="E66" s="148" t="n"/>
-      <c r="F66" s="148">
+      <c r="A66" s="147" t="n"/>
+      <c r="B66" s="148" t="n"/>
+      <c r="C66" s="148" t="n"/>
+      <c r="D66" s="148" t="n"/>
+      <c r="E66" s="149" t="n"/>
+      <c r="F66" s="150">
         <f>IFERROR(SUMIF($C$8:C66,"Income",$E$8:E66)-SUMIF($C$8:C66,"Expense",$E$8:E66)-SUMIF($C$8:C66,"Savings",$E$8:E66),"")</f>
         <v/>
       </c>
-      <c r="G66" s="149" t="n"/>
-      <c r="H66" s="146" t="n"/>
+      <c r="G66" s="151" t="n"/>
+      <c r="H66" s="147" t="n"/>
     </row>
     <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="150" t="n"/>
-      <c r="B67" s="151" t="n"/>
-      <c r="C67" s="151" t="n"/>
-      <c r="D67" s="151" t="n"/>
-      <c r="E67" s="152" t="n"/>
-      <c r="F67" s="152">
+      <c r="A67" s="152" t="n"/>
+      <c r="B67" s="153" t="n"/>
+      <c r="C67" s="153" t="n"/>
+      <c r="D67" s="153" t="n"/>
+      <c r="E67" s="154" t="n"/>
+      <c r="F67" s="155">
         <f>IFERROR(SUMIF($C$8:C67,"Income",$E$8:E67)-SUMIF($C$8:C67,"Expense",$E$8:E67)-SUMIF($C$8:C67,"Savings",$E$8:E67),"")</f>
         <v/>
       </c>
-      <c r="G67" s="153" t="n"/>
-      <c r="H67" s="150" t="n"/>
+      <c r="G67" s="156" t="n"/>
+      <c r="H67" s="152" t="n"/>
     </row>
     <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="146" t="n"/>
-      <c r="B68" s="147" t="n"/>
-      <c r="C68" s="147" t="n"/>
-      <c r="D68" s="147" t="n"/>
-      <c r="E68" s="148" t="n"/>
-      <c r="F68" s="148">
+      <c r="A68" s="147" t="n"/>
+      <c r="B68" s="148" t="n"/>
+      <c r="C68" s="148" t="n"/>
+      <c r="D68" s="148" t="n"/>
+      <c r="E68" s="149" t="n"/>
+      <c r="F68" s="150">
         <f>IFERROR(SUMIF($C$8:C68,"Income",$E$8:E68)-SUMIF($C$8:C68,"Expense",$E$8:E68)-SUMIF($C$8:C68,"Savings",$E$8:E68),"")</f>
         <v/>
       </c>
-      <c r="G68" s="149" t="n"/>
-      <c r="H68" s="146" t="n"/>
+      <c r="G68" s="151" t="n"/>
+      <c r="H68" s="147" t="n"/>
     </row>
     <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="150" t="n"/>
-      <c r="B69" s="151" t="n"/>
-      <c r="C69" s="151" t="n"/>
-      <c r="D69" s="151" t="n"/>
-      <c r="E69" s="152" t="n"/>
-      <c r="F69" s="152">
+      <c r="A69" s="152" t="n"/>
+      <c r="B69" s="153" t="n"/>
+      <c r="C69" s="153" t="n"/>
+      <c r="D69" s="153" t="n"/>
+      <c r="E69" s="154" t="n"/>
+      <c r="F69" s="155">
         <f>IFERROR(SUMIF($C$8:C69,"Income",$E$8:E69)-SUMIF($C$8:C69,"Expense",$E$8:E69)-SUMIF($C$8:C69,"Savings",$E$8:E69),"")</f>
         <v/>
       </c>
-      <c r="G69" s="153" t="n"/>
-      <c r="H69" s="150" t="n"/>
+      <c r="G69" s="156" t="n"/>
+      <c r="H69" s="152" t="n"/>
     </row>
     <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="146" t="n"/>
-      <c r="B70" s="147" t="n"/>
-      <c r="C70" s="147" t="n"/>
-      <c r="D70" s="147" t="n"/>
-      <c r="E70" s="148" t="n"/>
-      <c r="F70" s="148">
+      <c r="A70" s="147" t="n"/>
+      <c r="B70" s="148" t="n"/>
+      <c r="C70" s="148" t="n"/>
+      <c r="D70" s="148" t="n"/>
+      <c r="E70" s="149" t="n"/>
+      <c r="F70" s="150">
         <f>IFERROR(SUMIF($C$8:C70,"Income",$E$8:E70)-SUMIF($C$8:C70,"Expense",$E$8:E70)-SUMIF($C$8:C70,"Savings",$E$8:E70),"")</f>
         <v/>
       </c>
-      <c r="G70" s="149" t="n"/>
-      <c r="H70" s="146" t="n"/>
+      <c r="G70" s="151" t="n"/>
+      <c r="H70" s="147" t="n"/>
     </row>
     <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="150" t="n"/>
-      <c r="B71" s="151" t="n"/>
-      <c r="C71" s="151" t="n"/>
-      <c r="D71" s="151" t="n"/>
-      <c r="E71" s="152" t="n"/>
-      <c r="F71" s="152">
+      <c r="A71" s="152" t="n"/>
+      <c r="B71" s="153" t="n"/>
+      <c r="C71" s="153" t="n"/>
+      <c r="D71" s="153" t="n"/>
+      <c r="E71" s="154" t="n"/>
+      <c r="F71" s="155">
         <f>IFERROR(SUMIF($C$8:C71,"Income",$E$8:E71)-SUMIF($C$8:C71,"Expense",$E$8:E71)-SUMIF($C$8:C71,"Savings",$E$8:E71),"")</f>
         <v/>
       </c>
-      <c r="G71" s="153" t="n"/>
-      <c r="H71" s="150" t="n"/>
+      <c r="G71" s="156" t="n"/>
+      <c r="H71" s="152" t="n"/>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="146" t="n"/>
-      <c r="B72" s="147" t="n"/>
-      <c r="C72" s="147" t="n"/>
-      <c r="D72" s="147" t="n"/>
-      <c r="E72" s="148" t="n"/>
-      <c r="F72" s="148">
+      <c r="A72" s="147" t="n"/>
+      <c r="B72" s="148" t="n"/>
+      <c r="C72" s="148" t="n"/>
+      <c r="D72" s="148" t="n"/>
+      <c r="E72" s="149" t="n"/>
+      <c r="F72" s="150">
         <f>IFERROR(SUMIF($C$8:C72,"Income",$E$8:E72)-SUMIF($C$8:C72,"Expense",$E$8:E72)-SUMIF($C$8:C72,"Savings",$E$8:E72),"")</f>
         <v/>
       </c>
-      <c r="G72" s="149" t="n"/>
-      <c r="H72" s="146" t="n"/>
+      <c r="G72" s="151" t="n"/>
+      <c r="H72" s="147" t="n"/>
     </row>
     <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="150" t="n"/>
-      <c r="B73" s="151" t="n"/>
-      <c r="C73" s="151" t="n"/>
-      <c r="D73" s="151" t="n"/>
-      <c r="E73" s="152" t="n"/>
-      <c r="F73" s="152">
+      <c r="A73" s="152" t="n"/>
+      <c r="B73" s="153" t="n"/>
+      <c r="C73" s="153" t="n"/>
+      <c r="D73" s="153" t="n"/>
+      <c r="E73" s="154" t="n"/>
+      <c r="F73" s="155">
         <f>IFERROR(SUMIF($C$8:C73,"Income",$E$8:E73)-SUMIF($C$8:C73,"Expense",$E$8:E73)-SUMIF($C$8:C73,"Savings",$E$8:E73),"")</f>
         <v/>
       </c>
-      <c r="G73" s="153" t="n"/>
-      <c r="H73" s="150" t="n"/>
+      <c r="G73" s="156" t="n"/>
+      <c r="H73" s="152" t="n"/>
     </row>
     <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="146" t="n"/>
-      <c r="B74" s="147" t="n"/>
-      <c r="C74" s="147" t="n"/>
-      <c r="D74" s="147" t="n"/>
-      <c r="E74" s="148" t="n"/>
-      <c r="F74" s="148">
+      <c r="A74" s="147" t="n"/>
+      <c r="B74" s="148" t="n"/>
+      <c r="C74" s="148" t="n"/>
+      <c r="D74" s="148" t="n"/>
+      <c r="E74" s="149" t="n"/>
+      <c r="F74" s="150">
         <f>IFERROR(SUMIF($C$8:C74,"Income",$E$8:E74)-SUMIF($C$8:C74,"Expense",$E$8:E74)-SUMIF($C$8:C74,"Savings",$E$8:E74),"")</f>
         <v/>
       </c>
-      <c r="G74" s="149" t="n"/>
-      <c r="H74" s="146" t="n"/>
+      <c r="G74" s="151" t="n"/>
+      <c r="H74" s="147" t="n"/>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="150" t="n"/>
-      <c r="B75" s="151" t="n"/>
-      <c r="C75" s="151" t="n"/>
-      <c r="D75" s="151" t="n"/>
-      <c r="E75" s="152" t="n"/>
-      <c r="F75" s="152">
+      <c r="A75" s="152" t="n"/>
+      <c r="B75" s="153" t="n"/>
+      <c r="C75" s="153" t="n"/>
+      <c r="D75" s="153" t="n"/>
+      <c r="E75" s="154" t="n"/>
+      <c r="F75" s="155">
         <f>IFERROR(SUMIF($C$8:C75,"Income",$E$8:E75)-SUMIF($C$8:C75,"Expense",$E$8:E75)-SUMIF($C$8:C75,"Savings",$E$8:E75),"")</f>
         <v/>
       </c>
-      <c r="G75" s="153" t="n"/>
-      <c r="H75" s="150" t="n"/>
+      <c r="G75" s="156" t="n"/>
+      <c r="H75" s="152" t="n"/>
     </row>
     <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="146" t="n"/>
-      <c r="B76" s="147" t="n"/>
-      <c r="C76" s="147" t="n"/>
-      <c r="D76" s="147" t="n"/>
-      <c r="E76" s="148" t="n"/>
-      <c r="F76" s="148">
+      <c r="A76" s="147" t="n"/>
+      <c r="B76" s="148" t="n"/>
+      <c r="C76" s="148" t="n"/>
+      <c r="D76" s="148" t="n"/>
+      <c r="E76" s="149" t="n"/>
+      <c r="F76" s="150">
         <f>IFERROR(SUMIF($C$8:C76,"Income",$E$8:E76)-SUMIF($C$8:C76,"Expense",$E$8:E76)-SUMIF($C$8:C76,"Savings",$E$8:E76),"")</f>
         <v/>
       </c>
-      <c r="G76" s="149" t="n"/>
-      <c r="H76" s="146" t="n"/>
+      <c r="G76" s="151" t="n"/>
+      <c r="H76" s="147" t="n"/>
     </row>
     <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="150" t="n"/>
-      <c r="B77" s="151" t="n"/>
-      <c r="C77" s="151" t="n"/>
-      <c r="D77" s="151" t="n"/>
-      <c r="E77" s="152" t="n"/>
-      <c r="F77" s="152">
+      <c r="A77" s="152" t="n"/>
+      <c r="B77" s="153" t="n"/>
+      <c r="C77" s="153" t="n"/>
+      <c r="D77" s="153" t="n"/>
+      <c r="E77" s="154" t="n"/>
+      <c r="F77" s="155">
         <f>IFERROR(SUMIF($C$8:C77,"Income",$E$8:E77)-SUMIF($C$8:C77,"Expense",$E$8:E77)-SUMIF($C$8:C77,"Savings",$E$8:E77),"")</f>
         <v/>
       </c>
-      <c r="G77" s="153" t="n"/>
-      <c r="H77" s="150" t="n"/>
+      <c r="G77" s="156" t="n"/>
+      <c r="H77" s="152" t="n"/>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="146" t="n"/>
-      <c r="B78" s="147" t="n"/>
-      <c r="C78" s="147" t="n"/>
-      <c r="D78" s="147" t="n"/>
-      <c r="E78" s="148" t="n"/>
-      <c r="F78" s="148">
+      <c r="A78" s="147" t="n"/>
+      <c r="B78" s="148" t="n"/>
+      <c r="C78" s="148" t="n"/>
+      <c r="D78" s="148" t="n"/>
+      <c r="E78" s="149" t="n"/>
+      <c r="F78" s="150">
         <f>IFERROR(SUMIF($C$8:C78,"Income",$E$8:E78)-SUMIF($C$8:C78,"Expense",$E$8:E78)-SUMIF($C$8:C78,"Savings",$E$8:E78),"")</f>
         <v/>
       </c>
-      <c r="G78" s="149" t="n"/>
-      <c r="H78" s="146" t="n"/>
+      <c r="G78" s="151" t="n"/>
+      <c r="H78" s="147" t="n"/>
     </row>
     <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="150" t="n"/>
-      <c r="B79" s="151" t="n"/>
-      <c r="C79" s="151" t="n"/>
-      <c r="D79" s="151" t="n"/>
-      <c r="E79" s="152" t="n"/>
-      <c r="F79" s="152">
+      <c r="A79" s="152" t="n"/>
+      <c r="B79" s="153" t="n"/>
+      <c r="C79" s="153" t="n"/>
+      <c r="D79" s="153" t="n"/>
+      <c r="E79" s="154" t="n"/>
+      <c r="F79" s="155">
         <f>IFERROR(SUMIF($C$8:C79,"Income",$E$8:E79)-SUMIF($C$8:C79,"Expense",$E$8:E79)-SUMIF($C$8:C79,"Savings",$E$8:E79),"")</f>
         <v/>
       </c>
-      <c r="G79" s="153" t="n"/>
-      <c r="H79" s="150" t="n"/>
+      <c r="G79" s="156" t="n"/>
+      <c r="H79" s="152" t="n"/>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="146" t="n"/>
-      <c r="B80" s="147" t="n"/>
-      <c r="C80" s="147" t="n"/>
-      <c r="D80" s="147" t="n"/>
-      <c r="E80" s="148" t="n"/>
-      <c r="F80" s="148">
+      <c r="A80" s="147" t="n"/>
+      <c r="B80" s="148" t="n"/>
+      <c r="C80" s="148" t="n"/>
+      <c r="D80" s="148" t="n"/>
+      <c r="E80" s="149" t="n"/>
+      <c r="F80" s="150">
         <f>IFERROR(SUMIF($C$8:C80,"Income",$E$8:E80)-SUMIF($C$8:C80,"Expense",$E$8:E80)-SUMIF($C$8:C80,"Savings",$E$8:E80),"")</f>
         <v/>
       </c>
-      <c r="G80" s="149" t="n"/>
-      <c r="H80" s="146" t="n"/>
+      <c r="G80" s="151" t="n"/>
+      <c r="H80" s="147" t="n"/>
     </row>
     <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="150" t="n"/>
-      <c r="B81" s="151" t="n"/>
-      <c r="C81" s="151" t="n"/>
-      <c r="D81" s="151" t="n"/>
-      <c r="E81" s="152" t="n"/>
-      <c r="F81" s="152">
+      <c r="A81" s="152" t="n"/>
+      <c r="B81" s="153" t="n"/>
+      <c r="C81" s="153" t="n"/>
+      <c r="D81" s="153" t="n"/>
+      <c r="E81" s="154" t="n"/>
+      <c r="F81" s="155">
         <f>IFERROR(SUMIF($C$8:C81,"Income",$E$8:E81)-SUMIF($C$8:C81,"Expense",$E$8:E81)-SUMIF($C$8:C81,"Savings",$E$8:E81),"")</f>
         <v/>
       </c>
-      <c r="G81" s="153" t="n"/>
-      <c r="H81" s="150" t="n"/>
+      <c r="G81" s="156" t="n"/>
+      <c r="H81" s="152" t="n"/>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="146" t="n"/>
-      <c r="B82" s="147" t="n"/>
-      <c r="C82" s="147" t="n"/>
-      <c r="D82" s="147" t="n"/>
-      <c r="E82" s="148" t="n"/>
-      <c r="F82" s="148">
+      <c r="A82" s="147" t="n"/>
+      <c r="B82" s="148" t="n"/>
+      <c r="C82" s="148" t="n"/>
+      <c r="D82" s="148" t="n"/>
+      <c r="E82" s="149" t="n"/>
+      <c r="F82" s="150">
         <f>IFERROR(SUMIF($C$8:C82,"Income",$E$8:E82)-SUMIF($C$8:C82,"Expense",$E$8:E82)-SUMIF($C$8:C82,"Savings",$E$8:E82),"")</f>
         <v/>
       </c>
-      <c r="G82" s="149" t="n"/>
-      <c r="H82" s="146" t="n"/>
+      <c r="G82" s="151" t="n"/>
+      <c r="H82" s="147" t="n"/>
     </row>
     <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="150" t="n"/>
-      <c r="B83" s="151" t="n"/>
-      <c r="C83" s="151" t="n"/>
-      <c r="D83" s="151" t="n"/>
-      <c r="E83" s="152" t="n"/>
-      <c r="F83" s="152">
+      <c r="A83" s="152" t="n"/>
+      <c r="B83" s="153" t="n"/>
+      <c r="C83" s="153" t="n"/>
+      <c r="D83" s="153" t="n"/>
+      <c r="E83" s="154" t="n"/>
+      <c r="F83" s="155">
         <f>IFERROR(SUMIF($C$8:C83,"Income",$E$8:E83)-SUMIF($C$8:C83,"Expense",$E$8:E83)-SUMIF($C$8:C83,"Savings",$E$8:E83),"")</f>
         <v/>
       </c>
-      <c r="G83" s="153" t="n"/>
-      <c r="H83" s="150" t="n"/>
+      <c r="G83" s="156" t="n"/>
+      <c r="H83" s="152" t="n"/>
     </row>
     <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="146" t="n"/>
-      <c r="B84" s="147" t="n"/>
-      <c r="C84" s="147" t="n"/>
-      <c r="D84" s="147" t="n"/>
-      <c r="E84" s="148" t="n"/>
-      <c r="F84" s="148">
+      <c r="A84" s="147" t="n"/>
+      <c r="B84" s="148" t="n"/>
+      <c r="C84" s="148" t="n"/>
+      <c r="D84" s="148" t="n"/>
+      <c r="E84" s="149" t="n"/>
+      <c r="F84" s="150">
         <f>IFERROR(SUMIF($C$8:C84,"Income",$E$8:E84)-SUMIF($C$8:C84,"Expense",$E$8:E84)-SUMIF($C$8:C84,"Savings",$E$8:E84),"")</f>
         <v/>
       </c>
-      <c r="G84" s="149" t="n"/>
-      <c r="H84" s="146" t="n"/>
+      <c r="G84" s="151" t="n"/>
+      <c r="H84" s="147" t="n"/>
     </row>
     <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="150" t="n"/>
-      <c r="B85" s="151" t="n"/>
-      <c r="C85" s="151" t="n"/>
-      <c r="D85" s="151" t="n"/>
-      <c r="E85" s="152" t="n"/>
-      <c r="F85" s="152">
+      <c r="A85" s="152" t="n"/>
+      <c r="B85" s="153" t="n"/>
+      <c r="C85" s="153" t="n"/>
+      <c r="D85" s="153" t="n"/>
+      <c r="E85" s="154" t="n"/>
+      <c r="F85" s="155">
         <f>IFERROR(SUMIF($C$8:C85,"Income",$E$8:E85)-SUMIF($C$8:C85,"Expense",$E$8:E85)-SUMIF($C$8:C85,"Savings",$E$8:E85),"")</f>
         <v/>
       </c>
-      <c r="G85" s="153" t="n"/>
-      <c r="H85" s="150" t="n"/>
+      <c r="G85" s="156" t="n"/>
+      <c r="H85" s="152" t="n"/>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="146" t="n"/>
-      <c r="B86" s="147" t="n"/>
-      <c r="C86" s="147" t="n"/>
-      <c r="D86" s="147" t="n"/>
-      <c r="E86" s="148" t="n"/>
-      <c r="F86" s="148">
+      <c r="A86" s="147" t="n"/>
+      <c r="B86" s="148" t="n"/>
+      <c r="C86" s="148" t="n"/>
+      <c r="D86" s="148" t="n"/>
+      <c r="E86" s="149" t="n"/>
+      <c r="F86" s="150">
         <f>IFERROR(SUMIF($C$8:C86,"Income",$E$8:E86)-SUMIF($C$8:C86,"Expense",$E$8:E86)-SUMIF($C$8:C86,"Savings",$E$8:E86),"")</f>
         <v/>
       </c>
-      <c r="G86" s="149" t="n"/>
-      <c r="H86" s="146" t="n"/>
+      <c r="G86" s="151" t="n"/>
+      <c r="H86" s="147" t="n"/>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="150" t="n"/>
-      <c r="B87" s="151" t="n"/>
-      <c r="C87" s="151" t="n"/>
-      <c r="D87" s="151" t="n"/>
-      <c r="E87" s="152" t="n"/>
-      <c r="F87" s="152">
+      <c r="A87" s="152" t="n"/>
+      <c r="B87" s="153" t="n"/>
+      <c r="C87" s="153" t="n"/>
+      <c r="D87" s="153" t="n"/>
+      <c r="E87" s="154" t="n"/>
+      <c r="F87" s="155">
         <f>IFERROR(SUMIF($C$8:C87,"Income",$E$8:E87)-SUMIF($C$8:C87,"Expense",$E$8:E87)-SUMIF($C$8:C87,"Savings",$E$8:E87),"")</f>
         <v/>
       </c>
-      <c r="G87" s="153" t="n"/>
-      <c r="H87" s="150" t="n"/>
+      <c r="G87" s="156" t="n"/>
+      <c r="H87" s="152" t="n"/>
     </row>
     <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="146" t="n"/>
-      <c r="B88" s="147" t="n"/>
-      <c r="C88" s="147" t="n"/>
-      <c r="D88" s="147" t="n"/>
-      <c r="E88" s="148" t="n"/>
-      <c r="F88" s="148">
+      <c r="A88" s="147" t="n"/>
+      <c r="B88" s="148" t="n"/>
+      <c r="C88" s="148" t="n"/>
+      <c r="D88" s="148" t="n"/>
+      <c r="E88" s="149" t="n"/>
+      <c r="F88" s="150">
         <f>IFERROR(SUMIF($C$8:C88,"Income",$E$8:E88)-SUMIF($C$8:C88,"Expense",$E$8:E88)-SUMIF($C$8:C88,"Savings",$E$8:E88),"")</f>
         <v/>
       </c>
-      <c r="G88" s="149" t="n"/>
-      <c r="H88" s="146" t="n"/>
+      <c r="G88" s="151" t="n"/>
+      <c r="H88" s="147" t="n"/>
     </row>
     <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="150" t="n"/>
-      <c r="B89" s="151" t="n"/>
-      <c r="C89" s="151" t="n"/>
-      <c r="D89" s="151" t="n"/>
-      <c r="E89" s="152" t="n"/>
-      <c r="F89" s="152">
+      <c r="A89" s="152" t="n"/>
+      <c r="B89" s="153" t="n"/>
+      <c r="C89" s="153" t="n"/>
+      <c r="D89" s="153" t="n"/>
+      <c r="E89" s="154" t="n"/>
+      <c r="F89" s="155">
         <f>IFERROR(SUMIF($C$8:C89,"Income",$E$8:E89)-SUMIF($C$8:C89,"Expense",$E$8:E89)-SUMIF($C$8:C89,"Savings",$E$8:E89),"")</f>
         <v/>
       </c>
-      <c r="G89" s="153" t="n"/>
-      <c r="H89" s="150" t="n"/>
+      <c r="G89" s="156" t="n"/>
+      <c r="H89" s="152" t="n"/>
     </row>
     <row r="90" ht="18" customHeight="1">
-      <c r="A90" s="146" t="n"/>
-      <c r="B90" s="147" t="n"/>
-      <c r="C90" s="147" t="n"/>
-      <c r="D90" s="147" t="n"/>
-      <c r="E90" s="148" t="n"/>
-      <c r="F90" s="148">
+      <c r="A90" s="147" t="n"/>
+      <c r="B90" s="148" t="n"/>
+      <c r="C90" s="148" t="n"/>
+      <c r="D90" s="148" t="n"/>
+      <c r="E90" s="149" t="n"/>
+      <c r="F90" s="150">
         <f>IFERROR(SUMIF($C$8:C90,"Income",$E$8:E90)-SUMIF($C$8:C90,"Expense",$E$8:E90)-SUMIF($C$8:C90,"Savings",$E$8:E90),"")</f>
         <v/>
       </c>
-      <c r="G90" s="149" t="n"/>
-      <c r="H90" s="146" t="n"/>
+      <c r="G90" s="151" t="n"/>
+      <c r="H90" s="147" t="n"/>
     </row>
     <row r="91" ht="18" customHeight="1">
-      <c r="A91" s="150" t="n"/>
-      <c r="B91" s="151" t="n"/>
-      <c r="C91" s="151" t="n"/>
-      <c r="D91" s="151" t="n"/>
-      <c r="E91" s="152" t="n"/>
-      <c r="F91" s="152">
+      <c r="A91" s="152" t="n"/>
+      <c r="B91" s="153" t="n"/>
+      <c r="C91" s="153" t="n"/>
+      <c r="D91" s="153" t="n"/>
+      <c r="E91" s="154" t="n"/>
+      <c r="F91" s="155">
         <f>IFERROR(SUMIF($C$8:C91,"Income",$E$8:E91)-SUMIF($C$8:C91,"Expense",$E$8:E91)-SUMIF($C$8:C91,"Savings",$E$8:E91),"")</f>
         <v/>
       </c>
-      <c r="G91" s="153" t="n"/>
-      <c r="H91" s="150" t="n"/>
+      <c r="G91" s="156" t="n"/>
+      <c r="H91" s="152" t="n"/>
     </row>
     <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="146" t="n"/>
-      <c r="B92" s="147" t="n"/>
-      <c r="C92" s="147" t="n"/>
-      <c r="D92" s="147" t="n"/>
-      <c r="E92" s="148" t="n"/>
-      <c r="F92" s="148">
+      <c r="A92" s="147" t="n"/>
+      <c r="B92" s="148" t="n"/>
+      <c r="C92" s="148" t="n"/>
+      <c r="D92" s="148" t="n"/>
+      <c r="E92" s="149" t="n"/>
+      <c r="F92" s="150">
         <f>IFERROR(SUMIF($C$8:C92,"Income",$E$8:E92)-SUMIF($C$8:C92,"Expense",$E$8:E92)-SUMIF($C$8:C92,"Savings",$E$8:E92),"")</f>
         <v/>
       </c>
-      <c r="G92" s="149" t="n"/>
-      <c r="H92" s="146" t="n"/>
+      <c r="G92" s="151" t="n"/>
+      <c r="H92" s="147" t="n"/>
     </row>
     <row r="93" ht="18" customHeight="1">
-      <c r="A93" s="150" t="n"/>
-      <c r="B93" s="151" t="n"/>
-      <c r="C93" s="151" t="n"/>
-      <c r="D93" s="151" t="n"/>
-      <c r="E93" s="152" t="n"/>
-      <c r="F93" s="152">
+      <c r="A93" s="152" t="n"/>
+      <c r="B93" s="153" t="n"/>
+      <c r="C93" s="153" t="n"/>
+      <c r="D93" s="153" t="n"/>
+      <c r="E93" s="154" t="n"/>
+      <c r="F93" s="155">
         <f>IFERROR(SUMIF($C$8:C93,"Income",$E$8:E93)-SUMIF($C$8:C93,"Expense",$E$8:E93)-SUMIF($C$8:C93,"Savings",$E$8:E93),"")</f>
         <v/>
       </c>
-      <c r="G93" s="153" t="n"/>
-      <c r="H93" s="150" t="n"/>
+      <c r="G93" s="156" t="n"/>
+      <c r="H93" s="152" t="n"/>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="A94" s="146" t="n"/>
-      <c r="B94" s="147" t="n"/>
-      <c r="C94" s="147" t="n"/>
-      <c r="D94" s="147" t="n"/>
-      <c r="E94" s="148" t="n"/>
-      <c r="F94" s="148">
+      <c r="A94" s="147" t="n"/>
+      <c r="B94" s="148" t="n"/>
+      <c r="C94" s="148" t="n"/>
+      <c r="D94" s="148" t="n"/>
+      <c r="E94" s="149" t="n"/>
+      <c r="F94" s="150">
         <f>IFERROR(SUMIF($C$8:C94,"Income",$E$8:E94)-SUMIF($C$8:C94,"Expense",$E$8:E94)-SUMIF($C$8:C94,"Savings",$E$8:E94),"")</f>
         <v/>
       </c>
-      <c r="G94" s="149" t="n"/>
-      <c r="H94" s="146" t="n"/>
+      <c r="G94" s="151" t="n"/>
+      <c r="H94" s="147" t="n"/>
     </row>
     <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="150" t="n"/>
-      <c r="B95" s="151" t="n"/>
-      <c r="C95" s="151" t="n"/>
-      <c r="D95" s="151" t="n"/>
-      <c r="E95" s="152" t="n"/>
-      <c r="F95" s="152">
+      <c r="A95" s="152" t="n"/>
+      <c r="B95" s="153" t="n"/>
+      <c r="C95" s="153" t="n"/>
+      <c r="D95" s="153" t="n"/>
+      <c r="E95" s="154" t="n"/>
+      <c r="F95" s="155">
         <f>IFERROR(SUMIF($C$8:C95,"Income",$E$8:E95)-SUMIF($C$8:C95,"Expense",$E$8:E95)-SUMIF($C$8:C95,"Savings",$E$8:E95),"")</f>
         <v/>
       </c>
-      <c r="G95" s="153" t="n"/>
-      <c r="H95" s="150" t="n"/>
+      <c r="G95" s="156" t="n"/>
+      <c r="H95" s="152" t="n"/>
     </row>
     <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="146" t="n"/>
-      <c r="B96" s="147" t="n"/>
-      <c r="C96" s="147" t="n"/>
-      <c r="D96" s="147" t="n"/>
-      <c r="E96" s="148" t="n"/>
-      <c r="F96" s="148">
+      <c r="A96" s="147" t="n"/>
+      <c r="B96" s="148" t="n"/>
+      <c r="C96" s="148" t="n"/>
+      <c r="D96" s="148" t="n"/>
+      <c r="E96" s="149" t="n"/>
+      <c r="F96" s="150">
         <f>IFERROR(SUMIF($C$8:C96,"Income",$E$8:E96)-SUMIF($C$8:C96,"Expense",$E$8:E96)-SUMIF($C$8:C96,"Savings",$E$8:E96),"")</f>
         <v/>
       </c>
-      <c r="G96" s="149" t="n"/>
-      <c r="H96" s="146" t="n"/>
+      <c r="G96" s="151" t="n"/>
+      <c r="H96" s="147" t="n"/>
     </row>
     <row r="97" ht="18" customHeight="1">
-      <c r="A97" s="150" t="n"/>
-      <c r="B97" s="151" t="n"/>
-      <c r="C97" s="151" t="n"/>
-      <c r="D97" s="151" t="n"/>
-      <c r="E97" s="152" t="n"/>
-      <c r="F97" s="152">
+      <c r="A97" s="152" t="n"/>
+      <c r="B97" s="153" t="n"/>
+      <c r="C97" s="153" t="n"/>
+      <c r="D97" s="153" t="n"/>
+      <c r="E97" s="154" t="n"/>
+      <c r="F97" s="155">
         <f>IFERROR(SUMIF($C$8:C97,"Income",$E$8:E97)-SUMIF($C$8:C97,"Expense",$E$8:E97)-SUMIF($C$8:C97,"Savings",$E$8:E97),"")</f>
         <v/>
       </c>
-      <c r="G97" s="153" t="n"/>
-      <c r="H97" s="150" t="n"/>
+      <c r="G97" s="156" t="n"/>
+      <c r="H97" s="152" t="n"/>
     </row>
     <row r="98" ht="18" customHeight="1">
-      <c r="A98" s="146" t="n"/>
-      <c r="B98" s="147" t="n"/>
-      <c r="C98" s="147" t="n"/>
-      <c r="D98" s="147" t="n"/>
-      <c r="E98" s="148" t="n"/>
-      <c r="F98" s="148">
+      <c r="A98" s="147" t="n"/>
+      <c r="B98" s="148" t="n"/>
+      <c r="C98" s="148" t="n"/>
+      <c r="D98" s="148" t="n"/>
+      <c r="E98" s="149" t="n"/>
+      <c r="F98" s="150">
         <f>IFERROR(SUMIF($C$8:C98,"Income",$E$8:E98)-SUMIF($C$8:C98,"Expense",$E$8:E98)-SUMIF($C$8:C98,"Savings",$E$8:E98),"")</f>
         <v/>
       </c>
-      <c r="G98" s="149" t="n"/>
-      <c r="H98" s="146" t="n"/>
+      <c r="G98" s="151" t="n"/>
+      <c r="H98" s="147" t="n"/>
     </row>
     <row r="99" ht="18" customHeight="1">
-      <c r="A99" s="150" t="n"/>
-      <c r="B99" s="151" t="n"/>
-      <c r="C99" s="151" t="n"/>
-      <c r="D99" s="151" t="n"/>
-      <c r="E99" s="152" t="n"/>
-      <c r="F99" s="152">
+      <c r="A99" s="152" t="n"/>
+      <c r="B99" s="153" t="n"/>
+      <c r="C99" s="153" t="n"/>
+      <c r="D99" s="153" t="n"/>
+      <c r="E99" s="154" t="n"/>
+      <c r="F99" s="155">
         <f>IFERROR(SUMIF($C$8:C99,"Income",$E$8:E99)-SUMIF($C$8:C99,"Expense",$E$8:E99)-SUMIF($C$8:C99,"Savings",$E$8:E99),"")</f>
         <v/>
       </c>
-      <c r="G99" s="153" t="n"/>
-      <c r="H99" s="150" t="n"/>
+      <c r="G99" s="156" t="n"/>
+      <c r="H99" s="152" t="n"/>
     </row>
     <row r="100" ht="18" customHeight="1">
-      <c r="A100" s="146" t="n"/>
-      <c r="B100" s="147" t="n"/>
-      <c r="C100" s="147" t="n"/>
-      <c r="D100" s="147" t="n"/>
-      <c r="E100" s="148" t="n"/>
-      <c r="F100" s="148">
+      <c r="A100" s="147" t="n"/>
+      <c r="B100" s="148" t="n"/>
+      <c r="C100" s="148" t="n"/>
+      <c r="D100" s="148" t="n"/>
+      <c r="E100" s="149" t="n"/>
+      <c r="F100" s="150">
         <f>IFERROR(SUMIF($C$8:C100,"Income",$E$8:E100)-SUMIF($C$8:C100,"Expense",$E$8:E100)-SUMIF($C$8:C100,"Savings",$E$8:E100),"")</f>
         <v/>
       </c>
-      <c r="G100" s="149" t="n"/>
-      <c r="H100" s="146" t="n"/>
+      <c r="G100" s="151" t="n"/>
+      <c r="H100" s="147" t="n"/>
     </row>
     <row r="101" ht="18" customHeight="1">
-      <c r="A101" s="150" t="n"/>
-      <c r="B101" s="151" t="n"/>
-      <c r="C101" s="151" t="n"/>
-      <c r="D101" s="151" t="n"/>
-      <c r="E101" s="152" t="n"/>
-      <c r="F101" s="152">
+      <c r="A101" s="152" t="n"/>
+      <c r="B101" s="153" t="n"/>
+      <c r="C101" s="153" t="n"/>
+      <c r="D101" s="153" t="n"/>
+      <c r="E101" s="154" t="n"/>
+      <c r="F101" s="155">
         <f>IFERROR(SUMIF($C$8:C101,"Income",$E$8:E101)-SUMIF($C$8:C101,"Expense",$E$8:E101)-SUMIF($C$8:C101,"Savings",$E$8:E101),"")</f>
         <v/>
       </c>
-      <c r="G101" s="153" t="n"/>
-      <c r="H101" s="150" t="n"/>
+      <c r="G101" s="156" t="n"/>
+      <c r="H101" s="152" t="n"/>
     </row>
     <row r="102" ht="18" customHeight="1">
-      <c r="A102" s="146" t="n"/>
-      <c r="B102" s="147" t="n"/>
-      <c r="C102" s="147" t="n"/>
-      <c r="D102" s="147" t="n"/>
-      <c r="E102" s="148" t="n"/>
-      <c r="F102" s="148">
+      <c r="A102" s="147" t="n"/>
+      <c r="B102" s="148" t="n"/>
+      <c r="C102" s="148" t="n"/>
+      <c r="D102" s="148" t="n"/>
+      <c r="E102" s="149" t="n"/>
+      <c r="F102" s="150">
         <f>IFERROR(SUMIF($C$8:C102,"Income",$E$8:E102)-SUMIF($C$8:C102,"Expense",$E$8:E102)-SUMIF($C$8:C102,"Savings",$E$8:E102),"")</f>
         <v/>
       </c>
-      <c r="G102" s="149" t="n"/>
-      <c r="H102" s="146" t="n"/>
+      <c r="G102" s="151" t="n"/>
+      <c r="H102" s="147" t="n"/>
     </row>
     <row r="103" ht="18" customHeight="1">
-      <c r="A103" s="150" t="n"/>
-      <c r="B103" s="151" t="n"/>
-      <c r="C103" s="151" t="n"/>
-      <c r="D103" s="151" t="n"/>
-      <c r="E103" s="152" t="n"/>
-      <c r="F103" s="152">
+      <c r="A103" s="152" t="n"/>
+      <c r="B103" s="153" t="n"/>
+      <c r="C103" s="153" t="n"/>
+      <c r="D103" s="153" t="n"/>
+      <c r="E103" s="154" t="n"/>
+      <c r="F103" s="155">
         <f>IFERROR(SUMIF($C$8:C103,"Income",$E$8:E103)-SUMIF($C$8:C103,"Expense",$E$8:E103)-SUMIF($C$8:C103,"Savings",$E$8:E103),"")</f>
         <v/>
       </c>
-      <c r="G103" s="153" t="n"/>
-      <c r="H103" s="150" t="n"/>
+      <c r="G103" s="156" t="n"/>
+      <c r="H103" s="152" t="n"/>
     </row>
     <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="146" t="n"/>
-      <c r="B104" s="147" t="n"/>
-      <c r="C104" s="147" t="n"/>
-      <c r="D104" s="147" t="n"/>
-      <c r="E104" s="148" t="n"/>
-      <c r="F104" s="148">
+      <c r="A104" s="147" t="n"/>
+      <c r="B104" s="148" t="n"/>
+      <c r="C104" s="148" t="n"/>
+      <c r="D104" s="148" t="n"/>
+      <c r="E104" s="149" t="n"/>
+      <c r="F104" s="150">
         <f>IFERROR(SUMIF($C$8:C104,"Income",$E$8:E104)-SUMIF($C$8:C104,"Expense",$E$8:E104)-SUMIF($C$8:C104,"Savings",$E$8:E104),"")</f>
         <v/>
       </c>
-      <c r="G104" s="149" t="n"/>
-      <c r="H104" s="146" t="n"/>
+      <c r="G104" s="151" t="n"/>
+      <c r="H104" s="147" t="n"/>
     </row>
     <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="150" t="n"/>
-      <c r="B105" s="151" t="n"/>
-      <c r="C105" s="151" t="n"/>
-      <c r="D105" s="151" t="n"/>
-      <c r="E105" s="152" t="n"/>
-      <c r="F105" s="152">
+      <c r="A105" s="152" t="n"/>
+      <c r="B105" s="153" t="n"/>
+      <c r="C105" s="153" t="n"/>
+      <c r="D105" s="153" t="n"/>
+      <c r="E105" s="154" t="n"/>
+      <c r="F105" s="155">
         <f>IFERROR(SUMIF($C$8:C105,"Income",$E$8:E105)-SUMIF($C$8:C105,"Expense",$E$8:E105)-SUMIF($C$8:C105,"Savings",$E$8:E105),"")</f>
         <v/>
       </c>
-      <c r="G105" s="153" t="n"/>
-      <c r="H105" s="150" t="n"/>
+      <c r="G105" s="156" t="n"/>
+      <c r="H105" s="152" t="n"/>
     </row>
     <row r="106" ht="18" customHeight="1">
-      <c r="A106" s="146" t="n"/>
-      <c r="B106" s="147" t="n"/>
-      <c r="C106" s="147" t="n"/>
-      <c r="D106" s="147" t="n"/>
-      <c r="E106" s="148" t="n"/>
-      <c r="F106" s="148">
+      <c r="A106" s="147" t="n"/>
+      <c r="B106" s="148" t="n"/>
+      <c r="C106" s="148" t="n"/>
+      <c r="D106" s="148" t="n"/>
+      <c r="E106" s="149" t="n"/>
+      <c r="F106" s="150">
         <f>IFERROR(SUMIF($C$8:C106,"Income",$E$8:E106)-SUMIF($C$8:C106,"Expense",$E$8:E106)-SUMIF($C$8:C106,"Savings",$E$8:E106),"")</f>
         <v/>
       </c>
-      <c r="G106" s="149" t="n"/>
-      <c r="H106" s="146" t="n"/>
+      <c r="G106" s="151" t="n"/>
+      <c r="H106" s="147" t="n"/>
     </row>
     <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="150" t="n"/>
-      <c r="B107" s="151" t="n"/>
-      <c r="C107" s="151" t="n"/>
-      <c r="D107" s="151" t="n"/>
-      <c r="E107" s="152" t="n"/>
-      <c r="F107" s="152">
+      <c r="A107" s="152" t="n"/>
+      <c r="B107" s="153" t="n"/>
+      <c r="C107" s="153" t="n"/>
+      <c r="D107" s="153" t="n"/>
+      <c r="E107" s="154" t="n"/>
+      <c r="F107" s="155">
         <f>IFERROR(SUMIF($C$8:C107,"Income",$E$8:E107)-SUMIF($C$8:C107,"Expense",$E$8:E107)-SUMIF($C$8:C107,"Savings",$E$8:E107),"")</f>
         <v/>
       </c>
-      <c r="G107" s="153" t="n"/>
-      <c r="H107" s="150" t="n"/>
+      <c r="G107" s="156" t="n"/>
+      <c r="H107" s="152" t="n"/>
     </row>
     <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="146" t="n"/>
-      <c r="B108" s="147" t="n"/>
-      <c r="C108" s="147" t="n"/>
-      <c r="D108" s="147" t="n"/>
-      <c r="E108" s="148" t="n"/>
-      <c r="F108" s="148">
+      <c r="A108" s="147" t="n"/>
+      <c r="B108" s="148" t="n"/>
+      <c r="C108" s="148" t="n"/>
+      <c r="D108" s="148" t="n"/>
+      <c r="E108" s="149" t="n"/>
+      <c r="F108" s="150">
         <f>IFERROR(SUMIF($C$8:C108,"Income",$E$8:E108)-SUMIF($C$8:C108,"Expense",$E$8:E108)-SUMIF($C$8:C108,"Savings",$E$8:E108),"")</f>
         <v/>
       </c>
-      <c r="G108" s="149" t="n"/>
-      <c r="H108" s="146" t="n"/>
+      <c r="G108" s="151" t="n"/>
+      <c r="H108" s="147" t="n"/>
     </row>
     <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="150" t="n"/>
-      <c r="B109" s="151" t="n"/>
-      <c r="C109" s="151" t="n"/>
-      <c r="D109" s="151" t="n"/>
-      <c r="E109" s="152" t="n"/>
-      <c r="F109" s="152">
+      <c r="A109" s="152" t="n"/>
+      <c r="B109" s="153" t="n"/>
+      <c r="C109" s="153" t="n"/>
+      <c r="D109" s="153" t="n"/>
+      <c r="E109" s="154" t="n"/>
+      <c r="F109" s="155">
         <f>IFERROR(SUMIF($C$8:C109,"Income",$E$8:E109)-SUMIF($C$8:C109,"Expense",$E$8:E109)-SUMIF($C$8:C109,"Savings",$E$8:E109),"")</f>
         <v/>
       </c>
-      <c r="G109" s="153" t="n"/>
-      <c r="H109" s="150" t="n"/>
+      <c r="G109" s="156" t="n"/>
+      <c r="H109" s="152" t="n"/>
     </row>
     <row r="110" ht="18" customHeight="1">
-      <c r="A110" s="146" t="n"/>
-      <c r="B110" s="147" t="n"/>
-      <c r="C110" s="147" t="n"/>
-      <c r="D110" s="147" t="n"/>
-      <c r="E110" s="148" t="n"/>
-      <c r="F110" s="148">
+      <c r="A110" s="147" t="n"/>
+      <c r="B110" s="148" t="n"/>
+      <c r="C110" s="148" t="n"/>
+      <c r="D110" s="148" t="n"/>
+      <c r="E110" s="149" t="n"/>
+      <c r="F110" s="150">
         <f>IFERROR(SUMIF($C$8:C110,"Income",$E$8:E110)-SUMIF($C$8:C110,"Expense",$E$8:E110)-SUMIF($C$8:C110,"Savings",$E$8:E110),"")</f>
         <v/>
       </c>
-      <c r="G110" s="149" t="n"/>
-      <c r="H110" s="146" t="n"/>
+      <c r="G110" s="151" t="n"/>
+      <c r="H110" s="147" t="n"/>
     </row>
     <row r="111" ht="18" customHeight="1">
-      <c r="A111" s="150" t="n"/>
-      <c r="B111" s="151" t="n"/>
-      <c r="C111" s="151" t="n"/>
-      <c r="D111" s="151" t="n"/>
-      <c r="E111" s="152" t="n"/>
-      <c r="F111" s="152">
+      <c r="A111" s="152" t="n"/>
+      <c r="B111" s="153" t="n"/>
+      <c r="C111" s="153" t="n"/>
+      <c r="D111" s="153" t="n"/>
+      <c r="E111" s="154" t="n"/>
+      <c r="F111" s="155">
         <f>IFERROR(SUMIF($C$8:C111,"Income",$E$8:E111)-SUMIF($C$8:C111,"Expense",$E$8:E111)-SUMIF($C$8:C111,"Savings",$E$8:E111),"")</f>
         <v/>
       </c>
-      <c r="G111" s="153" t="n"/>
-      <c r="H111" s="150" t="n"/>
+      <c r="G111" s="156" t="n"/>
+      <c r="H111" s="152" t="n"/>
     </row>
     <row r="112" ht="18" customHeight="1">
-      <c r="A112" s="146" t="n"/>
-      <c r="B112" s="147" t="n"/>
-      <c r="C112" s="147" t="n"/>
-      <c r="D112" s="147" t="n"/>
-      <c r="E112" s="148" t="n"/>
-      <c r="F112" s="148">
+      <c r="A112" s="147" t="n"/>
+      <c r="B112" s="148" t="n"/>
+      <c r="C112" s="148" t="n"/>
+      <c r="D112" s="148" t="n"/>
+      <c r="E112" s="149" t="n"/>
+      <c r="F112" s="150">
         <f>IFERROR(SUMIF($C$8:C112,"Income",$E$8:E112)-SUMIF($C$8:C112,"Expense",$E$8:E112)-SUMIF($C$8:C112,"Savings",$E$8:E112),"")</f>
         <v/>
       </c>
-      <c r="G112" s="149" t="n"/>
-      <c r="H112" s="146" t="n"/>
+      <c r="G112" s="151" t="n"/>
+      <c r="H112" s="147" t="n"/>
     </row>
     <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="150" t="n"/>
-      <c r="B113" s="151" t="n"/>
-      <c r="C113" s="151" t="n"/>
-      <c r="D113" s="151" t="n"/>
-      <c r="E113" s="152" t="n"/>
-      <c r="F113" s="152">
+      <c r="A113" s="152" t="n"/>
+      <c r="B113" s="153" t="n"/>
+      <c r="C113" s="153" t="n"/>
+      <c r="D113" s="153" t="n"/>
+      <c r="E113" s="154" t="n"/>
+      <c r="F113" s="155">
         <f>IFERROR(SUMIF($C$8:C113,"Income",$E$8:E113)-SUMIF($C$8:C113,"Expense",$E$8:E113)-SUMIF($C$8:C113,"Savings",$E$8:E113),"")</f>
         <v/>
       </c>
-      <c r="G113" s="153" t="n"/>
-      <c r="H113" s="150" t="n"/>
+      <c r="G113" s="156" t="n"/>
+      <c r="H113" s="152" t="n"/>
     </row>
     <row r="114" ht="18" customHeight="1">
-      <c r="A114" s="146" t="n"/>
-      <c r="B114" s="147" t="n"/>
-      <c r="C114" s="147" t="n"/>
-      <c r="D114" s="147" t="n"/>
-      <c r="E114" s="148" t="n"/>
-      <c r="F114" s="148">
+      <c r="A114" s="147" t="n"/>
+      <c r="B114" s="148" t="n"/>
+      <c r="C114" s="148" t="n"/>
+      <c r="D114" s="148" t="n"/>
+      <c r="E114" s="149" t="n"/>
+      <c r="F114" s="150">
         <f>IFERROR(SUMIF($C$8:C114,"Income",$E$8:E114)-SUMIF($C$8:C114,"Expense",$E$8:E114)-SUMIF($C$8:C114,"Savings",$E$8:E114),"")</f>
         <v/>
       </c>
-      <c r="G114" s="149" t="n"/>
-      <c r="H114" s="146" t="n"/>
+      <c r="G114" s="151" t="n"/>
+      <c r="H114" s="147" t="n"/>
     </row>
     <row r="115" ht="18" customHeight="1">
-      <c r="A115" s="150" t="n"/>
-      <c r="B115" s="151" t="n"/>
-      <c r="C115" s="151" t="n"/>
-      <c r="D115" s="151" t="n"/>
-      <c r="E115" s="152" t="n"/>
-      <c r="F115" s="152">
+      <c r="A115" s="152" t="n"/>
+      <c r="B115" s="153" t="n"/>
+      <c r="C115" s="153" t="n"/>
+      <c r="D115" s="153" t="n"/>
+      <c r="E115" s="154" t="n"/>
+      <c r="F115" s="155">
         <f>IFERROR(SUMIF($C$8:C115,"Income",$E$8:E115)-SUMIF($C$8:C115,"Expense",$E$8:E115)-SUMIF($C$8:C115,"Savings",$E$8:E115),"")</f>
         <v/>
       </c>
-      <c r="G115" s="153" t="n"/>
-      <c r="H115" s="150" t="n"/>
+      <c r="G115" s="156" t="n"/>
+      <c r="H115" s="152" t="n"/>
     </row>
     <row r="116" ht="18" customHeight="1">
-      <c r="A116" s="146" t="n"/>
-      <c r="B116" s="147" t="n"/>
-      <c r="C116" s="147" t="n"/>
-      <c r="D116" s="147" t="n"/>
-      <c r="E116" s="148" t="n"/>
-      <c r="F116" s="148">
+      <c r="A116" s="147" t="n"/>
+      <c r="B116" s="148" t="n"/>
+      <c r="C116" s="148" t="n"/>
+      <c r="D116" s="148" t="n"/>
+      <c r="E116" s="149" t="n"/>
+      <c r="F116" s="150">
         <f>IFERROR(SUMIF($C$8:C116,"Income",$E$8:E116)-SUMIF($C$8:C116,"Expense",$E$8:E116)-SUMIF($C$8:C116,"Savings",$E$8:E116),"")</f>
         <v/>
       </c>
-      <c r="G116" s="149" t="n"/>
-      <c r="H116" s="146" t="n"/>
+      <c r="G116" s="151" t="n"/>
+      <c r="H116" s="147" t="n"/>
     </row>
     <row r="117" ht="18" customHeight="1">
-      <c r="A117" s="150" t="n"/>
-      <c r="B117" s="151" t="n"/>
-      <c r="C117" s="151" t="n"/>
-      <c r="D117" s="151" t="n"/>
-      <c r="E117" s="152" t="n"/>
-      <c r="F117" s="152">
+      <c r="A117" s="152" t="n"/>
+      <c r="B117" s="153" t="n"/>
+      <c r="C117" s="153" t="n"/>
+      <c r="D117" s="153" t="n"/>
+      <c r="E117" s="154" t="n"/>
+      <c r="F117" s="155">
         <f>IFERROR(SUMIF($C$8:C117,"Income",$E$8:E117)-SUMIF($C$8:C117,"Expense",$E$8:E117)-SUMIF($C$8:C117,"Savings",$E$8:E117),"")</f>
         <v/>
       </c>
-      <c r="G117" s="153" t="n"/>
-      <c r="H117" s="150" t="n"/>
+      <c r="G117" s="156" t="n"/>
+      <c r="H117" s="152" t="n"/>
     </row>
     <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="146" t="n"/>
-      <c r="B118" s="147" t="n"/>
-      <c r="C118" s="147" t="n"/>
-      <c r="D118" s="147" t="n"/>
-      <c r="E118" s="148" t="n"/>
-      <c r="F118" s="148">
+      <c r="A118" s="147" t="n"/>
+      <c r="B118" s="148" t="n"/>
+      <c r="C118" s="148" t="n"/>
+      <c r="D118" s="148" t="n"/>
+      <c r="E118" s="149" t="n"/>
+      <c r="F118" s="150">
         <f>IFERROR(SUMIF($C$8:C118,"Income",$E$8:E118)-SUMIF($C$8:C118,"Expense",$E$8:E118)-SUMIF($C$8:C118,"Savings",$E$8:E118),"")</f>
         <v/>
       </c>
-      <c r="G118" s="149" t="n"/>
-      <c r="H118" s="146" t="n"/>
+      <c r="G118" s="151" t="n"/>
+      <c r="H118" s="147" t="n"/>
     </row>
     <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="150" t="n"/>
-      <c r="B119" s="151" t="n"/>
-      <c r="C119" s="151" t="n"/>
-      <c r="D119" s="151" t="n"/>
-      <c r="E119" s="152" t="n"/>
-      <c r="F119" s="152">
+      <c r="A119" s="152" t="n"/>
+      <c r="B119" s="153" t="n"/>
+      <c r="C119" s="153" t="n"/>
+      <c r="D119" s="153" t="n"/>
+      <c r="E119" s="154" t="n"/>
+      <c r="F119" s="155">
         <f>IFERROR(SUMIF($C$8:C119,"Income",$E$8:E119)-SUMIF($C$8:C119,"Expense",$E$8:E119)-SUMIF($C$8:C119,"Savings",$E$8:E119),"")</f>
         <v/>
       </c>
-      <c r="G119" s="153" t="n"/>
-      <c r="H119" s="150" t="n"/>
+      <c r="G119" s="156" t="n"/>
+      <c r="H119" s="152" t="n"/>
     </row>
     <row r="120" ht="18" customHeight="1">
-      <c r="A120" s="146" t="n"/>
-      <c r="B120" s="147" t="n"/>
-      <c r="C120" s="147" t="n"/>
-      <c r="D120" s="147" t="n"/>
-      <c r="E120" s="148" t="n"/>
-      <c r="F120" s="148">
+      <c r="A120" s="147" t="n"/>
+      <c r="B120" s="148" t="n"/>
+      <c r="C120" s="148" t="n"/>
+      <c r="D120" s="148" t="n"/>
+      <c r="E120" s="149" t="n"/>
+      <c r="F120" s="150">
         <f>IFERROR(SUMIF($C$8:C120,"Income",$E$8:E120)-SUMIF($C$8:C120,"Expense",$E$8:E120)-SUMIF($C$8:C120,"Savings",$E$8:E120),"")</f>
         <v/>
       </c>
-      <c r="G120" s="149" t="n"/>
-      <c r="H120" s="146" t="n"/>
+      <c r="G120" s="151" t="n"/>
+      <c r="H120" s="147" t="n"/>
     </row>
     <row r="121" ht="18" customHeight="1">
-      <c r="A121" s="150" t="n"/>
-      <c r="B121" s="151" t="n"/>
-      <c r="C121" s="151" t="n"/>
-      <c r="D121" s="151" t="n"/>
-      <c r="E121" s="152" t="n"/>
-      <c r="F121" s="152">
+      <c r="A121" s="152" t="n"/>
+      <c r="B121" s="153" t="n"/>
+      <c r="C121" s="153" t="n"/>
+      <c r="D121" s="153" t="n"/>
+      <c r="E121" s="154" t="n"/>
+      <c r="F121" s="155">
         <f>IFERROR(SUMIF($C$8:C121,"Income",$E$8:E121)-SUMIF($C$8:C121,"Expense",$E$8:E121)-SUMIF($C$8:C121,"Savings",$E$8:E121),"")</f>
         <v/>
       </c>
-      <c r="G121" s="153" t="n"/>
-      <c r="H121" s="150" t="n"/>
+      <c r="G121" s="156" t="n"/>
+      <c r="H121" s="152" t="n"/>
     </row>
     <row r="122" ht="18" customHeight="1">
-      <c r="A122" s="146" t="n"/>
-      <c r="B122" s="147" t="n"/>
-      <c r="C122" s="147" t="n"/>
-      <c r="D122" s="147" t="n"/>
-      <c r="E122" s="148" t="n"/>
-      <c r="F122" s="148">
+      <c r="A122" s="147" t="n"/>
+      <c r="B122" s="148" t="n"/>
+      <c r="C122" s="148" t="n"/>
+      <c r="D122" s="148" t="n"/>
+      <c r="E122" s="149" t="n"/>
+      <c r="F122" s="150">
         <f>IFERROR(SUMIF($C$8:C122,"Income",$E$8:E122)-SUMIF($C$8:C122,"Expense",$E$8:E122)-SUMIF($C$8:C122,"Savings",$E$8:E122),"")</f>
         <v/>
       </c>
-      <c r="G122" s="149" t="n"/>
-      <c r="H122" s="146" t="n"/>
+      <c r="G122" s="151" t="n"/>
+      <c r="H122" s="147" t="n"/>
     </row>
     <row r="123" ht="18" customHeight="1">
-      <c r="A123" s="150" t="n"/>
-      <c r="B123" s="151" t="n"/>
-      <c r="C123" s="151" t="n"/>
-      <c r="D123" s="151" t="n"/>
-      <c r="E123" s="152" t="n"/>
-      <c r="F123" s="152">
+      <c r="A123" s="152" t="n"/>
+      <c r="B123" s="153" t="n"/>
+      <c r="C123" s="153" t="n"/>
+      <c r="D123" s="153" t="n"/>
+      <c r="E123" s="154" t="n"/>
+      <c r="F123" s="155">
         <f>IFERROR(SUMIF($C$8:C123,"Income",$E$8:E123)-SUMIF($C$8:C123,"Expense",$E$8:E123)-SUMIF($C$8:C123,"Savings",$E$8:E123),"")</f>
         <v/>
       </c>
-      <c r="G123" s="153" t="n"/>
-      <c r="H123" s="150" t="n"/>
+      <c r="G123" s="156" t="n"/>
+      <c r="H123" s="152" t="n"/>
     </row>
     <row r="124" ht="18" customHeight="1">
-      <c r="A124" s="146" t="n"/>
-      <c r="B124" s="147" t="n"/>
-      <c r="C124" s="147" t="n"/>
-      <c r="D124" s="147" t="n"/>
-      <c r="E124" s="148" t="n"/>
-      <c r="F124" s="148">
+      <c r="A124" s="147" t="n"/>
+      <c r="B124" s="148" t="n"/>
+      <c r="C124" s="148" t="n"/>
+      <c r="D124" s="148" t="n"/>
+      <c r="E124" s="149" t="n"/>
+      <c r="F124" s="150">
         <f>IFERROR(SUMIF($C$8:C124,"Income",$E$8:E124)-SUMIF($C$8:C124,"Expense",$E$8:E124)-SUMIF($C$8:C124,"Savings",$E$8:E124),"")</f>
         <v/>
       </c>
-      <c r="G124" s="149" t="n"/>
-      <c r="H124" s="146" t="n"/>
+      <c r="G124" s="151" t="n"/>
+      <c r="H124" s="147" t="n"/>
     </row>
     <row r="125" ht="18" customHeight="1">
-      <c r="A125" s="150" t="n"/>
-      <c r="B125" s="151" t="n"/>
-      <c r="C125" s="151" t="n"/>
-      <c r="D125" s="151" t="n"/>
-      <c r="E125" s="152" t="n"/>
-      <c r="F125" s="152">
+      <c r="A125" s="152" t="n"/>
+      <c r="B125" s="153" t="n"/>
+      <c r="C125" s="153" t="n"/>
+      <c r="D125" s="153" t="n"/>
+      <c r="E125" s="154" t="n"/>
+      <c r="F125" s="155">
         <f>IFERROR(SUMIF($C$8:C125,"Income",$E$8:E125)-SUMIF($C$8:C125,"Expense",$E$8:E125)-SUMIF($C$8:C125,"Savings",$E$8:E125),"")</f>
         <v/>
       </c>
-      <c r="G125" s="153" t="n"/>
-      <c r="H125" s="150" t="n"/>
+      <c r="G125" s="156" t="n"/>
+      <c r="H125" s="152" t="n"/>
     </row>
     <row r="126" ht="18" customHeight="1">
-      <c r="A126" s="146" t="n"/>
-      <c r="B126" s="147" t="n"/>
-      <c r="C126" s="147" t="n"/>
-      <c r="D126" s="147" t="n"/>
-      <c r="E126" s="148" t="n"/>
-      <c r="F126" s="148">
+      <c r="A126" s="147" t="n"/>
+      <c r="B126" s="148" t="n"/>
+      <c r="C126" s="148" t="n"/>
+      <c r="D126" s="148" t="n"/>
+      <c r="E126" s="149" t="n"/>
+      <c r="F126" s="150">
         <f>IFERROR(SUMIF($C$8:C126,"Income",$E$8:E126)-SUMIF($C$8:C126,"Expense",$E$8:E126)-SUMIF($C$8:C126,"Savings",$E$8:E126),"")</f>
         <v/>
       </c>
-      <c r="G126" s="149" t="n"/>
-      <c r="H126" s="146" t="n"/>
+      <c r="G126" s="151" t="n"/>
+      <c r="H126" s="147" t="n"/>
     </row>
     <row r="127" ht="18" customHeight="1">
-      <c r="A127" s="150" t="n"/>
-      <c r="B127" s="151" t="n"/>
-      <c r="C127" s="151" t="n"/>
-      <c r="D127" s="151" t="n"/>
-      <c r="E127" s="152" t="n"/>
-      <c r="F127" s="152">
+      <c r="A127" s="152" t="n"/>
+      <c r="B127" s="153" t="n"/>
+      <c r="C127" s="153" t="n"/>
+      <c r="D127" s="153" t="n"/>
+      <c r="E127" s="154" t="n"/>
+      <c r="F127" s="155">
         <f>IFERROR(SUMIF($C$8:C127,"Income",$E$8:E127)-SUMIF($C$8:C127,"Expense",$E$8:E127)-SUMIF($C$8:C127,"Savings",$E$8:E127),"")</f>
         <v/>
       </c>
-      <c r="G127" s="153" t="n"/>
-      <c r="H127" s="150" t="n"/>
+      <c r="G127" s="156" t="n"/>
+      <c r="H127" s="152" t="n"/>
     </row>
     <row r="128" ht="18" customHeight="1">
-      <c r="A128" s="146" t="n"/>
-      <c r="B128" s="147" t="n"/>
-      <c r="C128" s="147" t="n"/>
-      <c r="D128" s="147" t="n"/>
-      <c r="E128" s="148" t="n"/>
-      <c r="F128" s="148">
+      <c r="A128" s="147" t="n"/>
+      <c r="B128" s="148" t="n"/>
+      <c r="C128" s="148" t="n"/>
+      <c r="D128" s="148" t="n"/>
+      <c r="E128" s="149" t="n"/>
+      <c r="F128" s="150">
         <f>IFERROR(SUMIF($C$8:C128,"Income",$E$8:E128)-SUMIF($C$8:C128,"Expense",$E$8:E128)-SUMIF($C$8:C128,"Savings",$E$8:E128),"")</f>
         <v/>
       </c>
-      <c r="G128" s="149" t="n"/>
-      <c r="H128" s="146" t="n"/>
+      <c r="G128" s="151" t="n"/>
+      <c r="H128" s="147" t="n"/>
     </row>
     <row r="129" ht="18" customHeight="1">
-      <c r="A129" s="150" t="n"/>
-      <c r="B129" s="151" t="n"/>
-      <c r="C129" s="151" t="n"/>
-      <c r="D129" s="151" t="n"/>
-      <c r="E129" s="152" t="n"/>
-      <c r="F129" s="152">
+      <c r="A129" s="152" t="n"/>
+      <c r="B129" s="153" t="n"/>
+      <c r="C129" s="153" t="n"/>
+      <c r="D129" s="153" t="n"/>
+      <c r="E129" s="154" t="n"/>
+      <c r="F129" s="155">
         <f>IFERROR(SUMIF($C$8:C129,"Income",$E$8:E129)-SUMIF($C$8:C129,"Expense",$E$8:E129)-SUMIF($C$8:C129,"Savings",$E$8:E129),"")</f>
         <v/>
       </c>
-      <c r="G129" s="153" t="n"/>
-      <c r="H129" s="150" t="n"/>
+      <c r="G129" s="156" t="n"/>
+      <c r="H129" s="152" t="n"/>
     </row>
     <row r="130" ht="18" customHeight="1">
-      <c r="A130" s="146" t="n"/>
-      <c r="B130" s="147" t="n"/>
-      <c r="C130" s="147" t="n"/>
-      <c r="D130" s="147" t="n"/>
-      <c r="E130" s="148" t="n"/>
-      <c r="F130" s="148">
+      <c r="A130" s="147" t="n"/>
+      <c r="B130" s="148" t="n"/>
+      <c r="C130" s="148" t="n"/>
+      <c r="D130" s="148" t="n"/>
+      <c r="E130" s="149" t="n"/>
+      <c r="F130" s="150">
         <f>IFERROR(SUMIF($C$8:C130,"Income",$E$8:E130)-SUMIF($C$8:C130,"Expense",$E$8:E130)-SUMIF($C$8:C130,"Savings",$E$8:E130),"")</f>
         <v/>
       </c>
-      <c r="G130" s="149" t="n"/>
-      <c r="H130" s="146" t="n"/>
+      <c r="G130" s="151" t="n"/>
+      <c r="H130" s="147" t="n"/>
     </row>
     <row r="131" ht="18" customHeight="1">
-      <c r="A131" s="150" t="n"/>
-      <c r="B131" s="151" t="n"/>
-      <c r="C131" s="151" t="n"/>
-      <c r="D131" s="151" t="n"/>
-      <c r="E131" s="152" t="n"/>
-      <c r="F131" s="152">
+      <c r="A131" s="152" t="n"/>
+      <c r="B131" s="153" t="n"/>
+      <c r="C131" s="153" t="n"/>
+      <c r="D131" s="153" t="n"/>
+      <c r="E131" s="154" t="n"/>
+      <c r="F131" s="155">
         <f>IFERROR(SUMIF($C$8:C131,"Income",$E$8:E131)-SUMIF($C$8:C131,"Expense",$E$8:E131)-SUMIF($C$8:C131,"Savings",$E$8:E131),"")</f>
         <v/>
       </c>
-      <c r="G131" s="153" t="n"/>
-      <c r="H131" s="150" t="n"/>
+      <c r="G131" s="156" t="n"/>
+      <c r="H131" s="152" t="n"/>
     </row>
     <row r="132" ht="18" customHeight="1">
-      <c r="A132" s="146" t="n"/>
-      <c r="B132" s="147" t="n"/>
-      <c r="C132" s="147" t="n"/>
-      <c r="D132" s="147" t="n"/>
-      <c r="E132" s="148" t="n"/>
-      <c r="F132" s="148">
+      <c r="A132" s="147" t="n"/>
+      <c r="B132" s="148" t="n"/>
+      <c r="C132" s="148" t="n"/>
+      <c r="D132" s="148" t="n"/>
+      <c r="E132" s="149" t="n"/>
+      <c r="F132" s="150">
         <f>IFERROR(SUMIF($C$8:C132,"Income",$E$8:E132)-SUMIF($C$8:C132,"Expense",$E$8:E132)-SUMIF($C$8:C132,"Savings",$E$8:E132),"")</f>
         <v/>
       </c>
-      <c r="G132" s="149" t="n"/>
-      <c r="H132" s="146" t="n"/>
+      <c r="G132" s="151" t="n"/>
+      <c r="H132" s="147" t="n"/>
     </row>
     <row r="133" ht="18" customHeight="1">
-      <c r="A133" s="150" t="n"/>
-      <c r="B133" s="151" t="n"/>
-      <c r="C133" s="151" t="n"/>
-      <c r="D133" s="151" t="n"/>
-      <c r="E133" s="152" t="n"/>
-      <c r="F133" s="152">
+      <c r="A133" s="152" t="n"/>
+      <c r="B133" s="153" t="n"/>
+      <c r="C133" s="153" t="n"/>
+      <c r="D133" s="153" t="n"/>
+      <c r="E133" s="154" t="n"/>
+      <c r="F133" s="155">
         <f>IFERROR(SUMIF($C$8:C133,"Income",$E$8:E133)-SUMIF($C$8:C133,"Expense",$E$8:E133)-SUMIF($C$8:C133,"Savings",$E$8:E133),"")</f>
         <v/>
       </c>
-      <c r="G133" s="153" t="n"/>
-      <c r="H133" s="150" t="n"/>
+      <c r="G133" s="156" t="n"/>
+      <c r="H133" s="152" t="n"/>
     </row>
     <row r="134" ht="18" customHeight="1">
-      <c r="A134" s="146" t="n"/>
-      <c r="B134" s="147" t="n"/>
-      <c r="C134" s="147" t="n"/>
-      <c r="D134" s="147" t="n"/>
-      <c r="E134" s="148" t="n"/>
-      <c r="F134" s="148">
+      <c r="A134" s="147" t="n"/>
+      <c r="B134" s="148" t="n"/>
+      <c r="C134" s="148" t="n"/>
+      <c r="D134" s="148" t="n"/>
+      <c r="E134" s="149" t="n"/>
+      <c r="F134" s="150">
         <f>IFERROR(SUMIF($C$8:C134,"Income",$E$8:E134)-SUMIF($C$8:C134,"Expense",$E$8:E134)-SUMIF($C$8:C134,"Savings",$E$8:E134),"")</f>
         <v/>
       </c>
-      <c r="G134" s="149" t="n"/>
-      <c r="H134" s="146" t="n"/>
+      <c r="G134" s="151" t="n"/>
+      <c r="H134" s="147" t="n"/>
     </row>
     <row r="135" ht="18" customHeight="1">
-      <c r="A135" s="150" t="n"/>
-      <c r="B135" s="151" t="n"/>
-      <c r="C135" s="151" t="n"/>
-      <c r="D135" s="151" t="n"/>
-      <c r="E135" s="152" t="n"/>
-      <c r="F135" s="152">
+      <c r="A135" s="152" t="n"/>
+      <c r="B135" s="153" t="n"/>
+      <c r="C135" s="153" t="n"/>
+      <c r="D135" s="153" t="n"/>
+      <c r="E135" s="154" t="n"/>
+      <c r="F135" s="155">
         <f>IFERROR(SUMIF($C$8:C135,"Income",$E$8:E135)-SUMIF($C$8:C135,"Expense",$E$8:E135)-SUMIF($C$8:C135,"Savings",$E$8:E135),"")</f>
         <v/>
       </c>
-      <c r="G135" s="153" t="n"/>
-      <c r="H135" s="150" t="n"/>
+      <c r="G135" s="156" t="n"/>
+      <c r="H135" s="152" t="n"/>
     </row>
     <row r="136" ht="18" customHeight="1">
-      <c r="A136" s="146" t="n"/>
-      <c r="B136" s="147" t="n"/>
-      <c r="C136" s="147" t="n"/>
-      <c r="D136" s="147" t="n"/>
-      <c r="E136" s="148" t="n"/>
-      <c r="F136" s="148">
+      <c r="A136" s="147" t="n"/>
+      <c r="B136" s="148" t="n"/>
+      <c r="C136" s="148" t="n"/>
+      <c r="D136" s="148" t="n"/>
+      <c r="E136" s="149" t="n"/>
+      <c r="F136" s="150">
         <f>IFERROR(SUMIF($C$8:C136,"Income",$E$8:E136)-SUMIF($C$8:C136,"Expense",$E$8:E136)-SUMIF($C$8:C136,"Savings",$E$8:E136),"")</f>
         <v/>
       </c>
-      <c r="G136" s="149" t="n"/>
-      <c r="H136" s="146" t="n"/>
+      <c r="G136" s="151" t="n"/>
+      <c r="H136" s="147" t="n"/>
     </row>
     <row r="137" ht="18" customHeight="1">
-      <c r="A137" s="150" t="n"/>
-      <c r="B137" s="151" t="n"/>
-      <c r="C137" s="151" t="n"/>
-      <c r="D137" s="151" t="n"/>
-      <c r="E137" s="152" t="n"/>
-      <c r="F137" s="152">
+      <c r="A137" s="152" t="n"/>
+      <c r="B137" s="153" t="n"/>
+      <c r="C137" s="153" t="n"/>
+      <c r="D137" s="153" t="n"/>
+      <c r="E137" s="154" t="n"/>
+      <c r="F137" s="155">
         <f>IFERROR(SUMIF($C$8:C137,"Income",$E$8:E137)-SUMIF($C$8:C137,"Expense",$E$8:E137)-SUMIF($C$8:C137,"Savings",$E$8:E137),"")</f>
         <v/>
       </c>
-      <c r="G137" s="153" t="n"/>
-      <c r="H137" s="150" t="n"/>
+      <c r="G137" s="156" t="n"/>
+      <c r="H137" s="152" t="n"/>
     </row>
     <row r="138" ht="18" customHeight="1">
-      <c r="A138" s="146" t="n"/>
-      <c r="B138" s="147" t="n"/>
-      <c r="C138" s="147" t="n"/>
-      <c r="D138" s="147" t="n"/>
-      <c r="E138" s="148" t="n"/>
-      <c r="F138" s="148">
+      <c r="A138" s="147" t="n"/>
+      <c r="B138" s="148" t="n"/>
+      <c r="C138" s="148" t="n"/>
+      <c r="D138" s="148" t="n"/>
+      <c r="E138" s="149" t="n"/>
+      <c r="F138" s="150">
         <f>IFERROR(SUMIF($C$8:C138,"Income",$E$8:E138)-SUMIF($C$8:C138,"Expense",$E$8:E138)-SUMIF($C$8:C138,"Savings",$E$8:E138),"")</f>
         <v/>
       </c>
-      <c r="G138" s="149" t="n"/>
-      <c r="H138" s="146" t="n"/>
+      <c r="G138" s="151" t="n"/>
+      <c r="H138" s="147" t="n"/>
     </row>
     <row r="139" ht="18" customHeight="1">
-      <c r="A139" s="150" t="n"/>
-      <c r="B139" s="151" t="n"/>
-      <c r="C139" s="151" t="n"/>
-      <c r="D139" s="151" t="n"/>
-      <c r="E139" s="152" t="n"/>
-      <c r="F139" s="152">
+      <c r="A139" s="152" t="n"/>
+      <c r="B139" s="153" t="n"/>
+      <c r="C139" s="153" t="n"/>
+      <c r="D139" s="153" t="n"/>
+      <c r="E139" s="154" t="n"/>
+      <c r="F139" s="155">
         <f>IFERROR(SUMIF($C$8:C139,"Income",$E$8:E139)-SUMIF($C$8:C139,"Expense",$E$8:E139)-SUMIF($C$8:C139,"Savings",$E$8:E139),"")</f>
         <v/>
       </c>
-      <c r="G139" s="153" t="n"/>
-      <c r="H139" s="150" t="n"/>
+      <c r="G139" s="156" t="n"/>
+      <c r="H139" s="152" t="n"/>
     </row>
     <row r="140" ht="18" customHeight="1">
-      <c r="A140" s="146" t="n"/>
-      <c r="B140" s="147" t="n"/>
-      <c r="C140" s="147" t="n"/>
-      <c r="D140" s="147" t="n"/>
-      <c r="E140" s="148" t="n"/>
-      <c r="F140" s="148">
+      <c r="A140" s="147" t="n"/>
+      <c r="B140" s="148" t="n"/>
+      <c r="C140" s="148" t="n"/>
+      <c r="D140" s="148" t="n"/>
+      <c r="E140" s="149" t="n"/>
+      <c r="F140" s="150">
         <f>IFERROR(SUMIF($C$8:C140,"Income",$E$8:E140)-SUMIF($C$8:C140,"Expense",$E$8:E140)-SUMIF($C$8:C140,"Savings",$E$8:E140),"")</f>
         <v/>
       </c>
-      <c r="G140" s="149" t="n"/>
-      <c r="H140" s="146" t="n"/>
+      <c r="G140" s="151" t="n"/>
+      <c r="H140" s="147" t="n"/>
     </row>
     <row r="141" ht="18" customHeight="1">
-      <c r="A141" s="150" t="n"/>
-      <c r="B141" s="151" t="n"/>
-      <c r="C141" s="151" t="n"/>
-      <c r="D141" s="151" t="n"/>
-      <c r="E141" s="152" t="n"/>
-      <c r="F141" s="152">
+      <c r="A141" s="152" t="n"/>
+      <c r="B141" s="153" t="n"/>
+      <c r="C141" s="153" t="n"/>
+      <c r="D141" s="153" t="n"/>
+      <c r="E141" s="154" t="n"/>
+      <c r="F141" s="155">
         <f>IFERROR(SUMIF($C$8:C141,"Income",$E$8:E141)-SUMIF($C$8:C141,"Expense",$E$8:E141)-SUMIF($C$8:C141,"Savings",$E$8:E141),"")</f>
         <v/>
       </c>
-      <c r="G141" s="153" t="n"/>
-      <c r="H141" s="150" t="n"/>
+      <c r="G141" s="156" t="n"/>
+      <c r="H141" s="152" t="n"/>
     </row>
     <row r="142" ht="18" customHeight="1">
-      <c r="A142" s="146" t="n"/>
-      <c r="B142" s="147" t="n"/>
-      <c r="C142" s="147" t="n"/>
-      <c r="D142" s="147" t="n"/>
-      <c r="E142" s="148" t="n"/>
-      <c r="F142" s="148">
+      <c r="A142" s="147" t="n"/>
+      <c r="B142" s="148" t="n"/>
+      <c r="C142" s="148" t="n"/>
+      <c r="D142" s="148" t="n"/>
+      <c r="E142" s="149" t="n"/>
+      <c r="F142" s="150">
         <f>IFERROR(SUMIF($C$8:C142,"Income",$E$8:E142)-SUMIF($C$8:C142,"Expense",$E$8:E142)-SUMIF($C$8:C142,"Savings",$E$8:E142),"")</f>
         <v/>
       </c>
-      <c r="G142" s="149" t="n"/>
-      <c r="H142" s="146" t="n"/>
+      <c r="G142" s="151" t="n"/>
+      <c r="H142" s="147" t="n"/>
     </row>
     <row r="143" ht="18" customHeight="1">
-      <c r="A143" s="150" t="n"/>
-      <c r="B143" s="151" t="n"/>
-      <c r="C143" s="151" t="n"/>
-      <c r="D143" s="151" t="n"/>
-      <c r="E143" s="152" t="n"/>
-      <c r="F143" s="152">
+      <c r="A143" s="152" t="n"/>
+      <c r="B143" s="153" t="n"/>
+      <c r="C143" s="153" t="n"/>
+      <c r="D143" s="153" t="n"/>
+      <c r="E143" s="154" t="n"/>
+      <c r="F143" s="155">
         <f>IFERROR(SUMIF($C$8:C143,"Income",$E$8:E143)-SUMIF($C$8:C143,"Expense",$E$8:E143)-SUMIF($C$8:C143,"Savings",$E$8:E143),"")</f>
         <v/>
       </c>
-      <c r="G143" s="153" t="n"/>
-      <c r="H143" s="150" t="n"/>
+      <c r="G143" s="156" t="n"/>
+      <c r="H143" s="152" t="n"/>
     </row>
     <row r="144" ht="18" customHeight="1">
-      <c r="A144" s="146" t="n"/>
-      <c r="B144" s="147" t="n"/>
-      <c r="C144" s="147" t="n"/>
-      <c r="D144" s="147" t="n"/>
-      <c r="E144" s="148" t="n"/>
-      <c r="F144" s="148">
+      <c r="A144" s="147" t="n"/>
+      <c r="B144" s="148" t="n"/>
+      <c r="C144" s="148" t="n"/>
+      <c r="D144" s="148" t="n"/>
+      <c r="E144" s="149" t="n"/>
+      <c r="F144" s="150">
         <f>IFERROR(SUMIF($C$8:C144,"Income",$E$8:E144)-SUMIF($C$8:C144,"Expense",$E$8:E144)-SUMIF($C$8:C144,"Savings",$E$8:E144),"")</f>
         <v/>
       </c>
-      <c r="G144" s="149" t="n"/>
-      <c r="H144" s="146" t="n"/>
+      <c r="G144" s="151" t="n"/>
+      <c r="H144" s="147" t="n"/>
     </row>
     <row r="145" ht="18" customHeight="1">
-      <c r="A145" s="150" t="n"/>
-      <c r="B145" s="151" t="n"/>
-      <c r="C145" s="151" t="n"/>
-      <c r="D145" s="151" t="n"/>
-      <c r="E145" s="152" t="n"/>
-      <c r="F145" s="152">
+      <c r="A145" s="152" t="n"/>
+      <c r="B145" s="153" t="n"/>
+      <c r="C145" s="153" t="n"/>
+      <c r="D145" s="153" t="n"/>
+      <c r="E145" s="154" t="n"/>
+      <c r="F145" s="155">
         <f>IFERROR(SUMIF($C$8:C145,"Income",$E$8:E145)-SUMIF($C$8:C145,"Expense",$E$8:E145)-SUMIF($C$8:C145,"Savings",$E$8:E145),"")</f>
         <v/>
       </c>
-      <c r="G145" s="153" t="n"/>
-      <c r="H145" s="150" t="n"/>
+      <c r="G145" s="156" t="n"/>
+      <c r="H145" s="152" t="n"/>
     </row>
     <row r="146" ht="18" customHeight="1">
-      <c r="A146" s="146" t="n"/>
-      <c r="B146" s="147" t="n"/>
-      <c r="C146" s="147" t="n"/>
-      <c r="D146" s="147" t="n"/>
-      <c r="E146" s="148" t="n"/>
-      <c r="F146" s="148">
+      <c r="A146" s="147" t="n"/>
+      <c r="B146" s="148" t="n"/>
+      <c r="C146" s="148" t="n"/>
+      <c r="D146" s="148" t="n"/>
+      <c r="E146" s="149" t="n"/>
+      <c r="F146" s="150">
         <f>IFERROR(SUMIF($C$8:C146,"Income",$E$8:E146)-SUMIF($C$8:C146,"Expense",$E$8:E146)-SUMIF($C$8:C146,"Savings",$E$8:E146),"")</f>
         <v/>
       </c>
-      <c r="G146" s="149" t="n"/>
-      <c r="H146" s="146" t="n"/>
+      <c r="G146" s="151" t="n"/>
+      <c r="H146" s="147" t="n"/>
     </row>
     <row r="147" ht="18" customHeight="1">
-      <c r="A147" s="150" t="n"/>
-      <c r="B147" s="151" t="n"/>
-      <c r="C147" s="151" t="n"/>
-      <c r="D147" s="151" t="n"/>
-      <c r="E147" s="152" t="n"/>
-      <c r="F147" s="152">
+      <c r="A147" s="152" t="n"/>
+      <c r="B147" s="153" t="n"/>
+      <c r="C147" s="153" t="n"/>
+      <c r="D147" s="153" t="n"/>
+      <c r="E147" s="154" t="n"/>
+      <c r="F147" s="155">
         <f>IFERROR(SUMIF($C$8:C147,"Income",$E$8:E147)-SUMIF($C$8:C147,"Expense",$E$8:E147)-SUMIF($C$8:C147,"Savings",$E$8:E147),"")</f>
         <v/>
       </c>
-      <c r="G147" s="153" t="n"/>
-      <c r="H147" s="150" t="n"/>
+      <c r="G147" s="156" t="n"/>
+      <c r="H147" s="152" t="n"/>
     </row>
     <row r="148" ht="18" customHeight="1">
-      <c r="A148" s="146" t="n"/>
-      <c r="B148" s="147" t="n"/>
-      <c r="C148" s="147" t="n"/>
-      <c r="D148" s="147" t="n"/>
-      <c r="E148" s="148" t="n"/>
-      <c r="F148" s="148">
+      <c r="A148" s="147" t="n"/>
+      <c r="B148" s="148" t="n"/>
+      <c r="C148" s="148" t="n"/>
+      <c r="D148" s="148" t="n"/>
+      <c r="E148" s="149" t="n"/>
+      <c r="F148" s="150">
         <f>IFERROR(SUMIF($C$8:C148,"Income",$E$8:E148)-SUMIF($C$8:C148,"Expense",$E$8:E148)-SUMIF($C$8:C148,"Savings",$E$8:E148),"")</f>
         <v/>
       </c>
-      <c r="G148" s="149" t="n"/>
-      <c r="H148" s="146" t="n"/>
+      <c r="G148" s="151" t="n"/>
+      <c r="H148" s="147" t="n"/>
     </row>
     <row r="149" ht="18" customHeight="1">
-      <c r="A149" s="150" t="n"/>
-      <c r="B149" s="151" t="n"/>
-      <c r="C149" s="151" t="n"/>
-      <c r="D149" s="151" t="n"/>
-      <c r="E149" s="152" t="n"/>
-      <c r="F149" s="152">
+      <c r="A149" s="152" t="n"/>
+      <c r="B149" s="153" t="n"/>
+      <c r="C149" s="153" t="n"/>
+      <c r="D149" s="153" t="n"/>
+      <c r="E149" s="154" t="n"/>
+      <c r="F149" s="155">
         <f>IFERROR(SUMIF($C$8:C149,"Income",$E$8:E149)-SUMIF($C$8:C149,"Expense",$E$8:E149)-SUMIF($C$8:C149,"Savings",$E$8:E149),"")</f>
         <v/>
       </c>
-      <c r="G149" s="153" t="n"/>
-      <c r="H149" s="150" t="n"/>
+      <c r="G149" s="156" t="n"/>
+      <c r="H149" s="152" t="n"/>
     </row>
     <row r="150" ht="18" customHeight="1">
-      <c r="A150" s="146" t="n"/>
-      <c r="B150" s="147" t="n"/>
-      <c r="C150" s="147" t="n"/>
-      <c r="D150" s="147" t="n"/>
-      <c r="E150" s="148" t="n"/>
-      <c r="F150" s="148">
+      <c r="A150" s="147" t="n"/>
+      <c r="B150" s="148" t="n"/>
+      <c r="C150" s="148" t="n"/>
+      <c r="D150" s="148" t="n"/>
+      <c r="E150" s="149" t="n"/>
+      <c r="F150" s="150">
         <f>IFERROR(SUMIF($C$8:C150,"Income",$E$8:E150)-SUMIF($C$8:C150,"Expense",$E$8:E150)-SUMIF($C$8:C150,"Savings",$E$8:E150),"")</f>
         <v/>
       </c>
-      <c r="G150" s="149" t="n"/>
-      <c r="H150" s="146" t="n"/>
+      <c r="G150" s="151" t="n"/>
+      <c r="H150" s="147" t="n"/>
     </row>
     <row r="151" ht="18" customHeight="1">
-      <c r="A151" s="150" t="n"/>
-      <c r="B151" s="151" t="n"/>
-      <c r="C151" s="151" t="n"/>
-      <c r="D151" s="151" t="n"/>
-      <c r="E151" s="152" t="n"/>
-      <c r="F151" s="152">
+      <c r="A151" s="152" t="n"/>
+      <c r="B151" s="153" t="n"/>
+      <c r="C151" s="153" t="n"/>
+      <c r="D151" s="153" t="n"/>
+      <c r="E151" s="154" t="n"/>
+      <c r="F151" s="155">
         <f>IFERROR(SUMIF($C$8:C151,"Income",$E$8:E151)-SUMIF($C$8:C151,"Expense",$E$8:E151)-SUMIF($C$8:C151,"Savings",$E$8:E151),"")</f>
         <v/>
       </c>
-      <c r="G151" s="153" t="n"/>
-      <c r="H151" s="150" t="n"/>
+      <c r="G151" s="156" t="n"/>
+      <c r="H151" s="152" t="n"/>
     </row>
     <row r="152" ht="18" customHeight="1">
-      <c r="A152" s="146" t="n"/>
-      <c r="B152" s="147" t="n"/>
-      <c r="C152" s="147" t="n"/>
-      <c r="D152" s="147" t="n"/>
-      <c r="E152" s="148" t="n"/>
-      <c r="F152" s="148">
+      <c r="A152" s="147" t="n"/>
+      <c r="B152" s="148" t="n"/>
+      <c r="C152" s="148" t="n"/>
+      <c r="D152" s="148" t="n"/>
+      <c r="E152" s="149" t="n"/>
+      <c r="F152" s="150">
         <f>IFERROR(SUMIF($C$8:C152,"Income",$E$8:E152)-SUMIF($C$8:C152,"Expense",$E$8:E152)-SUMIF($C$8:C152,"Savings",$E$8:E152),"")</f>
         <v/>
       </c>
-      <c r="G152" s="149" t="n"/>
-      <c r="H152" s="146" t="n"/>
+      <c r="G152" s="151" t="n"/>
+      <c r="H152" s="147" t="n"/>
     </row>
     <row r="153" ht="18" customHeight="1">
-      <c r="A153" s="150" t="n"/>
-      <c r="B153" s="151" t="n"/>
-      <c r="C153" s="151" t="n"/>
-      <c r="D153" s="151" t="n"/>
-      <c r="E153" s="152" t="n"/>
-      <c r="F153" s="152">
+      <c r="A153" s="152" t="n"/>
+      <c r="B153" s="153" t="n"/>
+      <c r="C153" s="153" t="n"/>
+      <c r="D153" s="153" t="n"/>
+      <c r="E153" s="154" t="n"/>
+      <c r="F153" s="155">
         <f>IFERROR(SUMIF($C$8:C153,"Income",$E$8:E153)-SUMIF($C$8:C153,"Expense",$E$8:E153)-SUMIF($C$8:C153,"Savings",$E$8:E153),"")</f>
         <v/>
       </c>
-      <c r="G153" s="153" t="n"/>
-      <c r="H153" s="150" t="n"/>
+      <c r="G153" s="156" t="n"/>
+      <c r="H153" s="152" t="n"/>
     </row>
     <row r="154" ht="18" customHeight="1">
-      <c r="A154" s="146" t="n"/>
-      <c r="B154" s="147" t="n"/>
-      <c r="C154" s="147" t="n"/>
-      <c r="D154" s="147" t="n"/>
-      <c r="E154" s="148" t="n"/>
-      <c r="F154" s="148">
+      <c r="A154" s="147" t="n"/>
+      <c r="B154" s="148" t="n"/>
+      <c r="C154" s="148" t="n"/>
+      <c r="D154" s="148" t="n"/>
+      <c r="E154" s="149" t="n"/>
+      <c r="F154" s="150">
         <f>IFERROR(SUMIF($C$8:C154,"Income",$E$8:E154)-SUMIF($C$8:C154,"Expense",$E$8:E154)-SUMIF($C$8:C154,"Savings",$E$8:E154),"")</f>
         <v/>
       </c>
-      <c r="G154" s="149" t="n"/>
-      <c r="H154" s="146" t="n"/>
+      <c r="G154" s="151" t="n"/>
+      <c r="H154" s="147" t="n"/>
     </row>
     <row r="155" ht="18" customHeight="1">
-      <c r="A155" s="150" t="n"/>
-      <c r="B155" s="151" t="n"/>
-      <c r="C155" s="151" t="n"/>
-      <c r="D155" s="151" t="n"/>
-      <c r="E155" s="152" t="n"/>
-      <c r="F155" s="152">
+      <c r="A155" s="152" t="n"/>
+      <c r="B155" s="153" t="n"/>
+      <c r="C155" s="153" t="n"/>
+      <c r="D155" s="153" t="n"/>
+      <c r="E155" s="154" t="n"/>
+      <c r="F155" s="155">
         <f>IFERROR(SUMIF($C$8:C155,"Income",$E$8:E155)-SUMIF($C$8:C155,"Expense",$E$8:E155)-SUMIF($C$8:C155,"Savings",$E$8:E155),"")</f>
         <v/>
       </c>
-      <c r="G155" s="153" t="n"/>
-      <c r="H155" s="150" t="n"/>
+      <c r="G155" s="156" t="n"/>
+      <c r="H155" s="152" t="n"/>
     </row>
     <row r="156" ht="18" customHeight="1">
-      <c r="A156" s="146" t="n"/>
-      <c r="B156" s="147" t="n"/>
-      <c r="C156" s="147" t="n"/>
-      <c r="D156" s="147" t="n"/>
-      <c r="E156" s="148" t="n"/>
-      <c r="F156" s="148">
+      <c r="A156" s="147" t="n"/>
+      <c r="B156" s="148" t="n"/>
+      <c r="C156" s="148" t="n"/>
+      <c r="D156" s="148" t="n"/>
+      <c r="E156" s="149" t="n"/>
+      <c r="F156" s="150">
         <f>IFERROR(SUMIF($C$8:C156,"Income",$E$8:E156)-SUMIF($C$8:C156,"Expense",$E$8:E156)-SUMIF($C$8:C156,"Savings",$E$8:E156),"")</f>
         <v/>
       </c>
-      <c r="G156" s="149" t="n"/>
-      <c r="H156" s="146" t="n"/>
+      <c r="G156" s="151" t="n"/>
+      <c r="H156" s="147" t="n"/>
     </row>
     <row r="157" ht="18" customHeight="1">
-      <c r="A157" s="150" t="n"/>
-      <c r="B157" s="151" t="n"/>
-      <c r="C157" s="151" t="n"/>
-      <c r="D157" s="151" t="n"/>
-      <c r="E157" s="152" t="n"/>
-      <c r="F157" s="152">
+      <c r="A157" s="152" t="n"/>
+      <c r="B157" s="153" t="n"/>
+      <c r="C157" s="153" t="n"/>
+      <c r="D157" s="153" t="n"/>
+      <c r="E157" s="154" t="n"/>
+      <c r="F157" s="155">
         <f>IFERROR(SUMIF($C$8:C157,"Income",$E$8:E157)-SUMIF($C$8:C157,"Expense",$E$8:E157)-SUMIF($C$8:C157,"Savings",$E$8:E157),"")</f>
         <v/>
       </c>
-      <c r="G157" s="153" t="n"/>
-      <c r="H157" s="150" t="n"/>
+      <c r="G157" s="156" t="n"/>
+      <c r="H157" s="152" t="n"/>
     </row>
     <row r="158" ht="18" customHeight="1">
-      <c r="A158" s="146" t="n"/>
-      <c r="B158" s="147" t="n"/>
-      <c r="C158" s="147" t="n"/>
-      <c r="D158" s="147" t="n"/>
-      <c r="E158" s="148" t="n"/>
-      <c r="F158" s="148">
+      <c r="A158" s="147" t="n"/>
+      <c r="B158" s="148" t="n"/>
+      <c r="C158" s="148" t="n"/>
+      <c r="D158" s="148" t="n"/>
+      <c r="E158" s="149" t="n"/>
+      <c r="F158" s="150">
         <f>IFERROR(SUMIF($C$8:C158,"Income",$E$8:E158)-SUMIF($C$8:C158,"Expense",$E$8:E158)-SUMIF($C$8:C158,"Savings",$E$8:E158),"")</f>
         <v/>
       </c>
-      <c r="G158" s="149" t="n"/>
-      <c r="H158" s="146" t="n"/>
+      <c r="G158" s="151" t="n"/>
+      <c r="H158" s="147" t="n"/>
     </row>
     <row r="159" ht="18" customHeight="1">
-      <c r="A159" s="150" t="n"/>
-      <c r="B159" s="151" t="n"/>
-      <c r="C159" s="151" t="n"/>
-      <c r="D159" s="151" t="n"/>
-      <c r="E159" s="152" t="n"/>
-      <c r="F159" s="152">
+      <c r="A159" s="152" t="n"/>
+      <c r="B159" s="153" t="n"/>
+      <c r="C159" s="153" t="n"/>
+      <c r="D159" s="153" t="n"/>
+      <c r="E159" s="154" t="n"/>
+      <c r="F159" s="155">
         <f>IFERROR(SUMIF($C$8:C159,"Income",$E$8:E159)-SUMIF($C$8:C159,"Expense",$E$8:E159)-SUMIF($C$8:C159,"Savings",$E$8:E159),"")</f>
         <v/>
       </c>
-      <c r="G159" s="153" t="n"/>
-      <c r="H159" s="150" t="n"/>
+      <c r="G159" s="156" t="n"/>
+      <c r="H159" s="152" t="n"/>
     </row>
     <row r="160" ht="18" customHeight="1">
-      <c r="A160" s="146" t="n"/>
-      <c r="B160" s="147" t="n"/>
-      <c r="C160" s="147" t="n"/>
-      <c r="D160" s="147" t="n"/>
-      <c r="E160" s="148" t="n"/>
-      <c r="F160" s="148">
+      <c r="A160" s="147" t="n"/>
+      <c r="B160" s="148" t="n"/>
+      <c r="C160" s="148" t="n"/>
+      <c r="D160" s="148" t="n"/>
+      <c r="E160" s="149" t="n"/>
+      <c r="F160" s="150">
         <f>IFERROR(SUMIF($C$8:C160,"Income",$E$8:E160)-SUMIF($C$8:C160,"Expense",$E$8:E160)-SUMIF($C$8:C160,"Savings",$E$8:E160),"")</f>
         <v/>
       </c>
-      <c r="G160" s="149" t="n"/>
-      <c r="H160" s="146" t="n"/>
+      <c r="G160" s="151" t="n"/>
+      <c r="H160" s="147" t="n"/>
     </row>
     <row r="161" ht="18" customHeight="1">
-      <c r="A161" s="150" t="n"/>
-      <c r="B161" s="151" t="n"/>
-      <c r="C161" s="151" t="n"/>
-      <c r="D161" s="151" t="n"/>
-      <c r="E161" s="152" t="n"/>
-      <c r="F161" s="152">
+      <c r="A161" s="152" t="n"/>
+      <c r="B161" s="153" t="n"/>
+      <c r="C161" s="153" t="n"/>
+      <c r="D161" s="153" t="n"/>
+      <c r="E161" s="154" t="n"/>
+      <c r="F161" s="155">
         <f>IFERROR(SUMIF($C$8:C161,"Income",$E$8:E161)-SUMIF($C$8:C161,"Expense",$E$8:E161)-SUMIF($C$8:C161,"Savings",$E$8:E161),"")</f>
         <v/>
       </c>
-      <c r="G161" s="153" t="n"/>
-      <c r="H161" s="150" t="n"/>
+      <c r="G161" s="156" t="n"/>
+      <c r="H161" s="152" t="n"/>
     </row>
     <row r="162" ht="18" customHeight="1">
-      <c r="A162" s="146" t="n"/>
-      <c r="B162" s="147" t="n"/>
-      <c r="C162" s="147" t="n"/>
-      <c r="D162" s="147" t="n"/>
-      <c r="E162" s="148" t="n"/>
-      <c r="F162" s="148">
+      <c r="A162" s="147" t="n"/>
+      <c r="B162" s="148" t="n"/>
+      <c r="C162" s="148" t="n"/>
+      <c r="D162" s="148" t="n"/>
+      <c r="E162" s="149" t="n"/>
+      <c r="F162" s="150">
         <f>IFERROR(SUMIF($C$8:C162,"Income",$E$8:E162)-SUMIF($C$8:C162,"Expense",$E$8:E162)-SUMIF($C$8:C162,"Savings",$E$8:E162),"")</f>
         <v/>
       </c>
-      <c r="G162" s="149" t="n"/>
-      <c r="H162" s="146" t="n"/>
+      <c r="G162" s="151" t="n"/>
+      <c r="H162" s="147" t="n"/>
     </row>
     <row r="163" ht="18" customHeight="1">
-      <c r="A163" s="150" t="n"/>
-      <c r="B163" s="151" t="n"/>
-      <c r="C163" s="151" t="n"/>
-      <c r="D163" s="151" t="n"/>
-      <c r="E163" s="152" t="n"/>
-      <c r="F163" s="152">
+      <c r="A163" s="152" t="n"/>
+      <c r="B163" s="153" t="n"/>
+      <c r="C163" s="153" t="n"/>
+      <c r="D163" s="153" t="n"/>
+      <c r="E163" s="154" t="n"/>
+      <c r="F163" s="155">
         <f>IFERROR(SUMIF($C$8:C163,"Income",$E$8:E163)-SUMIF($C$8:C163,"Expense",$E$8:E163)-SUMIF($C$8:C163,"Savings",$E$8:E163),"")</f>
         <v/>
       </c>
-      <c r="G163" s="153" t="n"/>
-      <c r="H163" s="150" t="n"/>
+      <c r="G163" s="156" t="n"/>
+      <c r="H163" s="152" t="n"/>
     </row>
     <row r="164" ht="18" customHeight="1">
-      <c r="A164" s="146" t="n"/>
-      <c r="B164" s="147" t="n"/>
-      <c r="C164" s="147" t="n"/>
-      <c r="D164" s="147" t="n"/>
-      <c r="E164" s="148" t="n"/>
-      <c r="F164" s="148">
+      <c r="A164" s="147" t="n"/>
+      <c r="B164" s="148" t="n"/>
+      <c r="C164" s="148" t="n"/>
+      <c r="D164" s="148" t="n"/>
+      <c r="E164" s="149" t="n"/>
+      <c r="F164" s="150">
         <f>IFERROR(SUMIF($C$8:C164,"Income",$E$8:E164)-SUMIF($C$8:C164,"Expense",$E$8:E164)-SUMIF($C$8:C164,"Savings",$E$8:E164),"")</f>
         <v/>
       </c>
-      <c r="G164" s="149" t="n"/>
-      <c r="H164" s="146" t="n"/>
+      <c r="G164" s="151" t="n"/>
+      <c r="H164" s="147" t="n"/>
     </row>
     <row r="165" ht="18" customHeight="1">
-      <c r="A165" s="150" t="n"/>
-      <c r="B165" s="151" t="n"/>
-      <c r="C165" s="151" t="n"/>
-      <c r="D165" s="151" t="n"/>
-      <c r="E165" s="152" t="n"/>
-      <c r="F165" s="152">
+      <c r="A165" s="152" t="n"/>
+      <c r="B165" s="153" t="n"/>
+      <c r="C165" s="153" t="n"/>
+      <c r="D165" s="153" t="n"/>
+      <c r="E165" s="154" t="n"/>
+      <c r="F165" s="155">
         <f>IFERROR(SUMIF($C$8:C165,"Income",$E$8:E165)-SUMIF($C$8:C165,"Expense",$E$8:E165)-SUMIF($C$8:C165,"Savings",$E$8:E165),"")</f>
         <v/>
       </c>
-      <c r="G165" s="153" t="n"/>
-      <c r="H165" s="150" t="n"/>
+      <c r="G165" s="156" t="n"/>
+      <c r="H165" s="152" t="n"/>
     </row>
     <row r="166" ht="18" customHeight="1">
-      <c r="A166" s="146" t="n"/>
-      <c r="B166" s="147" t="n"/>
-      <c r="C166" s="147" t="n"/>
-      <c r="D166" s="147" t="n"/>
-      <c r="E166" s="148" t="n"/>
-      <c r="F166" s="148">
+      <c r="A166" s="147" t="n"/>
+      <c r="B166" s="148" t="n"/>
+      <c r="C166" s="148" t="n"/>
+      <c r="D166" s="148" t="n"/>
+      <c r="E166" s="149" t="n"/>
+      <c r="F166" s="150">
         <f>IFERROR(SUMIF($C$8:C166,"Income",$E$8:E166)-SUMIF($C$8:C166,"Expense",$E$8:E166)-SUMIF($C$8:C166,"Savings",$E$8:E166),"")</f>
         <v/>
       </c>
-      <c r="G166" s="149" t="n"/>
-      <c r="H166" s="146" t="n"/>
+      <c r="G166" s="151" t="n"/>
+      <c r="H166" s="147" t="n"/>
     </row>
     <row r="167" ht="18" customHeight="1">
-      <c r="A167" s="150" t="n"/>
-      <c r="B167" s="151" t="n"/>
-      <c r="C167" s="151" t="n"/>
-      <c r="D167" s="151" t="n"/>
-      <c r="E167" s="152" t="n"/>
-      <c r="F167" s="152">
+      <c r="A167" s="152" t="n"/>
+      <c r="B167" s="153" t="n"/>
+      <c r="C167" s="153" t="n"/>
+      <c r="D167" s="153" t="n"/>
+      <c r="E167" s="154" t="n"/>
+      <c r="F167" s="155">
         <f>IFERROR(SUMIF($C$8:C167,"Income",$E$8:E167)-SUMIF($C$8:C167,"Expense",$E$8:E167)-SUMIF($C$8:C167,"Savings",$E$8:E167),"")</f>
         <v/>
       </c>
-      <c r="G167" s="153" t="n"/>
-      <c r="H167" s="150" t="n"/>
+      <c r="G167" s="156" t="n"/>
+      <c r="H167" s="152" t="n"/>
     </row>
     <row r="168" ht="18" customHeight="1">
-      <c r="A168" s="146" t="n"/>
-      <c r="B168" s="147" t="n"/>
-      <c r="C168" s="147" t="n"/>
-      <c r="D168" s="147" t="n"/>
-      <c r="E168" s="148" t="n"/>
-      <c r="F168" s="148">
+      <c r="A168" s="147" t="n"/>
+      <c r="B168" s="148" t="n"/>
+      <c r="C168" s="148" t="n"/>
+      <c r="D168" s="148" t="n"/>
+      <c r="E168" s="149" t="n"/>
+      <c r="F168" s="150">
         <f>IFERROR(SUMIF($C$8:C168,"Income",$E$8:E168)-SUMIF($C$8:C168,"Expense",$E$8:E168)-SUMIF($C$8:C168,"Savings",$E$8:E168),"")</f>
         <v/>
       </c>
-      <c r="G168" s="149" t="n"/>
-      <c r="H168" s="146" t="n"/>
+      <c r="G168" s="151" t="n"/>
+      <c r="H168" s="147" t="n"/>
     </row>
     <row r="169" ht="18" customHeight="1">
-      <c r="A169" s="150" t="n"/>
-      <c r="B169" s="151" t="n"/>
-      <c r="C169" s="151" t="n"/>
-      <c r="D169" s="151" t="n"/>
-      <c r="E169" s="152" t="n"/>
-      <c r="F169" s="152">
+      <c r="A169" s="152" t="n"/>
+      <c r="B169" s="153" t="n"/>
+      <c r="C169" s="153" t="n"/>
+      <c r="D169" s="153" t="n"/>
+      <c r="E169" s="154" t="n"/>
+      <c r="F169" s="155">
         <f>IFERROR(SUMIF($C$8:C169,"Income",$E$8:E169)-SUMIF($C$8:C169,"Expense",$E$8:E169)-SUMIF($C$8:C169,"Savings",$E$8:E169),"")</f>
         <v/>
       </c>
-      <c r="G169" s="153" t="n"/>
-      <c r="H169" s="150" t="n"/>
+      <c r="G169" s="156" t="n"/>
+      <c r="H169" s="152" t="n"/>
     </row>
     <row r="170" ht="18" customHeight="1">
-      <c r="A170" s="146" t="n"/>
-      <c r="B170" s="147" t="n"/>
-      <c r="C170" s="147" t="n"/>
-      <c r="D170" s="147" t="n"/>
-      <c r="E170" s="148" t="n"/>
-      <c r="F170" s="148">
+      <c r="A170" s="147" t="n"/>
+      <c r="B170" s="148" t="n"/>
+      <c r="C170" s="148" t="n"/>
+      <c r="D170" s="148" t="n"/>
+      <c r="E170" s="149" t="n"/>
+      <c r="F170" s="150">
         <f>IFERROR(SUMIF($C$8:C170,"Income",$E$8:E170)-SUMIF($C$8:C170,"Expense",$E$8:E170)-SUMIF($C$8:C170,"Savings",$E$8:E170),"")</f>
         <v/>
       </c>
-      <c r="G170" s="149" t="n"/>
-      <c r="H170" s="146" t="n"/>
+      <c r="G170" s="151" t="n"/>
+      <c r="H170" s="147" t="n"/>
     </row>
     <row r="171" ht="18" customHeight="1">
-      <c r="A171" s="150" t="n"/>
-      <c r="B171" s="151" t="n"/>
-      <c r="C171" s="151" t="n"/>
-      <c r="D171" s="151" t="n"/>
-      <c r="E171" s="152" t="n"/>
-      <c r="F171" s="152">
+      <c r="A171" s="152" t="n"/>
+      <c r="B171" s="153" t="n"/>
+      <c r="C171" s="153" t="n"/>
+      <c r="D171" s="153" t="n"/>
+      <c r="E171" s="154" t="n"/>
+      <c r="F171" s="155">
         <f>IFERROR(SUMIF($C$8:C171,"Income",$E$8:E171)-SUMIF($C$8:C171,"Expense",$E$8:E171)-SUMIF($C$8:C171,"Savings",$E$8:E171),"")</f>
         <v/>
       </c>
-      <c r="G171" s="153" t="n"/>
-      <c r="H171" s="150" t="n"/>
+      <c r="G171" s="156" t="n"/>
+      <c r="H171" s="152" t="n"/>
     </row>
     <row r="172" ht="18" customHeight="1">
-      <c r="A172" s="146" t="n"/>
-      <c r="B172" s="147" t="n"/>
-      <c r="C172" s="147" t="n"/>
-      <c r="D172" s="147" t="n"/>
-      <c r="E172" s="148" t="n"/>
-      <c r="F172" s="148">
+      <c r="A172" s="147" t="n"/>
+      <c r="B172" s="148" t="n"/>
+      <c r="C172" s="148" t="n"/>
+      <c r="D172" s="148" t="n"/>
+      <c r="E172" s="149" t="n"/>
+      <c r="F172" s="150">
         <f>IFERROR(SUMIF($C$8:C172,"Income",$E$8:E172)-SUMIF($C$8:C172,"Expense",$E$8:E172)-SUMIF($C$8:C172,"Savings",$E$8:E172),"")</f>
         <v/>
       </c>
-      <c r="G172" s="149" t="n"/>
-      <c r="H172" s="146" t="n"/>
+      <c r="G172" s="151" t="n"/>
+      <c r="H172" s="147" t="n"/>
     </row>
     <row r="173" ht="18" customHeight="1">
-      <c r="A173" s="150" t="n"/>
-      <c r="B173" s="151" t="n"/>
-      <c r="C173" s="151" t="n"/>
-      <c r="D173" s="151" t="n"/>
-      <c r="E173" s="152" t="n"/>
-      <c r="F173" s="152">
+      <c r="A173" s="152" t="n"/>
+      <c r="B173" s="153" t="n"/>
+      <c r="C173" s="153" t="n"/>
+      <c r="D173" s="153" t="n"/>
+      <c r="E173" s="154" t="n"/>
+      <c r="F173" s="155">
         <f>IFERROR(SUMIF($C$8:C173,"Income",$E$8:E173)-SUMIF($C$8:C173,"Expense",$E$8:E173)-SUMIF($C$8:C173,"Savings",$E$8:E173),"")</f>
         <v/>
       </c>
-      <c r="G173" s="153" t="n"/>
-      <c r="H173" s="150" t="n"/>
+      <c r="G173" s="156" t="n"/>
+      <c r="H173" s="152" t="n"/>
     </row>
     <row r="174" ht="18" customHeight="1">
-      <c r="A174" s="146" t="n"/>
-      <c r="B174" s="147" t="n"/>
-      <c r="C174" s="147" t="n"/>
-      <c r="D174" s="147" t="n"/>
-      <c r="E174" s="148" t="n"/>
-      <c r="F174" s="148">
+      <c r="A174" s="147" t="n"/>
+      <c r="B174" s="148" t="n"/>
+      <c r="C174" s="148" t="n"/>
+      <c r="D174" s="148" t="n"/>
+      <c r="E174" s="149" t="n"/>
+      <c r="F174" s="150">
         <f>IFERROR(SUMIF($C$8:C174,"Income",$E$8:E174)-SUMIF($C$8:C174,"Expense",$E$8:E174)-SUMIF($C$8:C174,"Savings",$E$8:E174),"")</f>
         <v/>
       </c>
-      <c r="G174" s="149" t="n"/>
-      <c r="H174" s="146" t="n"/>
+      <c r="G174" s="151" t="n"/>
+      <c r="H174" s="147" t="n"/>
     </row>
     <row r="175" ht="18" customHeight="1">
-      <c r="A175" s="150" t="n"/>
-      <c r="B175" s="151" t="n"/>
-      <c r="C175" s="151" t="n"/>
-      <c r="D175" s="151" t="n"/>
-      <c r="E175" s="152" t="n"/>
-      <c r="F175" s="152">
+      <c r="A175" s="152" t="n"/>
+      <c r="B175" s="153" t="n"/>
+      <c r="C175" s="153" t="n"/>
+      <c r="D175" s="153" t="n"/>
+      <c r="E175" s="154" t="n"/>
+      <c r="F175" s="155">
         <f>IFERROR(SUMIF($C$8:C175,"Income",$E$8:E175)-SUMIF($C$8:C175,"Expense",$E$8:E175)-SUMIF($C$8:C175,"Savings",$E$8:E175),"")</f>
         <v/>
       </c>
-      <c r="G175" s="153" t="n"/>
-      <c r="H175" s="150" t="n"/>
+      <c r="G175" s="156" t="n"/>
+      <c r="H175" s="152" t="n"/>
     </row>
     <row r="176" ht="18" customHeight="1">
-      <c r="A176" s="146" t="n"/>
-      <c r="B176" s="147" t="n"/>
-      <c r="C176" s="147" t="n"/>
-      <c r="D176" s="147" t="n"/>
-      <c r="E176" s="148" t="n"/>
-      <c r="F176" s="148">
+      <c r="A176" s="147" t="n"/>
+      <c r="B176" s="148" t="n"/>
+      <c r="C176" s="148" t="n"/>
+      <c r="D176" s="148" t="n"/>
+      <c r="E176" s="149" t="n"/>
+      <c r="F176" s="150">
         <f>IFERROR(SUMIF($C$8:C176,"Income",$E$8:E176)-SUMIF($C$8:C176,"Expense",$E$8:E176)-SUMIF($C$8:C176,"Savings",$E$8:E176),"")</f>
         <v/>
       </c>
-      <c r="G176" s="149" t="n"/>
-      <c r="H176" s="146" t="n"/>
+      <c r="G176" s="151" t="n"/>
+      <c r="H176" s="147" t="n"/>
     </row>
     <row r="177" ht="18" customHeight="1">
-      <c r="A177" s="150" t="n"/>
-      <c r="B177" s="151" t="n"/>
-      <c r="C177" s="151" t="n"/>
-      <c r="D177" s="151" t="n"/>
-      <c r="E177" s="152" t="n"/>
-      <c r="F177" s="152">
+      <c r="A177" s="152" t="n"/>
+      <c r="B177" s="153" t="n"/>
+      <c r="C177" s="153" t="n"/>
+      <c r="D177" s="153" t="n"/>
+      <c r="E177" s="154" t="n"/>
+      <c r="F177" s="155">
         <f>IFERROR(SUMIF($C$8:C177,"Income",$E$8:E177)-SUMIF($C$8:C177,"Expense",$E$8:E177)-SUMIF($C$8:C177,"Savings",$E$8:E177),"")</f>
         <v/>
       </c>
-      <c r="G177" s="153" t="n"/>
-      <c r="H177" s="150" t="n"/>
+      <c r="G177" s="156" t="n"/>
+      <c r="H177" s="152" t="n"/>
     </row>
     <row r="178" ht="18" customHeight="1">
-      <c r="A178" s="146" t="n"/>
-      <c r="B178" s="147" t="n"/>
-      <c r="C178" s="147" t="n"/>
-      <c r="D178" s="147" t="n"/>
-      <c r="E178" s="148" t="n"/>
-      <c r="F178" s="148">
+      <c r="A178" s="147" t="n"/>
+      <c r="B178" s="148" t="n"/>
+      <c r="C178" s="148" t="n"/>
+      <c r="D178" s="148" t="n"/>
+      <c r="E178" s="149" t="n"/>
+      <c r="F178" s="150">
         <f>IFERROR(SUMIF($C$8:C178,"Income",$E$8:E178)-SUMIF($C$8:C178,"Expense",$E$8:E178)-SUMIF($C$8:C178,"Savings",$E$8:E178),"")</f>
         <v/>
       </c>
-      <c r="G178" s="149" t="n"/>
-      <c r="H178" s="146" t="n"/>
+      <c r="G178" s="151" t="n"/>
+      <c r="H178" s="147" t="n"/>
     </row>
     <row r="179" ht="18" customHeight="1">
-      <c r="A179" s="150" t="n"/>
-      <c r="B179" s="151" t="n"/>
-      <c r="C179" s="151" t="n"/>
-      <c r="D179" s="151" t="n"/>
-      <c r="E179" s="152" t="n"/>
-      <c r="F179" s="152">
+      <c r="A179" s="152" t="n"/>
+      <c r="B179" s="153" t="n"/>
+      <c r="C179" s="153" t="n"/>
+      <c r="D179" s="153" t="n"/>
+      <c r="E179" s="154" t="n"/>
+      <c r="F179" s="155">
         <f>IFERROR(SUMIF($C$8:C179,"Income",$E$8:E179)-SUMIF($C$8:C179,"Expense",$E$8:E179)-SUMIF($C$8:C179,"Savings",$E$8:E179),"")</f>
         <v/>
       </c>
-      <c r="G179" s="153" t="n"/>
-      <c r="H179" s="150" t="n"/>
+      <c r="G179" s="156" t="n"/>
+      <c r="H179" s="152" t="n"/>
     </row>
     <row r="180" ht="18" customHeight="1">
-      <c r="A180" s="146" t="n"/>
-      <c r="B180" s="147" t="n"/>
-      <c r="C180" s="147" t="n"/>
-      <c r="D180" s="147" t="n"/>
-      <c r="E180" s="148" t="n"/>
-      <c r="F180" s="148">
+      <c r="A180" s="147" t="n"/>
+      <c r="B180" s="148" t="n"/>
+      <c r="C180" s="148" t="n"/>
+      <c r="D180" s="148" t="n"/>
+      <c r="E180" s="149" t="n"/>
+      <c r="F180" s="150">
         <f>IFERROR(SUMIF($C$8:C180,"Income",$E$8:E180)-SUMIF($C$8:C180,"Expense",$E$8:E180)-SUMIF($C$8:C180,"Savings",$E$8:E180),"")</f>
         <v/>
       </c>
-      <c r="G180" s="149" t="n"/>
-      <c r="H180" s="146" t="n"/>
+      <c r="G180" s="151" t="n"/>
+      <c r="H180" s="147" t="n"/>
     </row>
     <row r="181" ht="18" customHeight="1">
-      <c r="A181" s="150" t="n"/>
-      <c r="B181" s="151" t="n"/>
-      <c r="C181" s="151" t="n"/>
-      <c r="D181" s="151" t="n"/>
-      <c r="E181" s="152" t="n"/>
-      <c r="F181" s="152">
+      <c r="A181" s="152" t="n"/>
+      <c r="B181" s="153" t="n"/>
+      <c r="C181" s="153" t="n"/>
+      <c r="D181" s="153" t="n"/>
+      <c r="E181" s="154" t="n"/>
+      <c r="F181" s="155">
         <f>IFERROR(SUMIF($C$8:C181,"Income",$E$8:E181)-SUMIF($C$8:C181,"Expense",$E$8:E181)-SUMIF($C$8:C181,"Savings",$E$8:E181),"")</f>
         <v/>
       </c>
-      <c r="G181" s="153" t="n"/>
-      <c r="H181" s="150" t="n"/>
+      <c r="G181" s="156" t="n"/>
+      <c r="H181" s="152" t="n"/>
     </row>
     <row r="182" ht="18" customHeight="1">
-      <c r="A182" s="146" t="n"/>
-      <c r="B182" s="147" t="n"/>
-      <c r="C182" s="147" t="n"/>
-      <c r="D182" s="147" t="n"/>
-      <c r="E182" s="148" t="n"/>
-      <c r="F182" s="148">
+      <c r="A182" s="147" t="n"/>
+      <c r="B182" s="148" t="n"/>
+      <c r="C182" s="148" t="n"/>
+      <c r="D182" s="148" t="n"/>
+      <c r="E182" s="149" t="n"/>
+      <c r="F182" s="150">
         <f>IFERROR(SUMIF($C$8:C182,"Income",$E$8:E182)-SUMIF($C$8:C182,"Expense",$E$8:E182)-SUMIF($C$8:C182,"Savings",$E$8:E182),"")</f>
         <v/>
       </c>
-      <c r="G182" s="149" t="n"/>
-      <c r="H182" s="146" t="n"/>
+      <c r="G182" s="151" t="n"/>
+      <c r="H182" s="147" t="n"/>
     </row>
     <row r="183" ht="18" customHeight="1">
-      <c r="A183" s="150" t="n"/>
-      <c r="B183" s="151" t="n"/>
-      <c r="C183" s="151" t="n"/>
-      <c r="D183" s="151" t="n"/>
-      <c r="E183" s="152" t="n"/>
-      <c r="F183" s="152">
+      <c r="A183" s="152" t="n"/>
+      <c r="B183" s="153" t="n"/>
+      <c r="C183" s="153" t="n"/>
+      <c r="D183" s="153" t="n"/>
+      <c r="E183" s="154" t="n"/>
+      <c r="F183" s="155">
         <f>IFERROR(SUMIF($C$8:C183,"Income",$E$8:E183)-SUMIF($C$8:C183,"Expense",$E$8:E183)-SUMIF($C$8:C183,"Savings",$E$8:E183),"")</f>
         <v/>
       </c>
-      <c r="G183" s="153" t="n"/>
-      <c r="H183" s="150" t="n"/>
+      <c r="G183" s="156" t="n"/>
+      <c r="H183" s="152" t="n"/>
     </row>
     <row r="184" ht="18" customHeight="1">
-      <c r="A184" s="146" t="n"/>
-      <c r="B184" s="147" t="n"/>
-      <c r="C184" s="147" t="n"/>
-      <c r="D184" s="147" t="n"/>
-      <c r="E184" s="148" t="n"/>
-      <c r="F184" s="148">
+      <c r="A184" s="147" t="n"/>
+      <c r="B184" s="148" t="n"/>
+      <c r="C184" s="148" t="n"/>
+      <c r="D184" s="148" t="n"/>
+      <c r="E184" s="149" t="n"/>
+      <c r="F184" s="150">
         <f>IFERROR(SUMIF($C$8:C184,"Income",$E$8:E184)-SUMIF($C$8:C184,"Expense",$E$8:E184)-SUMIF($C$8:C184,"Savings",$E$8:E184),"")</f>
         <v/>
       </c>
-      <c r="G184" s="149" t="n"/>
-      <c r="H184" s="146" t="n"/>
+      <c r="G184" s="151" t="n"/>
+      <c r="H184" s="147" t="n"/>
     </row>
     <row r="185" ht="18" customHeight="1">
-      <c r="A185" s="150" t="n"/>
-      <c r="B185" s="151" t="n"/>
-      <c r="C185" s="151" t="n"/>
-      <c r="D185" s="151" t="n"/>
-      <c r="E185" s="152" t="n"/>
-      <c r="F185" s="152">
+      <c r="A185" s="152" t="n"/>
+      <c r="B185" s="153" t="n"/>
+      <c r="C185" s="153" t="n"/>
+      <c r="D185" s="153" t="n"/>
+      <c r="E185" s="154" t="n"/>
+      <c r="F185" s="155">
         <f>IFERROR(SUMIF($C$8:C185,"Income",$E$8:E185)-SUMIF($C$8:C185,"Expense",$E$8:E185)-SUMIF($C$8:C185,"Savings",$E$8:E185),"")</f>
         <v/>
       </c>
-      <c r="G185" s="153" t="n"/>
-      <c r="H185" s="150" t="n"/>
+      <c r="G185" s="156" t="n"/>
+      <c r="H185" s="152" t="n"/>
     </row>
     <row r="186" ht="18" customHeight="1">
-      <c r="A186" s="146" t="n"/>
-      <c r="B186" s="147" t="n"/>
-      <c r="C186" s="147" t="n"/>
-      <c r="D186" s="147" t="n"/>
-      <c r="E186" s="148" t="n"/>
-      <c r="F186" s="148">
+      <c r="A186" s="147" t="n"/>
+      <c r="B186" s="148" t="n"/>
+      <c r="C186" s="148" t="n"/>
+      <c r="D186" s="148" t="n"/>
+      <c r="E186" s="149" t="n"/>
+      <c r="F186" s="150">
         <f>IFERROR(SUMIF($C$8:C186,"Income",$E$8:E186)-SUMIF($C$8:C186,"Expense",$E$8:E186)-SUMIF($C$8:C186,"Savings",$E$8:E186),"")</f>
         <v/>
       </c>
-      <c r="G186" s="149" t="n"/>
-      <c r="H186" s="146" t="n"/>
+      <c r="G186" s="151" t="n"/>
+      <c r="H186" s="147" t="n"/>
     </row>
     <row r="187" ht="18" customHeight="1">
-      <c r="A187" s="150" t="n"/>
-      <c r="B187" s="151" t="n"/>
-      <c r="C187" s="151" t="n"/>
-      <c r="D187" s="151" t="n"/>
-      <c r="E187" s="152" t="n"/>
-      <c r="F187" s="152">
+      <c r="A187" s="152" t="n"/>
+      <c r="B187" s="153" t="n"/>
+      <c r="C187" s="153" t="n"/>
+      <c r="D187" s="153" t="n"/>
+      <c r="E187" s="154" t="n"/>
+      <c r="F187" s="155">
         <f>IFERROR(SUMIF($C$8:C187,"Income",$E$8:E187)-SUMIF($C$8:C187,"Expense",$E$8:E187)-SUMIF($C$8:C187,"Savings",$E$8:E187),"")</f>
         <v/>
       </c>
-      <c r="G187" s="153" t="n"/>
-      <c r="H187" s="150" t="n"/>
+      <c r="G187" s="156" t="n"/>
+      <c r="H187" s="152" t="n"/>
     </row>
     <row r="188" ht="18" customHeight="1">
-      <c r="A188" s="146" t="n"/>
-      <c r="B188" s="147" t="n"/>
-      <c r="C188" s="147" t="n"/>
-      <c r="D188" s="147" t="n"/>
-      <c r="E188" s="148" t="n"/>
-      <c r="F188" s="148">
+      <c r="A188" s="147" t="n"/>
+      <c r="B188" s="148" t="n"/>
+      <c r="C188" s="148" t="n"/>
+      <c r="D188" s="148" t="n"/>
+      <c r="E188" s="149" t="n"/>
+      <c r="F188" s="150">
         <f>IFERROR(SUMIF($C$8:C188,"Income",$E$8:E188)-SUMIF($C$8:C188,"Expense",$E$8:E188)-SUMIF($C$8:C188,"Savings",$E$8:E188),"")</f>
         <v/>
       </c>
-      <c r="G188" s="149" t="n"/>
-      <c r="H188" s="146" t="n"/>
+      <c r="G188" s="151" t="n"/>
+      <c r="H188" s="147" t="n"/>
     </row>
     <row r="189" ht="18" customHeight="1">
-      <c r="A189" s="150" t="n"/>
-      <c r="B189" s="151" t="n"/>
-      <c r="C189" s="151" t="n"/>
-      <c r="D189" s="151" t="n"/>
-      <c r="E189" s="152" t="n"/>
-      <c r="F189" s="152">
+      <c r="A189" s="152" t="n"/>
+      <c r="B189" s="153" t="n"/>
+      <c r="C189" s="153" t="n"/>
+      <c r="D189" s="153" t="n"/>
+      <c r="E189" s="154" t="n"/>
+      <c r="F189" s="155">
         <f>IFERROR(SUMIF($C$8:C189,"Income",$E$8:E189)-SUMIF($C$8:C189,"Expense",$E$8:E189)-SUMIF($C$8:C189,"Savings",$E$8:E189),"")</f>
         <v/>
       </c>
-      <c r="G189" s="153" t="n"/>
-      <c r="H189" s="150" t="n"/>
+      <c r="G189" s="156" t="n"/>
+      <c r="H189" s="152" t="n"/>
     </row>
     <row r="190" ht="18" customHeight="1">
-      <c r="A190" s="146" t="n"/>
-      <c r="B190" s="147" t="n"/>
-      <c r="C190" s="147" t="n"/>
-      <c r="D190" s="147" t="n"/>
-      <c r="E190" s="148" t="n"/>
-      <c r="F190" s="148">
+      <c r="A190" s="147" t="n"/>
+      <c r="B190" s="148" t="n"/>
+      <c r="C190" s="148" t="n"/>
+      <c r="D190" s="148" t="n"/>
+      <c r="E190" s="149" t="n"/>
+      <c r="F190" s="150">
         <f>IFERROR(SUMIF($C$8:C190,"Income",$E$8:E190)-SUMIF($C$8:C190,"Expense",$E$8:E190)-SUMIF($C$8:C190,"Savings",$E$8:E190),"")</f>
         <v/>
       </c>
-      <c r="G190" s="149" t="n"/>
-      <c r="H190" s="146" t="n"/>
+      <c r="G190" s="151" t="n"/>
+      <c r="H190" s="147" t="n"/>
     </row>
     <row r="191" ht="18" customHeight="1">
-      <c r="A191" s="150" t="n"/>
-      <c r="B191" s="151" t="n"/>
-      <c r="C191" s="151" t="n"/>
-      <c r="D191" s="151" t="n"/>
-      <c r="E191" s="152" t="n"/>
-      <c r="F191" s="152">
+      <c r="A191" s="152" t="n"/>
+      <c r="B191" s="153" t="n"/>
+      <c r="C191" s="153" t="n"/>
+      <c r="D191" s="153" t="n"/>
+      <c r="E191" s="154" t="n"/>
+      <c r="F191" s="155">
         <f>IFERROR(SUMIF($C$8:C191,"Income",$E$8:E191)-SUMIF($C$8:C191,"Expense",$E$8:E191)-SUMIF($C$8:C191,"Savings",$E$8:E191),"")</f>
         <v/>
       </c>
-      <c r="G191" s="153" t="n"/>
-      <c r="H191" s="150" t="n"/>
+      <c r="G191" s="156" t="n"/>
+      <c r="H191" s="152" t="n"/>
     </row>
     <row r="192" ht="18" customHeight="1">
-      <c r="A192" s="146" t="n"/>
-      <c r="B192" s="147" t="n"/>
-      <c r="C192" s="147" t="n"/>
-      <c r="D192" s="147" t="n"/>
-      <c r="E192" s="148" t="n"/>
-      <c r="F192" s="148">
+      <c r="A192" s="147" t="n"/>
+      <c r="B192" s="148" t="n"/>
+      <c r="C192" s="148" t="n"/>
+      <c r="D192" s="148" t="n"/>
+      <c r="E192" s="149" t="n"/>
+      <c r="F192" s="150">
         <f>IFERROR(SUMIF($C$8:C192,"Income",$E$8:E192)-SUMIF($C$8:C192,"Expense",$E$8:E192)-SUMIF($C$8:C192,"Savings",$E$8:E192),"")</f>
         <v/>
       </c>
-      <c r="G192" s="149" t="n"/>
-      <c r="H192" s="146" t="n"/>
+      <c r="G192" s="151" t="n"/>
+      <c r="H192" s="147" t="n"/>
     </row>
     <row r="193" ht="18" customHeight="1">
-      <c r="A193" s="150" t="n"/>
-      <c r="B193" s="151" t="n"/>
-      <c r="C193" s="151" t="n"/>
-      <c r="D193" s="151" t="n"/>
-      <c r="E193" s="152" t="n"/>
-      <c r="F193" s="152">
+      <c r="A193" s="152" t="n"/>
+      <c r="B193" s="153" t="n"/>
+      <c r="C193" s="153" t="n"/>
+      <c r="D193" s="153" t="n"/>
+      <c r="E193" s="154" t="n"/>
+      <c r="F193" s="155">
         <f>IFERROR(SUMIF($C$8:C193,"Income",$E$8:E193)-SUMIF($C$8:C193,"Expense",$E$8:E193)-SUMIF($C$8:C193,"Savings",$E$8:E193),"")</f>
         <v/>
       </c>
-      <c r="G193" s="153" t="n"/>
-      <c r="H193" s="150" t="n"/>
+      <c r="G193" s="156" t="n"/>
+      <c r="H193" s="152" t="n"/>
     </row>
     <row r="194" ht="18" customHeight="1">
-      <c r="A194" s="146" t="n"/>
-      <c r="B194" s="147" t="n"/>
-      <c r="C194" s="147" t="n"/>
-      <c r="D194" s="147" t="n"/>
-      <c r="E194" s="148" t="n"/>
-      <c r="F194" s="148">
+      <c r="A194" s="147" t="n"/>
+      <c r="B194" s="148" t="n"/>
+      <c r="C194" s="148" t="n"/>
+      <c r="D194" s="148" t="n"/>
+      <c r="E194" s="149" t="n"/>
+      <c r="F194" s="150">
         <f>IFERROR(SUMIF($C$8:C194,"Income",$E$8:E194)-SUMIF($C$8:C194,"Expense",$E$8:E194)-SUMIF($C$8:C194,"Savings",$E$8:E194),"")</f>
         <v/>
       </c>
-      <c r="G194" s="149" t="n"/>
-      <c r="H194" s="146" t="n"/>
+      <c r="G194" s="151" t="n"/>
+      <c r="H194" s="147" t="n"/>
     </row>
     <row r="195" ht="18" customHeight="1">
-      <c r="A195" s="150" t="n"/>
-      <c r="B195" s="151" t="n"/>
-      <c r="C195" s="151" t="n"/>
-      <c r="D195" s="151" t="n"/>
-      <c r="E195" s="152" t="n"/>
-      <c r="F195" s="152">
+      <c r="A195" s="152" t="n"/>
+      <c r="B195" s="153" t="n"/>
+      <c r="C195" s="153" t="n"/>
+      <c r="D195" s="153" t="n"/>
+      <c r="E195" s="154" t="n"/>
+      <c r="F195" s="155">
         <f>IFERROR(SUMIF($C$8:C195,"Income",$E$8:E195)-SUMIF($C$8:C195,"Expense",$E$8:E195)-SUMIF($C$8:C195,"Savings",$E$8:E195),"")</f>
         <v/>
       </c>
-      <c r="G195" s="153" t="n"/>
-      <c r="H195" s="150" t="n"/>
+      <c r="G195" s="156" t="n"/>
+      <c r="H195" s="152" t="n"/>
     </row>
     <row r="196" ht="18" customHeight="1">
-      <c r="A196" s="146" t="n"/>
-      <c r="B196" s="147" t="n"/>
-      <c r="C196" s="147" t="n"/>
-      <c r="D196" s="147" t="n"/>
-      <c r="E196" s="148" t="n"/>
-      <c r="F196" s="148">
+      <c r="A196" s="147" t="n"/>
+      <c r="B196" s="148" t="n"/>
+      <c r="C196" s="148" t="n"/>
+      <c r="D196" s="148" t="n"/>
+      <c r="E196" s="149" t="n"/>
+      <c r="F196" s="150">
         <f>IFERROR(SUMIF($C$8:C196,"Income",$E$8:E196)-SUMIF($C$8:C196,"Expense",$E$8:E196)-SUMIF($C$8:C196,"Savings",$E$8:E196),"")</f>
         <v/>
       </c>
-      <c r="G196" s="149" t="n"/>
-      <c r="H196" s="146" t="n"/>
+      <c r="G196" s="151" t="n"/>
+      <c r="H196" s="147" t="n"/>
     </row>
     <row r="197" ht="18" customHeight="1">
-      <c r="A197" s="150" t="n"/>
-      <c r="B197" s="151" t="n"/>
-      <c r="C197" s="151" t="n"/>
-      <c r="D197" s="151" t="n"/>
-      <c r="E197" s="152" t="n"/>
-      <c r="F197" s="152">
+      <c r="A197" s="152" t="n"/>
+      <c r="B197" s="153" t="n"/>
+      <c r="C197" s="153" t="n"/>
+      <c r="D197" s="153" t="n"/>
+      <c r="E197" s="154" t="n"/>
+      <c r="F197" s="155">
         <f>IFERROR(SUMIF($C$8:C197,"Income",$E$8:E197)-SUMIF($C$8:C197,"Expense",$E$8:E197)-SUMIF($C$8:C197,"Savings",$E$8:E197),"")</f>
         <v/>
       </c>
-      <c r="G197" s="153" t="n"/>
-      <c r="H197" s="150" t="n"/>
+      <c r="G197" s="156" t="n"/>
+      <c r="H197" s="152" t="n"/>
     </row>
     <row r="198" ht="18" customHeight="1">
-      <c r="A198" s="146" t="n"/>
-      <c r="B198" s="147" t="n"/>
-      <c r="C198" s="147" t="n"/>
-      <c r="D198" s="147" t="n"/>
-      <c r="E198" s="148" t="n"/>
-      <c r="F198" s="148">
+      <c r="A198" s="147" t="n"/>
+      <c r="B198" s="148" t="n"/>
+      <c r="C198" s="148" t="n"/>
+      <c r="D198" s="148" t="n"/>
+      <c r="E198" s="149" t="n"/>
+      <c r="F198" s="150">
         <f>IFERROR(SUMIF($C$8:C198,"Income",$E$8:E198)-SUMIF($C$8:C198,"Expense",$E$8:E198)-SUMIF($C$8:C198,"Savings",$E$8:E198),"")</f>
         <v/>
       </c>
-      <c r="G198" s="149" t="n"/>
-      <c r="H198" s="146" t="n"/>
+      <c r="G198" s="151" t="n"/>
+      <c r="H198" s="147" t="n"/>
     </row>
     <row r="199" ht="18" customHeight="1">
-      <c r="A199" s="150" t="n"/>
-      <c r="B199" s="151" t="n"/>
-      <c r="C199" s="151" t="n"/>
-      <c r="D199" s="151" t="n"/>
-      <c r="E199" s="152" t="n"/>
-      <c r="F199" s="152">
+      <c r="A199" s="152" t="n"/>
+      <c r="B199" s="153" t="n"/>
+      <c r="C199" s="153" t="n"/>
+      <c r="D199" s="153" t="n"/>
+      <c r="E199" s="154" t="n"/>
+      <c r="F199" s="155">
         <f>IFERROR(SUMIF($C$8:C199,"Income",$E$8:E199)-SUMIF($C$8:C199,"Expense",$E$8:E199)-SUMIF($C$8:C199,"Savings",$E$8:E199),"")</f>
         <v/>
       </c>
-      <c r="G199" s="153" t="n"/>
-      <c r="H199" s="150" t="n"/>
+      <c r="G199" s="156" t="n"/>
+      <c r="H199" s="152" t="n"/>
     </row>
     <row r="200" ht="18" customHeight="1">
-      <c r="A200" s="146" t="n"/>
-      <c r="B200" s="147" t="n"/>
-      <c r="C200" s="147" t="n"/>
-      <c r="D200" s="147" t="n"/>
-      <c r="E200" s="148" t="n"/>
-      <c r="F200" s="148">
+      <c r="A200" s="147" t="n"/>
+      <c r="B200" s="148" t="n"/>
+      <c r="C200" s="148" t="n"/>
+      <c r="D200" s="148" t="n"/>
+      <c r="E200" s="149" t="n"/>
+      <c r="F200" s="150">
         <f>IFERROR(SUMIF($C$8:C200,"Income",$E$8:E200)-SUMIF($C$8:C200,"Expense",$E$8:E200)-SUMIF($C$8:C200,"Savings",$E$8:E200),"")</f>
         <v/>
       </c>
-      <c r="G200" s="149" t="n"/>
-      <c r="H200" s="146" t="n"/>
+      <c r="G200" s="151" t="n"/>
+      <c r="H200" s="147" t="n"/>
     </row>
     <row r="201" ht="18" customHeight="1">
-      <c r="A201" s="150" t="n"/>
-      <c r="B201" s="151" t="n"/>
-      <c r="C201" s="151" t="n"/>
-      <c r="D201" s="151" t="n"/>
-      <c r="E201" s="152" t="n"/>
-      <c r="F201" s="152">
+      <c r="A201" s="152" t="n"/>
+      <c r="B201" s="153" t="n"/>
+      <c r="C201" s="153" t="n"/>
+      <c r="D201" s="153" t="n"/>
+      <c r="E201" s="154" t="n"/>
+      <c r="F201" s="155">
         <f>IFERROR(SUMIF($C$8:C201,"Income",$E$8:E201)-SUMIF($C$8:C201,"Expense",$E$8:E201)-SUMIF($C$8:C201,"Savings",$E$8:E201),"")</f>
         <v/>
       </c>
-      <c r="G201" s="153" t="n"/>
-      <c r="H201" s="150" t="n"/>
+      <c r="G201" s="156" t="n"/>
+      <c r="H201" s="152" t="n"/>
     </row>
     <row r="202" ht="18" customHeight="1">
-      <c r="A202" s="146" t="n"/>
-      <c r="B202" s="147" t="n"/>
-      <c r="C202" s="147" t="n"/>
-      <c r="D202" s="147" t="n"/>
-      <c r="E202" s="148" t="n"/>
-      <c r="F202" s="148">
+      <c r="A202" s="147" t="n"/>
+      <c r="B202" s="148" t="n"/>
+      <c r="C202" s="148" t="n"/>
+      <c r="D202" s="148" t="n"/>
+      <c r="E202" s="149" t="n"/>
+      <c r="F202" s="150">
         <f>IFERROR(SUMIF($C$8:C202,"Income",$E$8:E202)-SUMIF($C$8:C202,"Expense",$E$8:E202)-SUMIF($C$8:C202,"Savings",$E$8:E202),"")</f>
         <v/>
       </c>
-      <c r="G202" s="149" t="n"/>
-      <c r="H202" s="146" t="n"/>
+      <c r="G202" s="151" t="n"/>
+      <c r="H202" s="147" t="n"/>
     </row>
     <row r="203" ht="18" customHeight="1">
-      <c r="A203" s="150" t="n"/>
-      <c r="B203" s="151" t="n"/>
-      <c r="C203" s="151" t="n"/>
-      <c r="D203" s="151" t="n"/>
-      <c r="E203" s="152" t="n"/>
-      <c r="F203" s="152">
+      <c r="A203" s="152" t="n"/>
+      <c r="B203" s="153" t="n"/>
+      <c r="C203" s="153" t="n"/>
+      <c r="D203" s="153" t="n"/>
+      <c r="E203" s="154" t="n"/>
+      <c r="F203" s="155">
         <f>IFERROR(SUMIF($C$8:C203,"Income",$E$8:E203)-SUMIF($C$8:C203,"Expense",$E$8:E203)-SUMIF($C$8:C203,"Savings",$E$8:E203),"")</f>
         <v/>
       </c>
-      <c r="G203" s="153" t="n"/>
-      <c r="H203" s="150" t="n"/>
+      <c r="G203" s="156" t="n"/>
+      <c r="H203" s="152" t="n"/>
     </row>
     <row r="204" ht="18" customHeight="1">
-      <c r="A204" s="146" t="n"/>
-      <c r="B204" s="147" t="n"/>
-      <c r="C204" s="147" t="n"/>
-      <c r="D204" s="147" t="n"/>
-      <c r="E204" s="148" t="n"/>
-      <c r="F204" s="148">
+      <c r="A204" s="147" t="n"/>
+      <c r="B204" s="148" t="n"/>
+      <c r="C204" s="148" t="n"/>
+      <c r="D204" s="148" t="n"/>
+      <c r="E204" s="149" t="n"/>
+      <c r="F204" s="150">
         <f>IFERROR(SUMIF($C$8:C204,"Income",$E$8:E204)-SUMIF($C$8:C204,"Expense",$E$8:E204)-SUMIF($C$8:C204,"Savings",$E$8:E204),"")</f>
         <v/>
       </c>
-      <c r="G204" s="149" t="n"/>
-      <c r="H204" s="146" t="n"/>
+      <c r="G204" s="151" t="n"/>
+      <c r="H204" s="147" t="n"/>
     </row>
     <row r="205" ht="18" customHeight="1">
-      <c r="A205" s="150" t="n"/>
-      <c r="B205" s="151" t="n"/>
-      <c r="C205" s="151" t="n"/>
-      <c r="D205" s="151" t="n"/>
-      <c r="E205" s="152" t="n"/>
-      <c r="F205" s="152">
+      <c r="A205" s="152" t="n"/>
+      <c r="B205" s="153" t="n"/>
+      <c r="C205" s="153" t="n"/>
+      <c r="D205" s="153" t="n"/>
+      <c r="E205" s="154" t="n"/>
+      <c r="F205" s="155">
         <f>IFERROR(SUMIF($C$8:C205,"Income",$E$8:E205)-SUMIF($C$8:C205,"Expense",$E$8:E205)-SUMIF($C$8:C205,"Savings",$E$8:E205),"")</f>
         <v/>
       </c>
-      <c r="G205" s="153" t="n"/>
-      <c r="H205" s="150" t="n"/>
+      <c r="G205" s="156" t="n"/>
+      <c r="H205" s="152" t="n"/>
     </row>
     <row r="206" ht="18" customHeight="1">
-      <c r="A206" s="146" t="n"/>
-      <c r="B206" s="147" t="n"/>
-      <c r="C206" s="147" t="n"/>
-      <c r="D206" s="147" t="n"/>
-      <c r="E206" s="148" t="n"/>
-      <c r="F206" s="148">
+      <c r="A206" s="147" t="n"/>
+      <c r="B206" s="148" t="n"/>
+      <c r="C206" s="148" t="n"/>
+      <c r="D206" s="148" t="n"/>
+      <c r="E206" s="149" t="n"/>
+      <c r="F206" s="150">
         <f>IFERROR(SUMIF($C$8:C206,"Income",$E$8:E206)-SUMIF($C$8:C206,"Expense",$E$8:E206)-SUMIF($C$8:C206,"Savings",$E$8:E206),"")</f>
         <v/>
       </c>
-      <c r="G206" s="149" t="n"/>
-      <c r="H206" s="146" t="n"/>
+      <c r="G206" s="151" t="n"/>
+      <c r="H206" s="147" t="n"/>
     </row>
     <row r="207" ht="18" customHeight="1">
-      <c r="A207" s="150" t="n"/>
-      <c r="B207" s="151" t="n"/>
-      <c r="C207" s="151" t="n"/>
-      <c r="D207" s="151" t="n"/>
-      <c r="E207" s="152" t="n"/>
-      <c r="F207" s="152">
+      <c r="A207" s="152" t="n"/>
+      <c r="B207" s="153" t="n"/>
+      <c r="C207" s="153" t="n"/>
+      <c r="D207" s="153" t="n"/>
+      <c r="E207" s="154" t="n"/>
+      <c r="F207" s="155">
         <f>IFERROR(SUMIF($C$8:C207,"Income",$E$8:E207)-SUMIF($C$8:C207,"Expense",$E$8:E207)-SUMIF($C$8:C207,"Savings",$E$8:E207),"")</f>
         <v/>
       </c>
-      <c r="G207" s="153" t="n"/>
-      <c r="H207" s="150" t="n"/>
-    </row>
-    <row r="210" ht="26" customHeight="1">
-      <c r="A210" s="154" t="inlineStr">
+      <c r="G207" s="156" t="n"/>
+      <c r="H207" s="152" t="n"/>
+    </row>
+    <row r="210" ht="24" customHeight="1">
+      <c r="A210" s="157" t="inlineStr">
         <is>
-          <t>MONTHLY SUMMARY</t>
+          <t>MONTHLY SUMMARY (current year)</t>
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="145" t="inlineStr">
+    <row r="211" ht="20" customHeight="1">
+      <c r="A211" s="158" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B211" s="145" t="inlineStr">
+      <c r="B211" s="158" t="inlineStr">
         <is>
           <t>Income</t>
         </is>
       </c>
-      <c r="C211" s="145" t="inlineStr">
+      <c r="C211" s="158" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="D211" s="145" t="inlineStr">
+      <c r="D211" s="158" t="inlineStr">
         <is>
           <t>Savings</t>
         </is>
       </c>
-      <c r="E211" s="145" t="inlineStr">
+      <c r="E211" s="158" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="F211" s="145" t="inlineStr"/>
-      <c r="G211" s="145" t="inlineStr"/>
-      <c r="H211" s="145" t="inlineStr"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="155" t="inlineStr">
+      <c r="F211" s="158" t="inlineStr"/>
+      <c r="G211" s="158" t="inlineStr"/>
+      <c r="H211" s="158" t="inlineStr"/>
+    </row>
+    <row r="212" ht="18" customHeight="1">
+      <c r="A212" s="159" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="B212" s="156">
+      <c r="B212" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=1)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Income")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="C212" s="156">
+      <c r="C212" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=1)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Expense")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="D212" s="156">
+      <c r="D212" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=1)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Savings")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="E212" s="156">
+      <c r="E212" s="160">
         <f>B212-C212-D212</f>
         <v/>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="155" t="inlineStr">
+    <row r="213" ht="18" customHeight="1">
+      <c r="A213" s="159" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="B213" s="156">
+      <c r="B213" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=2)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Income")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="C213" s="156">
+      <c r="C213" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=2)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Expense")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="D213" s="156">
+      <c r="D213" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=2)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Savings")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="E213" s="156">
+      <c r="E213" s="160">
         <f>B213-C213-D213</f>
         <v/>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="155" t="inlineStr">
+    <row r="214" ht="18" customHeight="1">
+      <c r="A214" s="159" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="B214" s="156">
+      <c r="B214" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=3)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Income")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="C214" s="156">
+      <c r="C214" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=3)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Expense")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="D214" s="156">
+      <c r="D214" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=3)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Savings")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="E214" s="156">
+      <c r="E214" s="160">
         <f>B214-C214-D214</f>
         <v/>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="155" t="inlineStr">
+    <row r="215" ht="18" customHeight="1">
+      <c r="A215" s="159" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="B215" s="156">
+      <c r="B215" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=4)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Income")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="C215" s="156">
+      <c r="C215" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=4)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Expense")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="D215" s="156">
+      <c r="D215" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=4)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Savings")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="E215" s="156">
+      <c r="E215" s="160">
         <f>B215-C215-D215</f>
         <v/>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="155" t="inlineStr">
+    <row r="216" ht="18" customHeight="1">
+      <c r="A216" s="159" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="B216" s="156">
+      <c r="B216" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=5)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Income")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="C216" s="156">
+      <c r="C216" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=5)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Expense")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="D216" s="156">
+      <c r="D216" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=5)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Savings")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="E216" s="156">
+      <c r="E216" s="160">
         <f>B216-C216-D216</f>
         <v/>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="155" t="inlineStr">
+    <row r="217" ht="18" customHeight="1">
+      <c r="A217" s="159" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="B217" s="156">
+      <c r="B217" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=6)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Income")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="C217" s="156">
+      <c r="C217" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=6)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Expense")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="D217" s="156">
+      <c r="D217" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=6)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Savings")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="E217" s="156">
+      <c r="E217" s="160">
         <f>B217-C217-D217</f>
         <v/>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="155" t="inlineStr">
+    <row r="218" ht="18" customHeight="1">
+      <c r="A218" s="159" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="B218" s="156">
+      <c r="B218" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=7)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Income")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="C218" s="156">
+      <c r="C218" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=7)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Expense")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="D218" s="156">
+      <c r="D218" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=7)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Savings")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="E218" s="156">
+      <c r="E218" s="160">
         <f>B218-C218-D218</f>
         <v/>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="155" t="inlineStr">
+    <row r="219" ht="18" customHeight="1">
+      <c r="A219" s="159" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="B219" s="156">
+      <c r="B219" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=8)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Income")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="C219" s="156">
+      <c r="C219" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=8)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Expense")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="D219" s="156">
+      <c r="D219" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=8)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Savings")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="E219" s="156">
+      <c r="E219" s="160">
         <f>B219-C219-D219</f>
         <v/>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="155" t="inlineStr">
+    <row r="220" ht="18" customHeight="1">
+      <c r="A220" s="159" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="B220" s="156">
+      <c r="B220" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=9)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Income")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="C220" s="156">
+      <c r="C220" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=9)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Expense")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="D220" s="156">
+      <c r="D220" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=9)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Savings")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="E220" s="156">
+      <c r="E220" s="160">
         <f>B220-C220-D220</f>
         <v/>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="155" t="inlineStr">
+    <row r="221" ht="18" customHeight="1">
+      <c r="A221" s="159" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="B221" s="156">
+      <c r="B221" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=10)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Income")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="C221" s="156">
+      <c r="C221" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=10)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Expense")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="D221" s="156">
+      <c r="D221" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=10)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Savings")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="E221" s="156">
+      <c r="E221" s="160">
         <f>B221-C221-D221</f>
         <v/>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="155" t="inlineStr">
+    <row r="222" ht="18" customHeight="1">
+      <c r="A222" s="159" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="B222" s="156">
+      <c r="B222" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=11)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Income")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="C222" s="156">
+      <c r="C222" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=11)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Expense")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="D222" s="156">
+      <c r="D222" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=11)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Savings")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="E222" s="156">
+      <c r="E222" s="160">
         <f>B222-C222-D222</f>
         <v/>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="155" t="inlineStr">
+    <row r="223" ht="18" customHeight="1">
+      <c r="A223" s="159" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="B223" s="156">
+      <c r="B223" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=12)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Income")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="C223" s="156">
+      <c r="C223" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=12)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Expense")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="D223" s="156">
+      <c r="D223" s="160">
         <f>IFERROR(SUMPRODUCT((MONTH($A$8:$A$207)=12)*(YEAR($A$8:$A$207)=2026)*($C$8:$C$207="Savings")*($E$8:$E$207)),0)</f>
         <v/>
       </c>
-      <c r="E223" s="156">
+      <c r="E223" s="160">
         <f>B223-C223-D223</f>
         <v/>
       </c>
@@ -35018,10 +34591,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C8:C207" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Type" error="Choose Income, Expense, or Savings" type="list">
+    <dataValidation sqref="C8:C207" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid" error="Choose Income, Expense, or Savings" type="list">
       <formula1>"Income,Expense,Savings"</formula1>
     </dataValidation>
-    <dataValidation sqref="B8:B207" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Category" error="Select a category from the list" type="list">
+    <dataValidation sqref="B8:B207" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Dropdown Data'!$Q$2:$Q$21</formula1>
     </dataValidation>
     <dataValidation sqref="G8:G207" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -35047,27 +34620,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="157" t="inlineStr">
+      <c r="A1" s="161" t="inlineStr">
         <is>
-          <t>🔄 SUBSCRIPTION TRACKER</t>
+          <t>SUBSCRIPTION TRACKER</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" ht="18" customHeight="1">
       <c r="A2" s="142" t="inlineStr">
         <is>
-          <t>Track recurring costs · Auto-detects paid/unpaid status based on Last Paid Date</t>
+          <t>Auto-detects Paid/Unpaid based on Last Paid Date each calendar month</t>
         </is>
       </c>
     </row>
@@ -35089,116 +34662,109 @@
       </c>
       <c r="G3" s="143" t="inlineStr">
         <is>
-          <t>UNPAID THIS MONTH</t>
+          <t>UNPAID</t>
         </is>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="144">
-        <f>IFERROR(SUMPRODUCT((I8:I207&lt;&gt;"")*H8:H207),0)</f>
+        <f>IFERROR(SUMPRODUCT((A8:A57&lt;&gt;"")*G8:G57),0)</f>
         <v/>
       </c>
       <c r="C4" s="144">
-        <f>IFERROR(SUMPRODUCT((I8:I207&lt;&gt;"")*H8:H207)*12,0)</f>
-        <v/>
-      </c>
-      <c r="E4" s="158">
-        <f>COUNTA(A8:A207)</f>
-        <v/>
-      </c>
-      <c r="G4" s="158">
-        <f>COUNTIF(I8:I207,"Unpaid")</f>
+        <f>A4*12</f>
+        <v/>
+      </c>
+      <c r="E4" s="145">
+        <f>COUNTA(A8:A57)</f>
+        <v/>
+      </c>
+      <c r="G4" s="145">
+        <f>COUNTIF(I8:I57,"Unpaid")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="8" customHeight="1"/>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="145" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="146" t="inlineStr">
         <is>
           <t>Service Name</t>
         </is>
       </c>
-      <c r="B6" s="145" t="inlineStr">
+      <c r="B6" s="146" t="inlineStr">
         <is>
           <t>Billing Cycle</t>
         </is>
       </c>
-      <c r="C6" s="145" t="inlineStr">
+      <c r="C6" s="146" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D6" s="145" t="inlineStr">
+      <c r="D6" s="146" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="E6" s="145" t="inlineStr">
+      <c r="E6" s="146" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="F6" s="145" t="inlineStr">
+      <c r="F6" s="146" t="inlineStr">
         <is>
           <t>Last Paid Date</t>
         </is>
       </c>
-      <c r="G6" s="145" t="inlineStr">
+      <c r="G6" s="146" t="inlineStr">
         <is>
           <t>Monthly Equiv</t>
         </is>
       </c>
-      <c r="H6" s="145" t="inlineStr">
+      <c r="H6" s="146" t="inlineStr">
         <is>
-          <t>Monthly Cost</t>
+          <t>Annual Equiv</t>
         </is>
       </c>
-      <c r="I6" s="145" t="inlineStr">
+      <c r="I6" s="146" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="159" t="inlineStr">
-        <is>
-          <t>← Enter subscription details. Cycle: Monthly / Annual / Weekly. Last Paid Date auto-updates Status.</t>
-        </is>
-      </c>
-    </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="147" t="n"/>
-      <c r="B8" s="147" t="n"/>
-      <c r="C8" s="148" t="n"/>
-      <c r="D8" s="147" t="n"/>
-      <c r="E8" s="147" t="n"/>
-      <c r="F8" s="146" t="n"/>
-      <c r="G8" s="160">
-        <f>IFERROR(IF(B8="Monthly",C8,IF(B8="Annual",C8/12,IF(B8="Weekly",C8*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H8" s="148">
-        <f>IFERROR(IF(A8&lt;&gt;"",G8,""),"")</f>
-        <v/>
-      </c>
-      <c r="I8" s="161">
+      <c r="A8" s="148" t="n"/>
+      <c r="B8" s="148" t="n"/>
+      <c r="C8" s="149" t="n"/>
+      <c r="D8" s="148" t="n"/>
+      <c r="E8" s="148" t="n"/>
+      <c r="F8" s="147" t="n"/>
+      <c r="G8" s="149">
+        <f>IFERROR(IF(A8="","",IF(B8="Monthly",C8,IF(B8="Annual",C8/12,IF(B8="Weekly",C8*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="149">
+        <f>IFERROR(IF(A8="","",G8*12),"")</f>
+        <v/>
+      </c>
+      <c r="I8" s="162">
         <f>IFERROR(IF(A8="","",IF(F8="","Unpaid",IF(AND(YEAR(F8)=YEAR(TODAY()),MONTH(F8)=MONTH(TODAY())),"Paid","Unpaid"))),"")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="151" t="n"/>
-      <c r="B9" s="151" t="n"/>
-      <c r="C9" s="152" t="n"/>
-      <c r="D9" s="151" t="n"/>
-      <c r="E9" s="151" t="n"/>
-      <c r="F9" s="150" t="n"/>
-      <c r="G9" s="162">
-        <f>IFERROR(IF(B9="Monthly",C9,IF(B9="Annual",C9/12,IF(B9="Weekly",C9*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H9" s="152">
-        <f>IFERROR(IF(A9&lt;&gt;"",G9,""),"")</f>
+      <c r="A9" s="153" t="n"/>
+      <c r="B9" s="153" t="n"/>
+      <c r="C9" s="154" t="n"/>
+      <c r="D9" s="153" t="n"/>
+      <c r="E9" s="153" t="n"/>
+      <c r="F9" s="152" t="n"/>
+      <c r="G9" s="154">
+        <f>IFERROR(IF(A9="","",IF(B9="Monthly",C9,IF(B9="Annual",C9/12,IF(B9="Weekly",C9*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="154">
+        <f>IFERROR(IF(A9="","",G9*12),"")</f>
         <v/>
       </c>
       <c r="I9" s="163">
@@ -35207,38 +34773,38 @@
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="147" t="n"/>
-      <c r="B10" s="147" t="n"/>
-      <c r="C10" s="148" t="n"/>
-      <c r="D10" s="147" t="n"/>
-      <c r="E10" s="147" t="n"/>
-      <c r="F10" s="146" t="n"/>
-      <c r="G10" s="160">
-        <f>IFERROR(IF(B10="Monthly",C10,IF(B10="Annual",C10/12,IF(B10="Weekly",C10*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H10" s="148">
-        <f>IFERROR(IF(A10&lt;&gt;"",G10,""),"")</f>
-        <v/>
-      </c>
-      <c r="I10" s="161">
+      <c r="A10" s="148" t="n"/>
+      <c r="B10" s="148" t="n"/>
+      <c r="C10" s="149" t="n"/>
+      <c r="D10" s="148" t="n"/>
+      <c r="E10" s="148" t="n"/>
+      <c r="F10" s="147" t="n"/>
+      <c r="G10" s="149">
+        <f>IFERROR(IF(A10="","",IF(B10="Monthly",C10,IF(B10="Annual",C10/12,IF(B10="Weekly",C10*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="149">
+        <f>IFERROR(IF(A10="","",G10*12),"")</f>
+        <v/>
+      </c>
+      <c r="I10" s="162">
         <f>IFERROR(IF(A10="","",IF(F10="","Unpaid",IF(AND(YEAR(F10)=YEAR(TODAY()),MONTH(F10)=MONTH(TODAY())),"Paid","Unpaid"))),"")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="151" t="n"/>
-      <c r="B11" s="151" t="n"/>
-      <c r="C11" s="152" t="n"/>
-      <c r="D11" s="151" t="n"/>
-      <c r="E11" s="151" t="n"/>
-      <c r="F11" s="150" t="n"/>
-      <c r="G11" s="162">
-        <f>IFERROR(IF(B11="Monthly",C11,IF(B11="Annual",C11/12,IF(B11="Weekly",C11*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H11" s="152">
-        <f>IFERROR(IF(A11&lt;&gt;"",G11,""),"")</f>
+      <c r="A11" s="153" t="n"/>
+      <c r="B11" s="153" t="n"/>
+      <c r="C11" s="154" t="n"/>
+      <c r="D11" s="153" t="n"/>
+      <c r="E11" s="153" t="n"/>
+      <c r="F11" s="152" t="n"/>
+      <c r="G11" s="154">
+        <f>IFERROR(IF(A11="","",IF(B11="Monthly",C11,IF(B11="Annual",C11/12,IF(B11="Weekly",C11*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="154">
+        <f>IFERROR(IF(A11="","",G11*12),"")</f>
         <v/>
       </c>
       <c r="I11" s="163">
@@ -35247,38 +34813,38 @@
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="147" t="n"/>
-      <c r="B12" s="147" t="n"/>
-      <c r="C12" s="148" t="n"/>
-      <c r="D12" s="147" t="n"/>
-      <c r="E12" s="147" t="n"/>
-      <c r="F12" s="146" t="n"/>
-      <c r="G12" s="160">
-        <f>IFERROR(IF(B12="Monthly",C12,IF(B12="Annual",C12/12,IF(B12="Weekly",C12*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H12" s="148">
-        <f>IFERROR(IF(A12&lt;&gt;"",G12,""),"")</f>
-        <v/>
-      </c>
-      <c r="I12" s="161">
+      <c r="A12" s="148" t="n"/>
+      <c r="B12" s="148" t="n"/>
+      <c r="C12" s="149" t="n"/>
+      <c r="D12" s="148" t="n"/>
+      <c r="E12" s="148" t="n"/>
+      <c r="F12" s="147" t="n"/>
+      <c r="G12" s="149">
+        <f>IFERROR(IF(A12="","",IF(B12="Monthly",C12,IF(B12="Annual",C12/12,IF(B12="Weekly",C12*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="149">
+        <f>IFERROR(IF(A12="","",G12*12),"")</f>
+        <v/>
+      </c>
+      <c r="I12" s="162">
         <f>IFERROR(IF(A12="","",IF(F12="","Unpaid",IF(AND(YEAR(F12)=YEAR(TODAY()),MONTH(F12)=MONTH(TODAY())),"Paid","Unpaid"))),"")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="151" t="n"/>
-      <c r="B13" s="151" t="n"/>
-      <c r="C13" s="152" t="n"/>
-      <c r="D13" s="151" t="n"/>
-      <c r="E13" s="151" t="n"/>
-      <c r="F13" s="150" t="n"/>
-      <c r="G13" s="162">
-        <f>IFERROR(IF(B13="Monthly",C13,IF(B13="Annual",C13/12,IF(B13="Weekly",C13*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H13" s="152">
-        <f>IFERROR(IF(A13&lt;&gt;"",G13,""),"")</f>
+      <c r="A13" s="153" t="n"/>
+      <c r="B13" s="153" t="n"/>
+      <c r="C13" s="154" t="n"/>
+      <c r="D13" s="153" t="n"/>
+      <c r="E13" s="153" t="n"/>
+      <c r="F13" s="152" t="n"/>
+      <c r="G13" s="154">
+        <f>IFERROR(IF(A13="","",IF(B13="Monthly",C13,IF(B13="Annual",C13/12,IF(B13="Weekly",C13*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="154">
+        <f>IFERROR(IF(A13="","",G13*12),"")</f>
         <v/>
       </c>
       <c r="I13" s="163">
@@ -35287,38 +34853,38 @@
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="147" t="n"/>
-      <c r="B14" s="147" t="n"/>
-      <c r="C14" s="148" t="n"/>
-      <c r="D14" s="147" t="n"/>
-      <c r="E14" s="147" t="n"/>
-      <c r="F14" s="146" t="n"/>
-      <c r="G14" s="160">
-        <f>IFERROR(IF(B14="Monthly",C14,IF(B14="Annual",C14/12,IF(B14="Weekly",C14*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="148">
-        <f>IFERROR(IF(A14&lt;&gt;"",G14,""),"")</f>
-        <v/>
-      </c>
-      <c r="I14" s="161">
+      <c r="A14" s="148" t="n"/>
+      <c r="B14" s="148" t="n"/>
+      <c r="C14" s="149" t="n"/>
+      <c r="D14" s="148" t="n"/>
+      <c r="E14" s="148" t="n"/>
+      <c r="F14" s="147" t="n"/>
+      <c r="G14" s="149">
+        <f>IFERROR(IF(A14="","",IF(B14="Monthly",C14,IF(B14="Annual",C14/12,IF(B14="Weekly",C14*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="149">
+        <f>IFERROR(IF(A14="","",G14*12),"")</f>
+        <v/>
+      </c>
+      <c r="I14" s="162">
         <f>IFERROR(IF(A14="","",IF(F14="","Unpaid",IF(AND(YEAR(F14)=YEAR(TODAY()),MONTH(F14)=MONTH(TODAY())),"Paid","Unpaid"))),"")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="151" t="n"/>
-      <c r="B15" s="151" t="n"/>
-      <c r="C15" s="152" t="n"/>
-      <c r="D15" s="151" t="n"/>
-      <c r="E15" s="151" t="n"/>
-      <c r="F15" s="150" t="n"/>
-      <c r="G15" s="162">
-        <f>IFERROR(IF(B15="Monthly",C15,IF(B15="Annual",C15/12,IF(B15="Weekly",C15*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="152">
-        <f>IFERROR(IF(A15&lt;&gt;"",G15,""),"")</f>
+      <c r="A15" s="153" t="n"/>
+      <c r="B15" s="153" t="n"/>
+      <c r="C15" s="154" t="n"/>
+      <c r="D15" s="153" t="n"/>
+      <c r="E15" s="153" t="n"/>
+      <c r="F15" s="152" t="n"/>
+      <c r="G15" s="154">
+        <f>IFERROR(IF(A15="","",IF(B15="Monthly",C15,IF(B15="Annual",C15/12,IF(B15="Weekly",C15*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="154">
+        <f>IFERROR(IF(A15="","",G15*12),"")</f>
         <v/>
       </c>
       <c r="I15" s="163">
@@ -35327,38 +34893,38 @@
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="147" t="n"/>
-      <c r="B16" s="147" t="n"/>
-      <c r="C16" s="148" t="n"/>
-      <c r="D16" s="147" t="n"/>
-      <c r="E16" s="147" t="n"/>
-      <c r="F16" s="146" t="n"/>
-      <c r="G16" s="160">
-        <f>IFERROR(IF(B16="Monthly",C16,IF(B16="Annual",C16/12,IF(B16="Weekly",C16*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="148">
-        <f>IFERROR(IF(A16&lt;&gt;"",G16,""),"")</f>
-        <v/>
-      </c>
-      <c r="I16" s="161">
+      <c r="A16" s="148" t="n"/>
+      <c r="B16" s="148" t="n"/>
+      <c r="C16" s="149" t="n"/>
+      <c r="D16" s="148" t="n"/>
+      <c r="E16" s="148" t="n"/>
+      <c r="F16" s="147" t="n"/>
+      <c r="G16" s="149">
+        <f>IFERROR(IF(A16="","",IF(B16="Monthly",C16,IF(B16="Annual",C16/12,IF(B16="Weekly",C16*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="149">
+        <f>IFERROR(IF(A16="","",G16*12),"")</f>
+        <v/>
+      </c>
+      <c r="I16" s="162">
         <f>IFERROR(IF(A16="","",IF(F16="","Unpaid",IF(AND(YEAR(F16)=YEAR(TODAY()),MONTH(F16)=MONTH(TODAY())),"Paid","Unpaid"))),"")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="151" t="n"/>
-      <c r="B17" s="151" t="n"/>
-      <c r="C17" s="152" t="n"/>
-      <c r="D17" s="151" t="n"/>
-      <c r="E17" s="151" t="n"/>
-      <c r="F17" s="150" t="n"/>
-      <c r="G17" s="162">
-        <f>IFERROR(IF(B17="Monthly",C17,IF(B17="Annual",C17/12,IF(B17="Weekly",C17*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="152">
-        <f>IFERROR(IF(A17&lt;&gt;"",G17,""),"")</f>
+      <c r="A17" s="153" t="n"/>
+      <c r="B17" s="153" t="n"/>
+      <c r="C17" s="154" t="n"/>
+      <c r="D17" s="153" t="n"/>
+      <c r="E17" s="153" t="n"/>
+      <c r="F17" s="152" t="n"/>
+      <c r="G17" s="154">
+        <f>IFERROR(IF(A17="","",IF(B17="Monthly",C17,IF(B17="Annual",C17/12,IF(B17="Weekly",C17*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="154">
+        <f>IFERROR(IF(A17="","",G17*12),"")</f>
         <v/>
       </c>
       <c r="I17" s="163">
@@ -35367,38 +34933,38 @@
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="147" t="n"/>
-      <c r="B18" s="147" t="n"/>
-      <c r="C18" s="148" t="n"/>
-      <c r="D18" s="147" t="n"/>
-      <c r="E18" s="147" t="n"/>
-      <c r="F18" s="146" t="n"/>
-      <c r="G18" s="160">
-        <f>IFERROR(IF(B18="Monthly",C18,IF(B18="Annual",C18/12,IF(B18="Weekly",C18*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="148">
-        <f>IFERROR(IF(A18&lt;&gt;"",G18,""),"")</f>
-        <v/>
-      </c>
-      <c r="I18" s="161">
+      <c r="A18" s="148" t="n"/>
+      <c r="B18" s="148" t="n"/>
+      <c r="C18" s="149" t="n"/>
+      <c r="D18" s="148" t="n"/>
+      <c r="E18" s="148" t="n"/>
+      <c r="F18" s="147" t="n"/>
+      <c r="G18" s="149">
+        <f>IFERROR(IF(A18="","",IF(B18="Monthly",C18,IF(B18="Annual",C18/12,IF(B18="Weekly",C18*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="149">
+        <f>IFERROR(IF(A18="","",G18*12),"")</f>
+        <v/>
+      </c>
+      <c r="I18" s="162">
         <f>IFERROR(IF(A18="","",IF(F18="","Unpaid",IF(AND(YEAR(F18)=YEAR(TODAY()),MONTH(F18)=MONTH(TODAY())),"Paid","Unpaid"))),"")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="151" t="n"/>
-      <c r="B19" s="151" t="n"/>
-      <c r="C19" s="152" t="n"/>
-      <c r="D19" s="151" t="n"/>
-      <c r="E19" s="151" t="n"/>
-      <c r="F19" s="150" t="n"/>
-      <c r="G19" s="162">
-        <f>IFERROR(IF(B19="Monthly",C19,IF(B19="Annual",C19/12,IF(B19="Weekly",C19*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H19" s="152">
-        <f>IFERROR(IF(A19&lt;&gt;"",G19,""),"")</f>
+      <c r="A19" s="153" t="n"/>
+      <c r="B19" s="153" t="n"/>
+      <c r="C19" s="154" t="n"/>
+      <c r="D19" s="153" t="n"/>
+      <c r="E19" s="153" t="n"/>
+      <c r="F19" s="152" t="n"/>
+      <c r="G19" s="154">
+        <f>IFERROR(IF(A19="","",IF(B19="Monthly",C19,IF(B19="Annual",C19/12,IF(B19="Weekly",C19*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="154">
+        <f>IFERROR(IF(A19="","",G19*12),"")</f>
         <v/>
       </c>
       <c r="I19" s="163">
@@ -35407,38 +34973,38 @@
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="147" t="n"/>
-      <c r="B20" s="147" t="n"/>
-      <c r="C20" s="148" t="n"/>
-      <c r="D20" s="147" t="n"/>
-      <c r="E20" s="147" t="n"/>
-      <c r="F20" s="146" t="n"/>
-      <c r="G20" s="160">
-        <f>IFERROR(IF(B20="Monthly",C20,IF(B20="Annual",C20/12,IF(B20="Weekly",C20*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H20" s="148">
-        <f>IFERROR(IF(A20&lt;&gt;"",G20,""),"")</f>
-        <v/>
-      </c>
-      <c r="I20" s="161">
+      <c r="A20" s="148" t="n"/>
+      <c r="B20" s="148" t="n"/>
+      <c r="C20" s="149" t="n"/>
+      <c r="D20" s="148" t="n"/>
+      <c r="E20" s="148" t="n"/>
+      <c r="F20" s="147" t="n"/>
+      <c r="G20" s="149">
+        <f>IFERROR(IF(A20="","",IF(B20="Monthly",C20,IF(B20="Annual",C20/12,IF(B20="Weekly",C20*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="149">
+        <f>IFERROR(IF(A20="","",G20*12),"")</f>
+        <v/>
+      </c>
+      <c r="I20" s="162">
         <f>IFERROR(IF(A20="","",IF(F20="","Unpaid",IF(AND(YEAR(F20)=YEAR(TODAY()),MONTH(F20)=MONTH(TODAY())),"Paid","Unpaid"))),"")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="151" t="n"/>
-      <c r="B21" s="151" t="n"/>
-      <c r="C21" s="152" t="n"/>
-      <c r="D21" s="151" t="n"/>
-      <c r="E21" s="151" t="n"/>
-      <c r="F21" s="150" t="n"/>
-      <c r="G21" s="162">
-        <f>IFERROR(IF(B21="Monthly",C21,IF(B21="Annual",C21/12,IF(B21="Weekly",C21*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="152">
-        <f>IFERROR(IF(A21&lt;&gt;"",G21,""),"")</f>
+      <c r="A21" s="153" t="n"/>
+      <c r="B21" s="153" t="n"/>
+      <c r="C21" s="154" t="n"/>
+      <c r="D21" s="153" t="n"/>
+      <c r="E21" s="153" t="n"/>
+      <c r="F21" s="152" t="n"/>
+      <c r="G21" s="154">
+        <f>IFERROR(IF(A21="","",IF(B21="Monthly",C21,IF(B21="Annual",C21/12,IF(B21="Weekly",C21*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="154">
+        <f>IFERROR(IF(A21="","",G21*12),"")</f>
         <v/>
       </c>
       <c r="I21" s="163">
@@ -35447,38 +35013,38 @@
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="147" t="n"/>
-      <c r="B22" s="147" t="n"/>
-      <c r="C22" s="148" t="n"/>
-      <c r="D22" s="147" t="n"/>
-      <c r="E22" s="147" t="n"/>
-      <c r="F22" s="146" t="n"/>
-      <c r="G22" s="160">
-        <f>IFERROR(IF(B22="Monthly",C22,IF(B22="Annual",C22/12,IF(B22="Weekly",C22*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="148">
-        <f>IFERROR(IF(A22&lt;&gt;"",G22,""),"")</f>
-        <v/>
-      </c>
-      <c r="I22" s="161">
+      <c r="A22" s="148" t="n"/>
+      <c r="B22" s="148" t="n"/>
+      <c r="C22" s="149" t="n"/>
+      <c r="D22" s="148" t="n"/>
+      <c r="E22" s="148" t="n"/>
+      <c r="F22" s="147" t="n"/>
+      <c r="G22" s="149">
+        <f>IFERROR(IF(A22="","",IF(B22="Monthly",C22,IF(B22="Annual",C22/12,IF(B22="Weekly",C22*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="149">
+        <f>IFERROR(IF(A22="","",G22*12),"")</f>
+        <v/>
+      </c>
+      <c r="I22" s="162">
         <f>IFERROR(IF(A22="","",IF(F22="","Unpaid",IF(AND(YEAR(F22)=YEAR(TODAY()),MONTH(F22)=MONTH(TODAY())),"Paid","Unpaid"))),"")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="151" t="n"/>
-      <c r="B23" s="151" t="n"/>
-      <c r="C23" s="152" t="n"/>
-      <c r="D23" s="151" t="n"/>
-      <c r="E23" s="151" t="n"/>
-      <c r="F23" s="150" t="n"/>
-      <c r="G23" s="162">
-        <f>IFERROR(IF(B23="Monthly",C23,IF(B23="Annual",C23/12,IF(B23="Weekly",C23*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="152">
-        <f>IFERROR(IF(A23&lt;&gt;"",G23,""),"")</f>
+      <c r="A23" s="153" t="n"/>
+      <c r="B23" s="153" t="n"/>
+      <c r="C23" s="154" t="n"/>
+      <c r="D23" s="153" t="n"/>
+      <c r="E23" s="153" t="n"/>
+      <c r="F23" s="152" t="n"/>
+      <c r="G23" s="154">
+        <f>IFERROR(IF(A23="","",IF(B23="Monthly",C23,IF(B23="Annual",C23/12,IF(B23="Weekly",C23*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="154">
+        <f>IFERROR(IF(A23="","",G23*12),"")</f>
         <v/>
       </c>
       <c r="I23" s="163">
@@ -35487,38 +35053,38 @@
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="147" t="n"/>
-      <c r="B24" s="147" t="n"/>
-      <c r="C24" s="148" t="n"/>
-      <c r="D24" s="147" t="n"/>
-      <c r="E24" s="147" t="n"/>
-      <c r="F24" s="146" t="n"/>
-      <c r="G24" s="160">
-        <f>IFERROR(IF(B24="Monthly",C24,IF(B24="Annual",C24/12,IF(B24="Weekly",C24*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="148">
-        <f>IFERROR(IF(A24&lt;&gt;"",G24,""),"")</f>
-        <v/>
-      </c>
-      <c r="I24" s="161">
+      <c r="A24" s="148" t="n"/>
+      <c r="B24" s="148" t="n"/>
+      <c r="C24" s="149" t="n"/>
+      <c r="D24" s="148" t="n"/>
+      <c r="E24" s="148" t="n"/>
+      <c r="F24" s="147" t="n"/>
+      <c r="G24" s="149">
+        <f>IFERROR(IF(A24="","",IF(B24="Monthly",C24,IF(B24="Annual",C24/12,IF(B24="Weekly",C24*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="149">
+        <f>IFERROR(IF(A24="","",G24*12),"")</f>
+        <v/>
+      </c>
+      <c r="I24" s="162">
         <f>IFERROR(IF(A24="","",IF(F24="","Unpaid",IF(AND(YEAR(F24)=YEAR(TODAY()),MONTH(F24)=MONTH(TODAY())),"Paid","Unpaid"))),"")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="151" t="n"/>
-      <c r="B25" s="151" t="n"/>
-      <c r="C25" s="152" t="n"/>
-      <c r="D25" s="151" t="n"/>
-      <c r="E25" s="151" t="n"/>
-      <c r="F25" s="150" t="n"/>
-      <c r="G25" s="162">
-        <f>IFERROR(IF(B25="Monthly",C25,IF(B25="Annual",C25/12,IF(B25="Weekly",C25*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="152">
-        <f>IFERROR(IF(A25&lt;&gt;"",G25,""),"")</f>
+      <c r="A25" s="153" t="n"/>
+      <c r="B25" s="153" t="n"/>
+      <c r="C25" s="154" t="n"/>
+      <c r="D25" s="153" t="n"/>
+      <c r="E25" s="153" t="n"/>
+      <c r="F25" s="152" t="n"/>
+      <c r="G25" s="154">
+        <f>IFERROR(IF(A25="","",IF(B25="Monthly",C25,IF(B25="Annual",C25/12,IF(B25="Weekly",C25*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="154">
+        <f>IFERROR(IF(A25="","",G25*12),"")</f>
         <v/>
       </c>
       <c r="I25" s="163">
@@ -35527,38 +35093,38 @@
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="147" t="n"/>
-      <c r="B26" s="147" t="n"/>
-      <c r="C26" s="148" t="n"/>
-      <c r="D26" s="147" t="n"/>
-      <c r="E26" s="147" t="n"/>
-      <c r="F26" s="146" t="n"/>
-      <c r="G26" s="160">
-        <f>IFERROR(IF(B26="Monthly",C26,IF(B26="Annual",C26/12,IF(B26="Weekly",C26*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="148">
-        <f>IFERROR(IF(A26&lt;&gt;"",G26,""),"")</f>
-        <v/>
-      </c>
-      <c r="I26" s="161">
+      <c r="A26" s="148" t="n"/>
+      <c r="B26" s="148" t="n"/>
+      <c r="C26" s="149" t="n"/>
+      <c r="D26" s="148" t="n"/>
+      <c r="E26" s="148" t="n"/>
+      <c r="F26" s="147" t="n"/>
+      <c r="G26" s="149">
+        <f>IFERROR(IF(A26="","",IF(B26="Monthly",C26,IF(B26="Annual",C26/12,IF(B26="Weekly",C26*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="149">
+        <f>IFERROR(IF(A26="","",G26*12),"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="162">
         <f>IFERROR(IF(A26="","",IF(F26="","Unpaid",IF(AND(YEAR(F26)=YEAR(TODAY()),MONTH(F26)=MONTH(TODAY())),"Paid","Unpaid"))),"")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="151" t="n"/>
-      <c r="B27" s="151" t="n"/>
-      <c r="C27" s="152" t="n"/>
-      <c r="D27" s="151" t="n"/>
-      <c r="E27" s="151" t="n"/>
-      <c r="F27" s="150" t="n"/>
-      <c r="G27" s="162">
-        <f>IFERROR(IF(B27="Monthly",C27,IF(B27="Annual",C27/12,IF(B27="Weekly",C27*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="152">
-        <f>IFERROR(IF(A27&lt;&gt;"",G27,""),"")</f>
+      <c r="A27" s="153" t="n"/>
+      <c r="B27" s="153" t="n"/>
+      <c r="C27" s="154" t="n"/>
+      <c r="D27" s="153" t="n"/>
+      <c r="E27" s="153" t="n"/>
+      <c r="F27" s="152" t="n"/>
+      <c r="G27" s="154">
+        <f>IFERROR(IF(A27="","",IF(B27="Monthly",C27,IF(B27="Annual",C27/12,IF(B27="Weekly",C27*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="154">
+        <f>IFERROR(IF(A27="","",G27*12),"")</f>
         <v/>
       </c>
       <c r="I27" s="163">
@@ -35567,38 +35133,38 @@
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="147" t="n"/>
-      <c r="B28" s="147" t="n"/>
-      <c r="C28" s="148" t="n"/>
-      <c r="D28" s="147" t="n"/>
-      <c r="E28" s="147" t="n"/>
-      <c r="F28" s="146" t="n"/>
-      <c r="G28" s="160">
-        <f>IFERROR(IF(B28="Monthly",C28,IF(B28="Annual",C28/12,IF(B28="Weekly",C28*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="148">
-        <f>IFERROR(IF(A28&lt;&gt;"",G28,""),"")</f>
-        <v/>
-      </c>
-      <c r="I28" s="161">
+      <c r="A28" s="148" t="n"/>
+      <c r="B28" s="148" t="n"/>
+      <c r="C28" s="149" t="n"/>
+      <c r="D28" s="148" t="n"/>
+      <c r="E28" s="148" t="n"/>
+      <c r="F28" s="147" t="n"/>
+      <c r="G28" s="149">
+        <f>IFERROR(IF(A28="","",IF(B28="Monthly",C28,IF(B28="Annual",C28/12,IF(B28="Weekly",C28*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="149">
+        <f>IFERROR(IF(A28="","",G28*12),"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="162">
         <f>IFERROR(IF(A28="","",IF(F28="","Unpaid",IF(AND(YEAR(F28)=YEAR(TODAY()),MONTH(F28)=MONTH(TODAY())),"Paid","Unpaid"))),"")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="151" t="n"/>
-      <c r="B29" s="151" t="n"/>
-      <c r="C29" s="152" t="n"/>
-      <c r="D29" s="151" t="n"/>
-      <c r="E29" s="151" t="n"/>
-      <c r="F29" s="150" t="n"/>
-      <c r="G29" s="162">
-        <f>IFERROR(IF(B29="Monthly",C29,IF(B29="Annual",C29/12,IF(B29="Weekly",C29*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="152">
-        <f>IFERROR(IF(A29&lt;&gt;"",G29,""),"")</f>
+      <c r="A29" s="153" t="n"/>
+      <c r="B29" s="153" t="n"/>
+      <c r="C29" s="154" t="n"/>
+      <c r="D29" s="153" t="n"/>
+      <c r="E29" s="153" t="n"/>
+      <c r="F29" s="152" t="n"/>
+      <c r="G29" s="154">
+        <f>IFERROR(IF(A29="","",IF(B29="Monthly",C29,IF(B29="Annual",C29/12,IF(B29="Weekly",C29*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="154">
+        <f>IFERROR(IF(A29="","",G29*12),"")</f>
         <v/>
       </c>
       <c r="I29" s="163">
@@ -35607,38 +35173,38 @@
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="147" t="n"/>
-      <c r="B30" s="147" t="n"/>
-      <c r="C30" s="148" t="n"/>
-      <c r="D30" s="147" t="n"/>
-      <c r="E30" s="147" t="n"/>
-      <c r="F30" s="146" t="n"/>
-      <c r="G30" s="160">
-        <f>IFERROR(IF(B30="Monthly",C30,IF(B30="Annual",C30/12,IF(B30="Weekly",C30*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H30" s="148">
-        <f>IFERROR(IF(A30&lt;&gt;"",G30,""),"")</f>
-        <v/>
-      </c>
-      <c r="I30" s="161">
+      <c r="A30" s="148" t="n"/>
+      <c r="B30" s="148" t="n"/>
+      <c r="C30" s="149" t="n"/>
+      <c r="D30" s="148" t="n"/>
+      <c r="E30" s="148" t="n"/>
+      <c r="F30" s="147" t="n"/>
+      <c r="G30" s="149">
+        <f>IFERROR(IF(A30="","",IF(B30="Monthly",C30,IF(B30="Annual",C30/12,IF(B30="Weekly",C30*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="149">
+        <f>IFERROR(IF(A30="","",G30*12),"")</f>
+        <v/>
+      </c>
+      <c r="I30" s="162">
         <f>IFERROR(IF(A30="","",IF(F30="","Unpaid",IF(AND(YEAR(F30)=YEAR(TODAY()),MONTH(F30)=MONTH(TODAY())),"Paid","Unpaid"))),"")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="151" t="n"/>
-      <c r="B31" s="151" t="n"/>
-      <c r="C31" s="152" t="n"/>
-      <c r="D31" s="151" t="n"/>
-      <c r="E31" s="151" t="n"/>
-      <c r="F31" s="150" t="n"/>
-      <c r="G31" s="162">
-        <f>IFERROR(IF(B31="Monthly",C31,IF(B31="Annual",C31/12,IF(B31="Weekly",C31*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="152">
-        <f>IFERROR(IF(A31&lt;&gt;"",G31,""),"")</f>
+      <c r="A31" s="153" t="n"/>
+      <c r="B31" s="153" t="n"/>
+      <c r="C31" s="154" t="n"/>
+      <c r="D31" s="153" t="n"/>
+      <c r="E31" s="153" t="n"/>
+      <c r="F31" s="152" t="n"/>
+      <c r="G31" s="154">
+        <f>IFERROR(IF(A31="","",IF(B31="Monthly",C31,IF(B31="Annual",C31/12,IF(B31="Weekly",C31*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="154">
+        <f>IFERROR(IF(A31="","",G31*12),"")</f>
         <v/>
       </c>
       <c r="I31" s="163">
@@ -35647,38 +35213,38 @@
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="147" t="n"/>
-      <c r="B32" s="147" t="n"/>
-      <c r="C32" s="148" t="n"/>
-      <c r="D32" s="147" t="n"/>
-      <c r="E32" s="147" t="n"/>
-      <c r="F32" s="146" t="n"/>
-      <c r="G32" s="160">
-        <f>IFERROR(IF(B32="Monthly",C32,IF(B32="Annual",C32/12,IF(B32="Weekly",C32*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="148">
-        <f>IFERROR(IF(A32&lt;&gt;"",G32,""),"")</f>
-        <v/>
-      </c>
-      <c r="I32" s="161">
+      <c r="A32" s="148" t="n"/>
+      <c r="B32" s="148" t="n"/>
+      <c r="C32" s="149" t="n"/>
+      <c r="D32" s="148" t="n"/>
+      <c r="E32" s="148" t="n"/>
+      <c r="F32" s="147" t="n"/>
+      <c r="G32" s="149">
+        <f>IFERROR(IF(A32="","",IF(B32="Monthly",C32,IF(B32="Annual",C32/12,IF(B32="Weekly",C32*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="149">
+        <f>IFERROR(IF(A32="","",G32*12),"")</f>
+        <v/>
+      </c>
+      <c r="I32" s="162">
         <f>IFERROR(IF(A32="","",IF(F32="","Unpaid",IF(AND(YEAR(F32)=YEAR(TODAY()),MONTH(F32)=MONTH(TODAY())),"Paid","Unpaid"))),"")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="151" t="n"/>
-      <c r="B33" s="151" t="n"/>
-      <c r="C33" s="152" t="n"/>
-      <c r="D33" s="151" t="n"/>
-      <c r="E33" s="151" t="n"/>
-      <c r="F33" s="150" t="n"/>
-      <c r="G33" s="162">
-        <f>IFERROR(IF(B33="Monthly",C33,IF(B33="Annual",C33/12,IF(B33="Weekly",C33*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="152">
-        <f>IFERROR(IF(A33&lt;&gt;"",G33,""),"")</f>
+      <c r="A33" s="153" t="n"/>
+      <c r="B33" s="153" t="n"/>
+      <c r="C33" s="154" t="n"/>
+      <c r="D33" s="153" t="n"/>
+      <c r="E33" s="153" t="n"/>
+      <c r="F33" s="152" t="n"/>
+      <c r="G33" s="154">
+        <f>IFERROR(IF(A33="","",IF(B33="Monthly",C33,IF(B33="Annual",C33/12,IF(B33="Weekly",C33*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="154">
+        <f>IFERROR(IF(A33="","",G33*12),"")</f>
         <v/>
       </c>
       <c r="I33" s="163">
@@ -35687,38 +35253,38 @@
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="147" t="n"/>
-      <c r="B34" s="147" t="n"/>
-      <c r="C34" s="148" t="n"/>
-      <c r="D34" s="147" t="n"/>
-      <c r="E34" s="147" t="n"/>
-      <c r="F34" s="146" t="n"/>
-      <c r="G34" s="160">
-        <f>IFERROR(IF(B34="Monthly",C34,IF(B34="Annual",C34/12,IF(B34="Weekly",C34*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H34" s="148">
-        <f>IFERROR(IF(A34&lt;&gt;"",G34,""),"")</f>
-        <v/>
-      </c>
-      <c r="I34" s="161">
+      <c r="A34" s="148" t="n"/>
+      <c r="B34" s="148" t="n"/>
+      <c r="C34" s="149" t="n"/>
+      <c r="D34" s="148" t="n"/>
+      <c r="E34" s="148" t="n"/>
+      <c r="F34" s="147" t="n"/>
+      <c r="G34" s="149">
+        <f>IFERROR(IF(A34="","",IF(B34="Monthly",C34,IF(B34="Annual",C34/12,IF(B34="Weekly",C34*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="149">
+        <f>IFERROR(IF(A34="","",G34*12),"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="162">
         <f>IFERROR(IF(A34="","",IF(F34="","Unpaid",IF(AND(YEAR(F34)=YEAR(TODAY()),MONTH(F34)=MONTH(TODAY())),"Paid","Unpaid"))),"")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="151" t="n"/>
-      <c r="B35" s="151" t="n"/>
-      <c r="C35" s="152" t="n"/>
-      <c r="D35" s="151" t="n"/>
-      <c r="E35" s="151" t="n"/>
-      <c r="F35" s="150" t="n"/>
-      <c r="G35" s="162">
-        <f>IFERROR(IF(B35="Monthly",C35,IF(B35="Annual",C35/12,IF(B35="Weekly",C35*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="152">
-        <f>IFERROR(IF(A35&lt;&gt;"",G35,""),"")</f>
+      <c r="A35" s="153" t="n"/>
+      <c r="B35" s="153" t="n"/>
+      <c r="C35" s="154" t="n"/>
+      <c r="D35" s="153" t="n"/>
+      <c r="E35" s="153" t="n"/>
+      <c r="F35" s="152" t="n"/>
+      <c r="G35" s="154">
+        <f>IFERROR(IF(A35="","",IF(B35="Monthly",C35,IF(B35="Annual",C35/12,IF(B35="Weekly",C35*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="154">
+        <f>IFERROR(IF(A35="","",G35*12),"")</f>
         <v/>
       </c>
       <c r="I35" s="163">
@@ -35727,38 +35293,38 @@
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="147" t="n"/>
-      <c r="B36" s="147" t="n"/>
-      <c r="C36" s="148" t="n"/>
-      <c r="D36" s="147" t="n"/>
-      <c r="E36" s="147" t="n"/>
-      <c r="F36" s="146" t="n"/>
-      <c r="G36" s="160">
-        <f>IFERROR(IF(B36="Monthly",C36,IF(B36="Annual",C36/12,IF(B36="Weekly",C36*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="148">
-        <f>IFERROR(IF(A36&lt;&gt;"",G36,""),"")</f>
-        <v/>
-      </c>
-      <c r="I36" s="161">
+      <c r="A36" s="148" t="n"/>
+      <c r="B36" s="148" t="n"/>
+      <c r="C36" s="149" t="n"/>
+      <c r="D36" s="148" t="n"/>
+      <c r="E36" s="148" t="n"/>
+      <c r="F36" s="147" t="n"/>
+      <c r="G36" s="149">
+        <f>IFERROR(IF(A36="","",IF(B36="Monthly",C36,IF(B36="Annual",C36/12,IF(B36="Weekly",C36*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="149">
+        <f>IFERROR(IF(A36="","",G36*12),"")</f>
+        <v/>
+      </c>
+      <c r="I36" s="162">
         <f>IFERROR(IF(A36="","",IF(F36="","Unpaid",IF(AND(YEAR(F36)=YEAR(TODAY()),MONTH(F36)=MONTH(TODAY())),"Paid","Unpaid"))),"")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="151" t="n"/>
-      <c r="B37" s="151" t="n"/>
-      <c r="C37" s="152" t="n"/>
-      <c r="D37" s="151" t="n"/>
-      <c r="E37" s="151" t="n"/>
-      <c r="F37" s="150" t="n"/>
-      <c r="G37" s="162">
-        <f>IFERROR(IF(B37="Monthly",C37,IF(B37="Annual",C37/12,IF(B37="Weekly",C37*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="152">
-        <f>IFERROR(IF(A37&lt;&gt;"",G37,""),"")</f>
+      <c r="A37" s="153" t="n"/>
+      <c r="B37" s="153" t="n"/>
+      <c r="C37" s="154" t="n"/>
+      <c r="D37" s="153" t="n"/>
+      <c r="E37" s="153" t="n"/>
+      <c r="F37" s="152" t="n"/>
+      <c r="G37" s="154">
+        <f>IFERROR(IF(A37="","",IF(B37="Monthly",C37,IF(B37="Annual",C37/12,IF(B37="Weekly",C37*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="154">
+        <f>IFERROR(IF(A37="","",G37*12),"")</f>
         <v/>
       </c>
       <c r="I37" s="163">
@@ -35767,38 +35333,38 @@
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="147" t="n"/>
-      <c r="B38" s="147" t="n"/>
-      <c r="C38" s="148" t="n"/>
-      <c r="D38" s="147" t="n"/>
-      <c r="E38" s="147" t="n"/>
-      <c r="F38" s="146" t="n"/>
-      <c r="G38" s="160">
-        <f>IFERROR(IF(B38="Monthly",C38,IF(B38="Annual",C38/12,IF(B38="Weekly",C38*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H38" s="148">
-        <f>IFERROR(IF(A38&lt;&gt;"",G38,""),"")</f>
-        <v/>
-      </c>
-      <c r="I38" s="161">
+      <c r="A38" s="148" t="n"/>
+      <c r="B38" s="148" t="n"/>
+      <c r="C38" s="149" t="n"/>
+      <c r="D38" s="148" t="n"/>
+      <c r="E38" s="148" t="n"/>
+      <c r="F38" s="147" t="n"/>
+      <c r="G38" s="149">
+        <f>IFERROR(IF(A38="","",IF(B38="Monthly",C38,IF(B38="Annual",C38/12,IF(B38="Weekly",C38*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="149">
+        <f>IFERROR(IF(A38="","",G38*12),"")</f>
+        <v/>
+      </c>
+      <c r="I38" s="162">
         <f>IFERROR(IF(A38="","",IF(F38="","Unpaid",IF(AND(YEAR(F38)=YEAR(TODAY()),MONTH(F38)=MONTH(TODAY())),"Paid","Unpaid"))),"")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="151" t="n"/>
-      <c r="B39" s="151" t="n"/>
-      <c r="C39" s="152" t="n"/>
-      <c r="D39" s="151" t="n"/>
-      <c r="E39" s="151" t="n"/>
-      <c r="F39" s="150" t="n"/>
-      <c r="G39" s="162">
-        <f>IFERROR(IF(B39="Monthly",C39,IF(B39="Annual",C39/12,IF(B39="Weekly",C39*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H39" s="152">
-        <f>IFERROR(IF(A39&lt;&gt;"",G39,""),"")</f>
+      <c r="A39" s="153" t="n"/>
+      <c r="B39" s="153" t="n"/>
+      <c r="C39" s="154" t="n"/>
+      <c r="D39" s="153" t="n"/>
+      <c r="E39" s="153" t="n"/>
+      <c r="F39" s="152" t="n"/>
+      <c r="G39" s="154">
+        <f>IFERROR(IF(A39="","",IF(B39="Monthly",C39,IF(B39="Annual",C39/12,IF(B39="Weekly",C39*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="154">
+        <f>IFERROR(IF(A39="","",G39*12),"")</f>
         <v/>
       </c>
       <c r="I39" s="163">
@@ -35807,38 +35373,38 @@
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="147" t="n"/>
-      <c r="B40" s="147" t="n"/>
-      <c r="C40" s="148" t="n"/>
-      <c r="D40" s="147" t="n"/>
-      <c r="E40" s="147" t="n"/>
-      <c r="F40" s="146" t="n"/>
-      <c r="G40" s="160">
-        <f>IFERROR(IF(B40="Monthly",C40,IF(B40="Annual",C40/12,IF(B40="Weekly",C40*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="148">
-        <f>IFERROR(IF(A40&lt;&gt;"",G40,""),"")</f>
-        <v/>
-      </c>
-      <c r="I40" s="161">
+      <c r="A40" s="148" t="n"/>
+      <c r="B40" s="148" t="n"/>
+      <c r="C40" s="149" t="n"/>
+      <c r="D40" s="148" t="n"/>
+      <c r="E40" s="148" t="n"/>
+      <c r="F40" s="147" t="n"/>
+      <c r="G40" s="149">
+        <f>IFERROR(IF(A40="","",IF(B40="Monthly",C40,IF(B40="Annual",C40/12,IF(B40="Weekly",C40*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="149">
+        <f>IFERROR(IF(A40="","",G40*12),"")</f>
+        <v/>
+      </c>
+      <c r="I40" s="162">
         <f>IFERROR(IF(A40="","",IF(F40="","Unpaid",IF(AND(YEAR(F40)=YEAR(TODAY()),MONTH(F40)=MONTH(TODAY())),"Paid","Unpaid"))),"")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="151" t="n"/>
-      <c r="B41" s="151" t="n"/>
-      <c r="C41" s="152" t="n"/>
-      <c r="D41" s="151" t="n"/>
-      <c r="E41" s="151" t="n"/>
-      <c r="F41" s="150" t="n"/>
-      <c r="G41" s="162">
-        <f>IFERROR(IF(B41="Monthly",C41,IF(B41="Annual",C41/12,IF(B41="Weekly",C41*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="152">
-        <f>IFERROR(IF(A41&lt;&gt;"",G41,""),"")</f>
+      <c r="A41" s="153" t="n"/>
+      <c r="B41" s="153" t="n"/>
+      <c r="C41" s="154" t="n"/>
+      <c r="D41" s="153" t="n"/>
+      <c r="E41" s="153" t="n"/>
+      <c r="F41" s="152" t="n"/>
+      <c r="G41" s="154">
+        <f>IFERROR(IF(A41="","",IF(B41="Monthly",C41,IF(B41="Annual",C41/12,IF(B41="Weekly",C41*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="154">
+        <f>IFERROR(IF(A41="","",G41*12),"")</f>
         <v/>
       </c>
       <c r="I41" s="163">
@@ -35847,38 +35413,38 @@
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="147" t="n"/>
-      <c r="B42" s="147" t="n"/>
-      <c r="C42" s="148" t="n"/>
-      <c r="D42" s="147" t="n"/>
-      <c r="E42" s="147" t="n"/>
-      <c r="F42" s="146" t="n"/>
-      <c r="G42" s="160">
-        <f>IFERROR(IF(B42="Monthly",C42,IF(B42="Annual",C42/12,IF(B42="Weekly",C42*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="148">
-        <f>IFERROR(IF(A42&lt;&gt;"",G42,""),"")</f>
-        <v/>
-      </c>
-      <c r="I42" s="161">
+      <c r="A42" s="148" t="n"/>
+      <c r="B42" s="148" t="n"/>
+      <c r="C42" s="149" t="n"/>
+      <c r="D42" s="148" t="n"/>
+      <c r="E42" s="148" t="n"/>
+      <c r="F42" s="147" t="n"/>
+      <c r="G42" s="149">
+        <f>IFERROR(IF(A42="","",IF(B42="Monthly",C42,IF(B42="Annual",C42/12,IF(B42="Weekly",C42*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="149">
+        <f>IFERROR(IF(A42="","",G42*12),"")</f>
+        <v/>
+      </c>
+      <c r="I42" s="162">
         <f>IFERROR(IF(A42="","",IF(F42="","Unpaid",IF(AND(YEAR(F42)=YEAR(TODAY()),MONTH(F42)=MONTH(TODAY())),"Paid","Unpaid"))),"")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="151" t="n"/>
-      <c r="B43" s="151" t="n"/>
-      <c r="C43" s="152" t="n"/>
-      <c r="D43" s="151" t="n"/>
-      <c r="E43" s="151" t="n"/>
-      <c r="F43" s="150" t="n"/>
-      <c r="G43" s="162">
-        <f>IFERROR(IF(B43="Monthly",C43,IF(B43="Annual",C43/12,IF(B43="Weekly",C43*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="152">
-        <f>IFERROR(IF(A43&lt;&gt;"",G43,""),"")</f>
+      <c r="A43" s="153" t="n"/>
+      <c r="B43" s="153" t="n"/>
+      <c r="C43" s="154" t="n"/>
+      <c r="D43" s="153" t="n"/>
+      <c r="E43" s="153" t="n"/>
+      <c r="F43" s="152" t="n"/>
+      <c r="G43" s="154">
+        <f>IFERROR(IF(A43="","",IF(B43="Monthly",C43,IF(B43="Annual",C43/12,IF(B43="Weekly",C43*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="154">
+        <f>IFERROR(IF(A43="","",G43*12),"")</f>
         <v/>
       </c>
       <c r="I43" s="163">
@@ -35887,38 +35453,38 @@
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="147" t="n"/>
-      <c r="B44" s="147" t="n"/>
-      <c r="C44" s="148" t="n"/>
-      <c r="D44" s="147" t="n"/>
-      <c r="E44" s="147" t="n"/>
-      <c r="F44" s="146" t="n"/>
-      <c r="G44" s="160">
-        <f>IFERROR(IF(B44="Monthly",C44,IF(B44="Annual",C44/12,IF(B44="Weekly",C44*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H44" s="148">
-        <f>IFERROR(IF(A44&lt;&gt;"",G44,""),"")</f>
-        <v/>
-      </c>
-      <c r="I44" s="161">
+      <c r="A44" s="148" t="n"/>
+      <c r="B44" s="148" t="n"/>
+      <c r="C44" s="149" t="n"/>
+      <c r="D44" s="148" t="n"/>
+      <c r="E44" s="148" t="n"/>
+      <c r="F44" s="147" t="n"/>
+      <c r="G44" s="149">
+        <f>IFERROR(IF(A44="","",IF(B44="Monthly",C44,IF(B44="Annual",C44/12,IF(B44="Weekly",C44*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="149">
+        <f>IFERROR(IF(A44="","",G44*12),"")</f>
+        <v/>
+      </c>
+      <c r="I44" s="162">
         <f>IFERROR(IF(A44="","",IF(F44="","Unpaid",IF(AND(YEAR(F44)=YEAR(TODAY()),MONTH(F44)=MONTH(TODAY())),"Paid","Unpaid"))),"")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="151" t="n"/>
-      <c r="B45" s="151" t="n"/>
-      <c r="C45" s="152" t="n"/>
-      <c r="D45" s="151" t="n"/>
-      <c r="E45" s="151" t="n"/>
-      <c r="F45" s="150" t="n"/>
-      <c r="G45" s="162">
-        <f>IFERROR(IF(B45="Monthly",C45,IF(B45="Annual",C45/12,IF(B45="Weekly",C45*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="152">
-        <f>IFERROR(IF(A45&lt;&gt;"",G45,""),"")</f>
+      <c r="A45" s="153" t="n"/>
+      <c r="B45" s="153" t="n"/>
+      <c r="C45" s="154" t="n"/>
+      <c r="D45" s="153" t="n"/>
+      <c r="E45" s="153" t="n"/>
+      <c r="F45" s="152" t="n"/>
+      <c r="G45" s="154">
+        <f>IFERROR(IF(A45="","",IF(B45="Monthly",C45,IF(B45="Annual",C45/12,IF(B45="Weekly",C45*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="154">
+        <f>IFERROR(IF(A45="","",G45*12),"")</f>
         <v/>
       </c>
       <c r="I45" s="163">
@@ -35927,38 +35493,38 @@
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="147" t="n"/>
-      <c r="B46" s="147" t="n"/>
-      <c r="C46" s="148" t="n"/>
-      <c r="D46" s="147" t="n"/>
-      <c r="E46" s="147" t="n"/>
-      <c r="F46" s="146" t="n"/>
-      <c r="G46" s="160">
-        <f>IFERROR(IF(B46="Monthly",C46,IF(B46="Annual",C46/12,IF(B46="Weekly",C46*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H46" s="148">
-        <f>IFERROR(IF(A46&lt;&gt;"",G46,""),"")</f>
-        <v/>
-      </c>
-      <c r="I46" s="161">
+      <c r="A46" s="148" t="n"/>
+      <c r="B46" s="148" t="n"/>
+      <c r="C46" s="149" t="n"/>
+      <c r="D46" s="148" t="n"/>
+      <c r="E46" s="148" t="n"/>
+      <c r="F46" s="147" t="n"/>
+      <c r="G46" s="149">
+        <f>IFERROR(IF(A46="","",IF(B46="Monthly",C46,IF(B46="Annual",C46/12,IF(B46="Weekly",C46*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="149">
+        <f>IFERROR(IF(A46="","",G46*12),"")</f>
+        <v/>
+      </c>
+      <c r="I46" s="162">
         <f>IFERROR(IF(A46="","",IF(F46="","Unpaid",IF(AND(YEAR(F46)=YEAR(TODAY()),MONTH(F46)=MONTH(TODAY())),"Paid","Unpaid"))),"")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="151" t="n"/>
-      <c r="B47" s="151" t="n"/>
-      <c r="C47" s="152" t="n"/>
-      <c r="D47" s="151" t="n"/>
-      <c r="E47" s="151" t="n"/>
-      <c r="F47" s="150" t="n"/>
-      <c r="G47" s="162">
-        <f>IFERROR(IF(B47="Monthly",C47,IF(B47="Annual",C47/12,IF(B47="Weekly",C47*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H47" s="152">
-        <f>IFERROR(IF(A47&lt;&gt;"",G47,""),"")</f>
+      <c r="A47" s="153" t="n"/>
+      <c r="B47" s="153" t="n"/>
+      <c r="C47" s="154" t="n"/>
+      <c r="D47" s="153" t="n"/>
+      <c r="E47" s="153" t="n"/>
+      <c r="F47" s="152" t="n"/>
+      <c r="G47" s="154">
+        <f>IFERROR(IF(A47="","",IF(B47="Monthly",C47,IF(B47="Annual",C47/12,IF(B47="Weekly",C47*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="154">
+        <f>IFERROR(IF(A47="","",G47*12),"")</f>
         <v/>
       </c>
       <c r="I47" s="163">
@@ -35967,38 +35533,38 @@
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="147" t="n"/>
-      <c r="B48" s="147" t="n"/>
-      <c r="C48" s="148" t="n"/>
-      <c r="D48" s="147" t="n"/>
-      <c r="E48" s="147" t="n"/>
-      <c r="F48" s="146" t="n"/>
-      <c r="G48" s="160">
-        <f>IFERROR(IF(B48="Monthly",C48,IF(B48="Annual",C48/12,IF(B48="Weekly",C48*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H48" s="148">
-        <f>IFERROR(IF(A48&lt;&gt;"",G48,""),"")</f>
-        <v/>
-      </c>
-      <c r="I48" s="161">
+      <c r="A48" s="148" t="n"/>
+      <c r="B48" s="148" t="n"/>
+      <c r="C48" s="149" t="n"/>
+      <c r="D48" s="148" t="n"/>
+      <c r="E48" s="148" t="n"/>
+      <c r="F48" s="147" t="n"/>
+      <c r="G48" s="149">
+        <f>IFERROR(IF(A48="","",IF(B48="Monthly",C48,IF(B48="Annual",C48/12,IF(B48="Weekly",C48*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H48" s="149">
+        <f>IFERROR(IF(A48="","",G48*12),"")</f>
+        <v/>
+      </c>
+      <c r="I48" s="162">
         <f>IFERROR(IF(A48="","",IF(F48="","Unpaid",IF(AND(YEAR(F48)=YEAR(TODAY()),MONTH(F48)=MONTH(TODAY())),"Paid","Unpaid"))),"")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="151" t="n"/>
-      <c r="B49" s="151" t="n"/>
-      <c r="C49" s="152" t="n"/>
-      <c r="D49" s="151" t="n"/>
-      <c r="E49" s="151" t="n"/>
-      <c r="F49" s="150" t="n"/>
-      <c r="G49" s="162">
-        <f>IFERROR(IF(B49="Monthly",C49,IF(B49="Annual",C49/12,IF(B49="Weekly",C49*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H49" s="152">
-        <f>IFERROR(IF(A49&lt;&gt;"",G49,""),"")</f>
+      <c r="A49" s="153" t="n"/>
+      <c r="B49" s="153" t="n"/>
+      <c r="C49" s="154" t="n"/>
+      <c r="D49" s="153" t="n"/>
+      <c r="E49" s="153" t="n"/>
+      <c r="F49" s="152" t="n"/>
+      <c r="G49" s="154">
+        <f>IFERROR(IF(A49="","",IF(B49="Monthly",C49,IF(B49="Annual",C49/12,IF(B49="Weekly",C49*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="154">
+        <f>IFERROR(IF(A49="","",G49*12),"")</f>
         <v/>
       </c>
       <c r="I49" s="163">
@@ -36007,38 +35573,38 @@
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="147" t="n"/>
-      <c r="B50" s="147" t="n"/>
-      <c r="C50" s="148" t="n"/>
-      <c r="D50" s="147" t="n"/>
-      <c r="E50" s="147" t="n"/>
-      <c r="F50" s="146" t="n"/>
-      <c r="G50" s="160">
-        <f>IFERROR(IF(B50="Monthly",C50,IF(B50="Annual",C50/12,IF(B50="Weekly",C50*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H50" s="148">
-        <f>IFERROR(IF(A50&lt;&gt;"",G50,""),"")</f>
-        <v/>
-      </c>
-      <c r="I50" s="161">
+      <c r="A50" s="148" t="n"/>
+      <c r="B50" s="148" t="n"/>
+      <c r="C50" s="149" t="n"/>
+      <c r="D50" s="148" t="n"/>
+      <c r="E50" s="148" t="n"/>
+      <c r="F50" s="147" t="n"/>
+      <c r="G50" s="149">
+        <f>IFERROR(IF(A50="","",IF(B50="Monthly",C50,IF(B50="Annual",C50/12,IF(B50="Weekly",C50*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="149">
+        <f>IFERROR(IF(A50="","",G50*12),"")</f>
+        <v/>
+      </c>
+      <c r="I50" s="162">
         <f>IFERROR(IF(A50="","",IF(F50="","Unpaid",IF(AND(YEAR(F50)=YEAR(TODAY()),MONTH(F50)=MONTH(TODAY())),"Paid","Unpaid"))),"")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="151" t="n"/>
-      <c r="B51" s="151" t="n"/>
-      <c r="C51" s="152" t="n"/>
-      <c r="D51" s="151" t="n"/>
-      <c r="E51" s="151" t="n"/>
-      <c r="F51" s="150" t="n"/>
-      <c r="G51" s="162">
-        <f>IFERROR(IF(B51="Monthly",C51,IF(B51="Annual",C51/12,IF(B51="Weekly",C51*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H51" s="152">
-        <f>IFERROR(IF(A51&lt;&gt;"",G51,""),"")</f>
+      <c r="A51" s="153" t="n"/>
+      <c r="B51" s="153" t="n"/>
+      <c r="C51" s="154" t="n"/>
+      <c r="D51" s="153" t="n"/>
+      <c r="E51" s="153" t="n"/>
+      <c r="F51" s="152" t="n"/>
+      <c r="G51" s="154">
+        <f>IFERROR(IF(A51="","",IF(B51="Monthly",C51,IF(B51="Annual",C51/12,IF(B51="Weekly",C51*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="154">
+        <f>IFERROR(IF(A51="","",G51*12),"")</f>
         <v/>
       </c>
       <c r="I51" s="163">
@@ -36047,38 +35613,38 @@
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="147" t="n"/>
-      <c r="B52" s="147" t="n"/>
-      <c r="C52" s="148" t="n"/>
-      <c r="D52" s="147" t="n"/>
-      <c r="E52" s="147" t="n"/>
-      <c r="F52" s="146" t="n"/>
-      <c r="G52" s="160">
-        <f>IFERROR(IF(B52="Monthly",C52,IF(B52="Annual",C52/12,IF(B52="Weekly",C52*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H52" s="148">
-        <f>IFERROR(IF(A52&lt;&gt;"",G52,""),"")</f>
-        <v/>
-      </c>
-      <c r="I52" s="161">
+      <c r="A52" s="148" t="n"/>
+      <c r="B52" s="148" t="n"/>
+      <c r="C52" s="149" t="n"/>
+      <c r="D52" s="148" t="n"/>
+      <c r="E52" s="148" t="n"/>
+      <c r="F52" s="147" t="n"/>
+      <c r="G52" s="149">
+        <f>IFERROR(IF(A52="","",IF(B52="Monthly",C52,IF(B52="Annual",C52/12,IF(B52="Weekly",C52*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H52" s="149">
+        <f>IFERROR(IF(A52="","",G52*12),"")</f>
+        <v/>
+      </c>
+      <c r="I52" s="162">
         <f>IFERROR(IF(A52="","",IF(F52="","Unpaid",IF(AND(YEAR(F52)=YEAR(TODAY()),MONTH(F52)=MONTH(TODAY())),"Paid","Unpaid"))),"")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="151" t="n"/>
-      <c r="B53" s="151" t="n"/>
-      <c r="C53" s="152" t="n"/>
-      <c r="D53" s="151" t="n"/>
-      <c r="E53" s="151" t="n"/>
-      <c r="F53" s="150" t="n"/>
-      <c r="G53" s="162">
-        <f>IFERROR(IF(B53="Monthly",C53,IF(B53="Annual",C53/12,IF(B53="Weekly",C53*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H53" s="152">
-        <f>IFERROR(IF(A53&lt;&gt;"",G53,""),"")</f>
+      <c r="A53" s="153" t="n"/>
+      <c r="B53" s="153" t="n"/>
+      <c r="C53" s="154" t="n"/>
+      <c r="D53" s="153" t="n"/>
+      <c r="E53" s="153" t="n"/>
+      <c r="F53" s="152" t="n"/>
+      <c r="G53" s="154">
+        <f>IFERROR(IF(A53="","",IF(B53="Monthly",C53,IF(B53="Annual",C53/12,IF(B53="Weekly",C53*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H53" s="154">
+        <f>IFERROR(IF(A53="","",G53*12),"")</f>
         <v/>
       </c>
       <c r="I53" s="163">
@@ -36087,38 +35653,38 @@
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="147" t="n"/>
-      <c r="B54" s="147" t="n"/>
-      <c r="C54" s="148" t="n"/>
-      <c r="D54" s="147" t="n"/>
-      <c r="E54" s="147" t="n"/>
-      <c r="F54" s="146" t="n"/>
-      <c r="G54" s="160">
-        <f>IFERROR(IF(B54="Monthly",C54,IF(B54="Annual",C54/12,IF(B54="Weekly",C54*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H54" s="148">
-        <f>IFERROR(IF(A54&lt;&gt;"",G54,""),"")</f>
-        <v/>
-      </c>
-      <c r="I54" s="161">
+      <c r="A54" s="148" t="n"/>
+      <c r="B54" s="148" t="n"/>
+      <c r="C54" s="149" t="n"/>
+      <c r="D54" s="148" t="n"/>
+      <c r="E54" s="148" t="n"/>
+      <c r="F54" s="147" t="n"/>
+      <c r="G54" s="149">
+        <f>IFERROR(IF(A54="","",IF(B54="Monthly",C54,IF(B54="Annual",C54/12,IF(B54="Weekly",C54*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H54" s="149">
+        <f>IFERROR(IF(A54="","",G54*12),"")</f>
+        <v/>
+      </c>
+      <c r="I54" s="162">
         <f>IFERROR(IF(A54="","",IF(F54="","Unpaid",IF(AND(YEAR(F54)=YEAR(TODAY()),MONTH(F54)=MONTH(TODAY())),"Paid","Unpaid"))),"")</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="151" t="n"/>
-      <c r="B55" s="151" t="n"/>
-      <c r="C55" s="152" t="n"/>
-      <c r="D55" s="151" t="n"/>
-      <c r="E55" s="151" t="n"/>
-      <c r="F55" s="150" t="n"/>
-      <c r="G55" s="162">
-        <f>IFERROR(IF(B55="Monthly",C55,IF(B55="Annual",C55/12,IF(B55="Weekly",C55*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H55" s="152">
-        <f>IFERROR(IF(A55&lt;&gt;"",G55,""),"")</f>
+      <c r="A55" s="153" t="n"/>
+      <c r="B55" s="153" t="n"/>
+      <c r="C55" s="154" t="n"/>
+      <c r="D55" s="153" t="n"/>
+      <c r="E55" s="153" t="n"/>
+      <c r="F55" s="152" t="n"/>
+      <c r="G55" s="154">
+        <f>IFERROR(IF(A55="","",IF(B55="Monthly",C55,IF(B55="Annual",C55/12,IF(B55="Weekly",C55*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H55" s="154">
+        <f>IFERROR(IF(A55="","",G55*12),"")</f>
         <v/>
       </c>
       <c r="I55" s="163">
@@ -36127,38 +35693,38 @@
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="147" t="n"/>
-      <c r="B56" s="147" t="n"/>
-      <c r="C56" s="148" t="n"/>
-      <c r="D56" s="147" t="n"/>
-      <c r="E56" s="147" t="n"/>
-      <c r="F56" s="146" t="n"/>
-      <c r="G56" s="160">
-        <f>IFERROR(IF(B56="Monthly",C56,IF(B56="Annual",C56/12,IF(B56="Weekly",C56*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H56" s="148">
-        <f>IFERROR(IF(A56&lt;&gt;"",G56,""),"")</f>
-        <v/>
-      </c>
-      <c r="I56" s="161">
+      <c r="A56" s="148" t="n"/>
+      <c r="B56" s="148" t="n"/>
+      <c r="C56" s="149" t="n"/>
+      <c r="D56" s="148" t="n"/>
+      <c r="E56" s="148" t="n"/>
+      <c r="F56" s="147" t="n"/>
+      <c r="G56" s="149">
+        <f>IFERROR(IF(A56="","",IF(B56="Monthly",C56,IF(B56="Annual",C56/12,IF(B56="Weekly",C56*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H56" s="149">
+        <f>IFERROR(IF(A56="","",G56*12),"")</f>
+        <v/>
+      </c>
+      <c r="I56" s="162">
         <f>IFERROR(IF(A56="","",IF(F56="","Unpaid",IF(AND(YEAR(F56)=YEAR(TODAY()),MONTH(F56)=MONTH(TODAY())),"Paid","Unpaid"))),"")</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="151" t="n"/>
-      <c r="B57" s="151" t="n"/>
-      <c r="C57" s="152" t="n"/>
-      <c r="D57" s="151" t="n"/>
-      <c r="E57" s="151" t="n"/>
-      <c r="F57" s="150" t="n"/>
-      <c r="G57" s="162">
-        <f>IFERROR(IF(B57="Monthly",C57,IF(B57="Annual",C57/12,IF(B57="Weekly",C57*4.33,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H57" s="152">
-        <f>IFERROR(IF(A57&lt;&gt;"",G57,""),"")</f>
+      <c r="A57" s="153" t="n"/>
+      <c r="B57" s="153" t="n"/>
+      <c r="C57" s="154" t="n"/>
+      <c r="D57" s="153" t="n"/>
+      <c r="E57" s="153" t="n"/>
+      <c r="F57" s="152" t="n"/>
+      <c r="G57" s="154">
+        <f>IFERROR(IF(A57="","",IF(B57="Monthly",C57,IF(B57="Annual",C57/12,IF(B57="Weekly",C57*52/12,0)))),"")</f>
+        <v/>
+      </c>
+      <c r="H57" s="154">
+        <f>IFERROR(IF(A57="","",G57*12),"")</f>
         <v/>
       </c>
       <c r="I57" s="163">
@@ -36167,9 +35733,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A7:I7"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="A8:I57">
@@ -36190,15 +35755,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8:H57">
-    <cfRule type="dataBar" priority="4">
-      <dataBar>
-        <cfvo type="min" val="0"/>
-        <cfvo type="max"/>
-        <color rgb="007C3AED"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="B8:B57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Monthly,Annual,Weekly"</formula1>
